--- a/Versão5/PRO/Ontologia_Requisitos.xlsx
+++ b/Versão5/PRO/Ontologia_Requisitos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BB745B5-E4F9-4E61-9C81-87DCFE07C250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9320349-EDE4-4ED2-A4BD-93183BA72435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -1173,15 +1173,7 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="13">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
+  <dxfs count="12">
     <dxf>
       <font>
         <b val="0"/>
@@ -1808,7 +1800,7 @@
       </c>
       <c r="B18" s="41">
         <f ca="1">NOW()</f>
-        <v>46248.591620370367</v>
+        <v>46248.601714004632</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>96</v>
@@ -4223,15 +4215,15 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:C1 L1:W1 Y1:Z1 AB1:XFD1 A24:C1048576 L24:W1048576 Y24:XFD1048576">
-    <cfRule type="cellIs" dxfId="12" priority="429" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="429" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="11" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="AA1:AA23 A2:B23">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4384,7 +4376,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4474,7 +4466,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="8" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="7" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5491,31 +5483,26 @@
     <sortCondition ref="A1:A13"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B15 F2:G14">
-    <cfRule type="cellIs" dxfId="7" priority="16" operator="equal">
+  <conditionalFormatting sqref="A1:B15 F2:G14 D1:U1 H2:U15">
+    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B1 B7:B15">
-    <cfRule type="duplicateValues" dxfId="6" priority="1964"/>
     <cfRule type="duplicateValues" dxfId="5" priority="1963"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1964"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B6">
-    <cfRule type="duplicateValues" dxfId="4" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="29"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="2" priority="19" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:U1 D7:E15 F15:H15">
-    <cfRule type="cellIs" dxfId="1" priority="39" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H2:U15">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+  <conditionalFormatting sqref="D7:E15 F15:H15">
+    <cfRule type="cellIs" dxfId="0" priority="39" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/PRO/Ontologia_Requisitos.xlsx
+++ b/Versão5/PRO/Ontologia_Requisitos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9320349-EDE4-4ED2-A4BD-93183BA72435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA7C9B6-780D-47E1-9329-50D7A4D9652F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="843" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="216">
   <si>
     <t>Key</t>
   </si>
@@ -304,9 +304,6 @@
     <t>Equivalente a</t>
   </si>
   <si>
-    <t>ClasseIFC</t>
-  </si>
-  <si>
     <t>CategoriaRvt</t>
   </si>
   <si>
@@ -484,24 +481,6 @@
     <t>Necessidades.Projetuais</t>
   </si>
   <si>
-    <t>Necessidade.Sistema.Avac</t>
-  </si>
-  <si>
-    <t>Necessidade.Sistema.Hidráulico</t>
-  </si>
-  <si>
-    <t>Necessidade.Sistema.Elétrico</t>
-  </si>
-  <si>
-    <t>Necessidade.Sistema.Incêndio</t>
-  </si>
-  <si>
-    <t>Necessidade.Sistema.Sanitário</t>
-  </si>
-  <si>
-    <t>Necessidade.Sistema.Lógico</t>
-  </si>
-  <si>
     <t>categoria.revit</t>
   </si>
   <si>
@@ -625,24 +604,6 @@
     <t>Requisitadas</t>
   </si>
   <si>
-    <t>É.Requisito.Sistema.Avac</t>
-  </si>
-  <si>
-    <t>É.Requisito.Sistema.Hidráulico</t>
-  </si>
-  <si>
-    <t>É.Requisito.Sistema.Elétrico</t>
-  </si>
-  <si>
-    <t>É.Requisito.Sistema.Incêndio</t>
-  </si>
-  <si>
-    <t>É.Requisito.Sistema.Sanitário</t>
-  </si>
-  <si>
-    <t>É.Requisito.Sistema.Lógico</t>
-  </si>
-  <si>
     <t>Atendidas</t>
   </si>
   <si>
@@ -671,6 +632,93 @@
   </si>
   <si>
     <t>"Equipe de Instalações"</t>
+  </si>
+  <si>
+    <t>É.Requisito.Avac</t>
+  </si>
+  <si>
+    <t>É.Requisito.Hidráulico</t>
+  </si>
+  <si>
+    <t>É.Requisito.Elétrico</t>
+  </si>
+  <si>
+    <t>É.Requisito.Incêndio</t>
+  </si>
+  <si>
+    <t>É.Requisito.Sanitário</t>
+  </si>
+  <si>
+    <t>É.Requisito.Lógico</t>
+  </si>
+  <si>
+    <t>Necessidade.Avac</t>
+  </si>
+  <si>
+    <t>Necessidade.Incêndio</t>
+  </si>
+  <si>
+    <t>Necessidade.Hidráulica</t>
+  </si>
+  <si>
+    <t>Necessidade.Elétrica</t>
+  </si>
+  <si>
+    <t>Necessidade.Sanitária</t>
+  </si>
+  <si>
+    <t>Necessidade.Lógica</t>
+  </si>
+  <si>
+    <t>é.tipo</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. General requirements.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</t>
+  </si>
+  <si>
+    <t>Defines the Project-Specific Requirements Program.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos generales.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos espaciales para el proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de mobiliario para el proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de equipamiento para el proyecto.</t>
+  </si>
+  <si>
+    <t>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</t>
+  </si>
+  <si>
+    <t>Define el Programa de Requisitos Específicos del Proyecto.</t>
+  </si>
+  <si>
+    <t>Parâmetro Rvt</t>
+  </si>
+  <si>
+    <t>Atributo IFC</t>
+  </si>
+  <si>
+    <t>Classe IFC</t>
+  </si>
+  <si>
+    <t>[ - ]</t>
   </si>
 </sst>
 </file>
@@ -985,7 +1033,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1167,13 +1215,44 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="15">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1235,14 +1314,6 @@
         <b val="0"/>
         <i/>
         <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
         <color rgb="FFFFFFFF"/>
       </font>
     </dxf>
@@ -1252,6 +1323,14 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -1597,15 +1676,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="47" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="2" max="2" width="68.84375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="47" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
@@ -1613,10 +1692,10 @@
         <v>34</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
@@ -1624,21 +1703,21 @@
         <v>60</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C3" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -1646,10 +1725,10 @@
         <v>46</v>
       </c>
       <c r="C4" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -1658,10 +1737,10 @@
         <v>BIMProp</v>
       </c>
       <c r="C5" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -1670,10 +1749,10 @@
         <v>BIMData</v>
       </c>
       <c r="C6" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -1681,21 +1760,21 @@
         <v>47</v>
       </c>
       <c r="C7" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C8" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -1703,10 +1782,10 @@
         <v>49</v>
       </c>
       <c r="C9" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
@@ -1714,10 +1793,10 @@
         <v>23</v>
       </c>
       <c r="C10" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -1725,10 +1804,10 @@
         <v>23</v>
       </c>
       <c r="C11" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
@@ -1736,10 +1815,10 @@
         <v>23</v>
       </c>
       <c r="C12" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
@@ -1747,10 +1826,10 @@
         <v>23</v>
       </c>
       <c r="C13" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
@@ -1758,10 +1837,10 @@
         <v>23</v>
       </c>
       <c r="C14" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -1769,10 +1848,10 @@
         <v>23</v>
       </c>
       <c r="C15" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
@@ -1780,66 +1859,66 @@
         <v>23</v>
       </c>
       <c r="C16" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C17" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="41">
         <f ca="1">NOW()</f>
-        <v>46248.601714004632</v>
+        <v>46253.78771365741</v>
       </c>
       <c r="C18" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C19" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C20" s="46" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>23</v>
       </c>
       <c r="C21" s="46" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>56</v>
       </c>
@@ -1847,10 +1926,10 @@
         <v>23</v>
       </c>
       <c r="C22" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
@@ -1858,21 +1937,21 @@
         <v>23</v>
       </c>
       <c r="C23" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C24" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
@@ -1881,162 +1960,162 @@
         <v>Formalizar los conceptos de los elementos de Requisitos del Proyecto.</v>
       </c>
       <c r="C25" s="46" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B26" s="11" t="str">
         <f>_xlfn.TRANSLATE(B25,"pt","en")</f>
         <v>Formalizar los conceptos de los elementos de Requisitos del Proyecto.</v>
       </c>
       <c r="C26" s="46" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="B27" s="54" t="s">
         <v>106</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="C27" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="B28" s="55" t="s">
+        <v>108</v>
+      </c>
+      <c r="C28" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A29" s="8" t="s">
+        <v>109</v>
+      </c>
+      <c r="B29" s="55" t="s">
+        <v>110</v>
+      </c>
+      <c r="C29" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="B30" s="40" t="s">
+        <v>85</v>
+      </c>
+      <c r="C30" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="B31" s="40" t="s">
+        <v>84</v>
+      </c>
+      <c r="C31" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="B32" s="40" t="s">
+        <v>87</v>
+      </c>
+      <c r="C32" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="42" t="s">
+        <v>83</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="B34" s="42" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="B35" s="40" t="s">
+        <v>86</v>
+      </c>
+      <c r="C35" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B36" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="C36" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="8" t="s">
+        <v>118</v>
+      </c>
+      <c r="B37" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A38" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="B38" s="56" t="s">
+        <v>120</v>
+      </c>
+      <c r="C38" s="46" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A39" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="B39" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="C39" s="46" t="s">
         <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="B28" s="55" t="s">
-        <v>109</v>
-      </c>
-      <c r="C28" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8" t="s">
-        <v>110</v>
-      </c>
-      <c r="B29" s="55" t="s">
-        <v>111</v>
-      </c>
-      <c r="C29" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B30" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B31" s="40" t="s">
-        <v>85</v>
-      </c>
-      <c r="C31" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B33" s="42" t="s">
-        <v>84</v>
-      </c>
-      <c r="C33" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B34" s="42" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B35" s="40" t="s">
-        <v>87</v>
-      </c>
-      <c r="C35" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B36" s="42" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="8" t="s">
-        <v>119</v>
-      </c>
-      <c r="B37" s="40" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" s="56" t="s">
-        <v>121</v>
-      </c>
-      <c r="C38" s="46" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="B39" s="57" t="s">
-        <v>123</v>
-      </c>
-      <c r="C39" s="46" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -2055,35 +2134,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AA23"/>
-  <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AC23"/>
+  <sheetFormatPr defaultColWidth="32.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.7109375" style="28" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" style="28" customWidth="1"/>
-    <col min="5" max="5" width="7.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="28" customWidth="1"/>
-    <col min="7" max="11" width="7.85546875" style="28" customWidth="1"/>
-    <col min="12" max="12" width="13.140625" style="28" customWidth="1"/>
-    <col min="13" max="13" width="13.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.5703125" style="28" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.42578125" style="28" customWidth="1"/>
-    <col min="16" max="16" width="52.140625" style="28" customWidth="1"/>
-    <col min="17" max="17" width="59.85546875" style="28" customWidth="1"/>
-    <col min="18" max="18" width="3.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13" style="28" customWidth="1"/>
-    <col min="20" max="20" width="13.7109375" style="28" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="17.5703125" style="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="7.85546875" style="28" customWidth="1"/>
-    <col min="25" max="25" width="5.7109375" style="28" customWidth="1"/>
-    <col min="26" max="26" width="18.5703125" style="28" customWidth="1"/>
-    <col min="27" max="27" width="57" style="28" customWidth="1"/>
-    <col min="28" max="16384" width="32.140625" style="28"/>
+    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.23046875" style="28" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" style="28" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.15234375" style="28" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.4609375" style="28" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.4609375" style="28" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" style="28" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.3046875" style="28" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.53515625" style="28" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.61328125" style="28" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="54.15234375" style="28" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="49.69140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.07421875" style="28" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.3046875" style="28" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="6.07421875" style="28" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="5.23046875" style="28" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="6.15234375" style="28" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="6.765625" style="28" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.3828125" style="28" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.07421875" style="28" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="15.69140625" style="28" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="32.15234375" style="28"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="40.299999999999997" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -2135,55 +2217,61 @@
       <c r="Q1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="R1" s="15" t="s">
+      <c r="R1" s="45" t="s">
+        <v>91</v>
+      </c>
+      <c r="S1" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="T1" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="T1" s="15" t="s">
+      <c r="U1" s="15" t="s">
         <v>72</v>
       </c>
-      <c r="U1" s="16" t="s">
+      <c r="V1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="V1" s="15" t="s">
+      <c r="W1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="W1" s="51" t="s">
+      <c r="X1" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="X1" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y1" s="15" t="s">
+      <c r="Y1" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="Z1" s="15" t="s">
-        <v>91</v>
-      </c>
-      <c r="AA1" s="45" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="2" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Z1" s="16" t="s">
+        <v>212</v>
+      </c>
+      <c r="AA1" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="AB1" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="AC1" s="15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="53">
         <v>2</v>
       </c>
       <c r="B2" s="58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C2" s="58" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D2" s="59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F2" s="59" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="G2" s="50" t="s">
         <v>1</v>
@@ -2217,66 +2305,70 @@
         <v>É Requisito Geral</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q2" s="24" t="str">
-        <f t="shared" ref="Q2:Q3" si="4">_xlfn.TRANSLATE(P2,"pt","es")</f>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos generales.</v>
+        <v>172</v>
+      </c>
+      <c r="Q2" s="24" t="s">
+        <v>206</v>
       </c>
       <c r="R2" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="24" t="str">
-        <f t="shared" ref="S2:S3" si="5">SUBSTITUTE(C2, ".", " ")</f>
+        <v>200</v>
+      </c>
+      <c r="S2" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T2" s="24" t="str">
+        <f t="shared" ref="T2:T3" si="4">SUBSTITUTE(C2, ".", " ")</f>
         <v>Programáticos</v>
       </c>
-      <c r="T2" s="24" t="str">
-        <f t="shared" ref="T2:T3" si="6">SUBSTITUTE(D2, ".", " ")</f>
+      <c r="U2" s="24" t="str">
+        <f t="shared" ref="U2:U3" si="5">SUBSTITUTE(D2, ".", " ")</f>
         <v>Necessidades</v>
       </c>
-      <c r="U2" s="24" t="str">
-        <f t="shared" ref="U2:U3" si="7">SUBSTITUTE(E2, ".", " ")</f>
+      <c r="V2" s="24" t="str">
+        <f t="shared" ref="V2:V3" si="6">SUBSTITUTE(E2, ".", " ")</f>
         <v>Requisitadas</v>
       </c>
-      <c r="V2" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W2" s="52" t="str">
-        <f t="shared" ref="W2:W3" si="8">CONCATENATE("Key-REQ-",A2)</f>
+      <c r="W2" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X2" s="52" t="str">
+        <f t="shared" ref="X2:X3" si="7">CONCATENATE("Key-REQ-",A2)</f>
         <v>Key-REQ-2</v>
       </c>
-      <c r="X2" s="24" t="s">
-        <v>1</v>
-      </c>
       <c r="Y2" s="24" t="s">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="Z2" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA2" s="24" t="str">
-        <f t="shared" ref="AA2:AA3" si="9">_xlfn.TRANSLATE(P2,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. General requirements.</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="AA2" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB2" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC2" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="3" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="53">
         <v>3</v>
       </c>
       <c r="B3" s="58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C3" s="58" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D3" s="59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F3" s="59" t="s">
-        <v>193</v>
+        <v>180</v>
       </c>
       <c r="G3" s="50" t="s">
         <v>1</v>
@@ -2310,66 +2402,70 @@
         <v>É Requisito Pessoal</v>
       </c>
       <c r="P3" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q3" s="24" t="str">
+        <v>101</v>
+      </c>
+      <c r="Q3" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="R3" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="S3" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T3" s="24" t="str">
         <f t="shared" si="4"/>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos espaciales para el proyecto.</v>
-      </c>
-      <c r="R3" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S3" s="24" t="str">
+        <v>Programáticos</v>
+      </c>
+      <c r="U3" s="24" t="str">
         <f t="shared" si="5"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="T3" s="24" t="str">
+        <v>Necessidades</v>
+      </c>
+      <c r="V3" s="24" t="str">
         <f t="shared" si="6"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="U3" s="24" t="str">
+        <v>Requisitadas</v>
+      </c>
+      <c r="W3" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X3" s="52" t="str">
         <f t="shared" si="7"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V3" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W3" s="52" t="str">
-        <f t="shared" si="8"/>
         <v>Key-REQ-3</v>
       </c>
-      <c r="X3" s="24" t="s">
-        <v>1</v>
-      </c>
       <c r="Y3" s="24" t="s">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="Z3" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA3" s="24" t="str">
-        <f t="shared" si="9"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="4" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="AA3" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB3" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC3" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="4" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="53">
         <v>4</v>
       </c>
       <c r="B4" s="58" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="58" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="D4" s="59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E4" s="59" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="F4" s="59" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="G4" s="50" t="s">
         <v>1</v>
@@ -2387,809 +2483,845 @@
         <v>1</v>
       </c>
       <c r="L4" s="23" t="str">
-        <f t="shared" ref="L4:M14" si="10">CONCATENATE("", C4)</f>
+        <f t="shared" ref="L4:M14" si="8">CONCATENATE("", C4)</f>
         <v>Programáticos</v>
       </c>
       <c r="M4" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="N4" s="23" t="str">
+        <f t="shared" ref="N4:O14" si="9">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E4),"."," ")," De "," de "))</f>
+        <v>Requisitadas</v>
+      </c>
+      <c r="O4" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>É Requisito Espacial</v>
+      </c>
+      <c r="P4" s="24" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q4" s="24" t="s">
+        <v>207</v>
+      </c>
+      <c r="R4" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="S4" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T4" s="24" t="str">
+        <f t="shared" ref="T4:V14" si="10">SUBSTITUTE(C4, ".", " ")</f>
+        <v>Programáticos</v>
+      </c>
+      <c r="U4" s="24" t="str">
         <f t="shared" si="10"/>
         <v>Necessidades</v>
       </c>
-      <c r="N4" s="23" t="str">
-        <f t="shared" ref="N4:O14" si="11">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E4),"."," ")," De "," de "))</f>
+      <c r="V4" s="24" t="str">
+        <f t="shared" si="10"/>
         <v>Requisitadas</v>
       </c>
-      <c r="O4" s="23" t="str">
+      <c r="W4" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X4" s="52" t="str">
+        <f t="shared" ref="X4:X18" si="11">CONCATENATE("Key-REQ-",A4)</f>
+        <v>Key-REQ-4</v>
+      </c>
+      <c r="Y4" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z4" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA4" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB4" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC4" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="5" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="53">
+        <v>5</v>
+      </c>
+      <c r="B5" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D5" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="G5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L5" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="M5" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="N5" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="O5" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>É Requisito Mobiliário</v>
+      </c>
+      <c r="P5" s="24" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q5" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="R5" s="24" t="s">
+        <v>202</v>
+      </c>
+      <c r="S5" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T5" s="24" t="str">
+        <f t="shared" si="10"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="U5" s="24" t="str">
+        <f t="shared" si="10"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="V5" s="24" t="str">
+        <f t="shared" si="10"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="W5" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X5" s="52" t="str">
         <f t="shared" si="11"/>
-        <v>É Requisito Espacial</v>
-      </c>
-      <c r="P4" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="Q4" s="24" t="str">
-        <f t="shared" ref="Q4:Q23" si="12">_xlfn.TRANSLATE(P4,"pt","es")</f>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos espaciales para el proyecto.</v>
-      </c>
-      <c r="R4" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S4" s="24" t="str">
-        <f t="shared" ref="S4:U14" si="13">SUBSTITUTE(C4, ".", " ")</f>
+        <v>Key-REQ-5</v>
+      </c>
+      <c r="Y5" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z5" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA5" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB5" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC5" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="53">
+        <v>6</v>
+      </c>
+      <c r="B6" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D6" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>153</v>
+      </c>
+      <c r="G6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L6" s="23" t="str">
+        <f t="shared" si="8"/>
         <v>Programáticos</v>
       </c>
-      <c r="T4" s="24" t="str">
+      <c r="M6" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="N6" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="O6" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>É Requisito Equipamento</v>
+      </c>
+      <c r="P6" s="24" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q6" s="24" t="s">
+        <v>209</v>
+      </c>
+      <c r="R6" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="S6" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T6" s="24" t="str">
+        <f t="shared" si="10"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="U6" s="24" t="str">
+        <f t="shared" si="10"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="V6" s="24" t="str">
+        <f t="shared" si="10"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="W6" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X6" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-REQ-6</v>
+      </c>
+      <c r="Y6" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z6" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA6" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB6" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC6" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="7" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="53">
+        <v>7</v>
+      </c>
+      <c r="B7" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D7" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F7" s="59" t="s">
+        <v>187</v>
+      </c>
+      <c r="G7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L7" s="23" t="str">
+        <f t="shared" ref="L7:L11" si="12">CONCATENATE("", C7)</f>
+        <v>Programáticos</v>
+      </c>
+      <c r="M7" s="23" t="str">
+        <f t="shared" ref="M7:M11" si="13">CONCATENATE("", D7)</f>
+        <v>Necessidades</v>
+      </c>
+      <c r="N7" s="23" t="str">
+        <f t="shared" ref="N7:N11" si="14">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
+        <v>Requisitadas</v>
+      </c>
+      <c r="O7" s="23" t="str">
+        <f t="shared" ref="O7:O11" si="15">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
+        <v>É Requisito Avac</v>
+      </c>
+      <c r="P7" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q7" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="R7" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="S7" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T7" s="24" t="str">
+        <f t="shared" ref="T7:T11" si="16">SUBSTITUTE(C7, ".", " ")</f>
+        <v>Programáticos</v>
+      </c>
+      <c r="U7" s="24" t="str">
+        <f t="shared" ref="U7:U11" si="17">SUBSTITUTE(D7, ".", " ")</f>
+        <v>Necessidades</v>
+      </c>
+      <c r="V7" s="24" t="str">
+        <f t="shared" ref="V7:V11" si="18">SUBSTITUTE(E7, ".", " ")</f>
+        <v>Requisitadas</v>
+      </c>
+      <c r="W7" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X7" s="52" t="str">
+        <f t="shared" ref="X7:X11" si="19">CONCATENATE("Key-REQ-",A7)</f>
+        <v>Key-REQ-7</v>
+      </c>
+      <c r="Y7" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z7" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA7" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB7" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC7" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="53">
+        <v>8</v>
+      </c>
+      <c r="B8" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D8" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F8" s="59" t="s">
+        <v>188</v>
+      </c>
+      <c r="G8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L8" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="M8" s="23" t="str">
         <f t="shared" si="13"/>
         <v>Necessidades</v>
       </c>
-      <c r="U4" s="24" t="str">
+      <c r="N8" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="O8" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>É Requisito Hidráulico</v>
+      </c>
+      <c r="P8" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q8" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="R8" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="S8" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T8" s="24" t="str">
+        <f t="shared" si="16"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="U8" s="24" t="str">
+        <f t="shared" si="17"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="V8" s="24" t="str">
+        <f t="shared" si="18"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="W8" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X8" s="52" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-REQ-8</v>
+      </c>
+      <c r="Y8" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z8" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA8" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB8" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC8" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="53">
+        <v>9</v>
+      </c>
+      <c r="B9" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F9" s="59" t="s">
+        <v>189</v>
+      </c>
+      <c r="G9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L9" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="M9" s="23" t="str">
         <f t="shared" si="13"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="N9" s="23" t="str">
+        <f t="shared" si="14"/>
         <v>Requisitadas</v>
       </c>
-      <c r="V4" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W4" s="52" t="str">
-        <f t="shared" ref="W4:W18" si="14">CONCATENATE("Key-REQ-",A4)</f>
-        <v>Key-REQ-4</v>
-      </c>
-      <c r="X4" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA4" s="24" t="str">
-        <f t="shared" ref="AA4:AA14" si="15">_xlfn.TRANSLATE(P4,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Spatial Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="53">
-        <v>5</v>
-      </c>
-      <c r="B5" s="58" t="s">
+      <c r="O9" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>É Requisito Elétrico</v>
+      </c>
+      <c r="P9" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q9" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="R9" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="S9" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T9" s="24" t="str">
+        <f t="shared" si="16"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="U9" s="24" t="str">
+        <f t="shared" si="17"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="V9" s="24" t="str">
+        <f t="shared" si="18"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="W9" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X9" s="52" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-REQ-9</v>
+      </c>
+      <c r="Y9" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z9" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA9" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB9" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC9" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D5" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E5" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F5" s="59" t="s">
-        <v>159</v>
-      </c>
-      <c r="G5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L5" s="23" t="str">
+    </row>
+    <row r="10" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="53">
+        <v>10</v>
+      </c>
+      <c r="B10" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D10" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E10" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F10" s="59" t="s">
+        <v>190</v>
+      </c>
+      <c r="G10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L10" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="M10" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="N10" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="O10" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>É Requisito Incêndio</v>
+      </c>
+      <c r="P10" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q10" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="R10" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="S10" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T10" s="24" t="str">
+        <f t="shared" si="16"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="U10" s="24" t="str">
+        <f t="shared" si="17"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="V10" s="24" t="str">
+        <f t="shared" si="18"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="W10" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X10" s="52" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-REQ-10</v>
+      </c>
+      <c r="Y10" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z10" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA10" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB10" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC10" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="11" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="53">
+        <v>11</v>
+      </c>
+      <c r="B11" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D11" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>191</v>
+      </c>
+      <c r="G11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L11" s="23" t="str">
+        <f t="shared" si="12"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="M11" s="23" t="str">
+        <f t="shared" si="13"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="N11" s="23" t="str">
+        <f t="shared" si="14"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="O11" s="23" t="str">
+        <f t="shared" si="15"/>
+        <v>É Requisito Sanitário</v>
+      </c>
+      <c r="P11" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q11" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="R11" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="S11" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T11" s="24" t="str">
+        <f t="shared" si="16"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="U11" s="24" t="str">
+        <f t="shared" si="17"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="V11" s="24" t="str">
+        <f t="shared" si="18"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="W11" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X11" s="52" t="str">
+        <f t="shared" si="19"/>
+        <v>Key-REQ-11</v>
+      </c>
+      <c r="Y11" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z11" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA11" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB11" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC11" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="53">
+        <v>12</v>
+      </c>
+      <c r="B12" s="58" t="s">
+        <v>123</v>
+      </c>
+      <c r="C12" s="58" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="E12" s="59" t="s">
+        <v>176</v>
+      </c>
+      <c r="F12" s="59" t="s">
+        <v>192</v>
+      </c>
+      <c r="G12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L12" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Programáticos</v>
+      </c>
+      <c r="M12" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Necessidades</v>
+      </c>
+      <c r="N12" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="O12" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>É Requisito Lógico</v>
+      </c>
+      <c r="P12" s="24" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q12" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="R12" s="24" t="s">
+        <v>204</v>
+      </c>
+      <c r="S12" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T12" s="24" t="str">
         <f t="shared" si="10"/>
         <v>Programáticos</v>
       </c>
-      <c r="M5" s="23" t="str">
+      <c r="U12" s="24" t="str">
         <f t="shared" si="10"/>
         <v>Necessidades</v>
       </c>
-      <c r="N5" s="23" t="str">
+      <c r="V12" s="24" t="str">
+        <f t="shared" si="10"/>
+        <v>Requisitadas</v>
+      </c>
+      <c r="W12" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X12" s="52" t="str">
         <f t="shared" si="11"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="O5" s="23" t="str">
-        <f t="shared" si="11"/>
-        <v>É Requisito Mobiliário</v>
-      </c>
-      <c r="P5" s="24" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q5" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de mobiliario para el proyecto.</v>
-      </c>
-      <c r="R5" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S5" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="T5" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="U5" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V5" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W5" s="52" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-REQ-5</v>
-      </c>
-      <c r="X5" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA5" s="24" t="str">
-        <f t="shared" si="15"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Furniture Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="53">
-        <v>6</v>
-      </c>
-      <c r="B6" s="58" t="s">
+        <v>Key-REQ-12</v>
+      </c>
+      <c r="Y12" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z12" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA12" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB12" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC12" s="24" t="s">
         <v>124</v>
       </c>
-      <c r="C6" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F6" s="59" t="s">
-        <v>160</v>
-      </c>
-      <c r="G6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L6" s="23" t="str">
-        <f t="shared" si="10"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="M6" s="23" t="str">
-        <f t="shared" si="10"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="N6" s="23" t="str">
-        <f t="shared" si="11"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="O6" s="23" t="str">
-        <f t="shared" si="11"/>
-        <v>É Requisito Equipamento</v>
-      </c>
-      <c r="P6" s="24" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q6" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de equipamiento para el proyecto.</v>
-      </c>
-      <c r="R6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S6" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="T6" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="U6" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V6" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W6" s="52" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-REQ-6</v>
-      </c>
-      <c r="X6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA6" s="24" t="str">
-        <f t="shared" si="15"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Equipment Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="53">
-        <v>7</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C7" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D7" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E7" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F7" s="59" t="s">
-        <v>184</v>
-      </c>
-      <c r="G7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L7" s="23" t="str">
-        <f t="shared" ref="L7:L11" si="16">CONCATENATE("", C7)</f>
-        <v>Programáticos</v>
-      </c>
-      <c r="M7" s="23" t="str">
-        <f t="shared" ref="M7:M11" si="17">CONCATENATE("", D7)</f>
-        <v>Necessidades</v>
-      </c>
-      <c r="N7" s="23" t="str">
-        <f t="shared" ref="N7:N11" si="18">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E7),"."," ")," De "," de "))</f>
-        <v>Requisitadas</v>
-      </c>
-      <c r="O7" s="23" t="str">
-        <f t="shared" ref="O7:O11" si="19">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F7),"."," ")," De "," de "))</f>
-        <v>É Requisito Sistema Avac</v>
-      </c>
-      <c r="P7" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q7" s="24" t="str">
-        <f t="shared" ref="Q7:Q11" si="20">_xlfn.TRANSLATE(P7,"pt","es")</f>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</v>
-      </c>
-      <c r="R7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S7" s="24" t="str">
-        <f t="shared" ref="S7:S11" si="21">SUBSTITUTE(C7, ".", " ")</f>
-        <v>Programáticos</v>
-      </c>
-      <c r="T7" s="24" t="str">
-        <f t="shared" ref="T7:T11" si="22">SUBSTITUTE(D7, ".", " ")</f>
-        <v>Necessidades</v>
-      </c>
-      <c r="U7" s="24" t="str">
-        <f t="shared" ref="U7:U11" si="23">SUBSTITUTE(E7, ".", " ")</f>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V7" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W7" s="52" t="str">
-        <f t="shared" ref="W7:W11" si="24">CONCATENATE("Key-REQ-",A7)</f>
-        <v>Key-REQ-7</v>
-      </c>
-      <c r="X7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA7" s="24" t="str">
-        <f t="shared" ref="AA7:AA11" si="25">_xlfn.TRANSLATE(P7,"pt","en")</f>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="53">
-        <v>8</v>
-      </c>
-      <c r="B8" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F8" s="59" t="s">
-        <v>185</v>
-      </c>
-      <c r="G8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L8" s="23" t="str">
-        <f t="shared" si="16"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="M8" s="23" t="str">
-        <f t="shared" si="17"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="N8" s="23" t="str">
-        <f t="shared" si="18"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="O8" s="23" t="str">
-        <f t="shared" si="19"/>
-        <v>É Requisito Sistema Hidráulico</v>
-      </c>
-      <c r="P8" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q8" s="24" t="str">
-        <f t="shared" si="20"/>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</v>
-      </c>
-      <c r="R8" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S8" s="24" t="str">
-        <f t="shared" si="21"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="T8" s="24" t="str">
-        <f t="shared" si="22"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="U8" s="24" t="str">
-        <f t="shared" si="23"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V8" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W8" s="52" t="str">
-        <f t="shared" si="24"/>
-        <v>Key-REQ-8</v>
-      </c>
-      <c r="X8" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA8" s="24" t="str">
-        <f t="shared" si="25"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="53">
-        <v>9</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C9" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D9" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F9" s="59" t="s">
-        <v>186</v>
-      </c>
-      <c r="G9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L9" s="23" t="str">
-        <f t="shared" si="16"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="M9" s="23" t="str">
-        <f t="shared" si="17"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="N9" s="23" t="str">
-        <f t="shared" si="18"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="O9" s="23" t="str">
-        <f t="shared" si="19"/>
-        <v>É Requisito Sistema Elétrico</v>
-      </c>
-      <c r="P9" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q9" s="24" t="str">
-        <f t="shared" si="20"/>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</v>
-      </c>
-      <c r="R9" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S9" s="24" t="str">
-        <f t="shared" si="21"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="T9" s="24" t="str">
-        <f t="shared" si="22"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="U9" s="24" t="str">
-        <f t="shared" si="23"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V9" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W9" s="52" t="str">
-        <f t="shared" si="24"/>
-        <v>Key-REQ-9</v>
-      </c>
-      <c r="X9" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA9" s="24" t="str">
-        <f t="shared" si="25"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="53">
-        <v>10</v>
-      </c>
-      <c r="B10" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C10" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D10" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E10" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F10" s="59" t="s">
-        <v>187</v>
-      </c>
-      <c r="G10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L10" s="23" t="str">
-        <f t="shared" si="16"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="M10" s="23" t="str">
-        <f t="shared" si="17"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="N10" s="23" t="str">
-        <f t="shared" si="18"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="O10" s="23" t="str">
-        <f t="shared" si="19"/>
-        <v>É Requisito Sistema Incêndio</v>
-      </c>
-      <c r="P10" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q10" s="24" t="str">
-        <f t="shared" si="20"/>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</v>
-      </c>
-      <c r="R10" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S10" s="24" t="str">
-        <f t="shared" si="21"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="T10" s="24" t="str">
-        <f t="shared" si="22"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="U10" s="24" t="str">
-        <f t="shared" si="23"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V10" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W10" s="52" t="str">
-        <f t="shared" si="24"/>
-        <v>Key-REQ-10</v>
-      </c>
-      <c r="X10" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA10" s="24" t="str">
-        <f t="shared" si="25"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="53">
-        <v>11</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D11" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E11" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F11" s="59" t="s">
-        <v>188</v>
-      </c>
-      <c r="G11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L11" s="23" t="str">
-        <f t="shared" si="16"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="M11" s="23" t="str">
-        <f t="shared" si="17"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="N11" s="23" t="str">
-        <f t="shared" si="18"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="O11" s="23" t="str">
-        <f t="shared" si="19"/>
-        <v>É Requisito Sistema Sanitário</v>
-      </c>
-      <c r="P11" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q11" s="24" t="str">
-        <f t="shared" si="20"/>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</v>
-      </c>
-      <c r="R11" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S11" s="24" t="str">
-        <f t="shared" si="21"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="T11" s="24" t="str">
-        <f t="shared" si="22"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="U11" s="24" t="str">
-        <f t="shared" si="23"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V11" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W11" s="52" t="str">
-        <f t="shared" si="24"/>
-        <v>Key-REQ-11</v>
-      </c>
-      <c r="X11" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA11" s="24" t="str">
-        <f t="shared" si="25"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="53">
-        <v>12</v>
-      </c>
-      <c r="B12" s="58" t="s">
-        <v>124</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>182</v>
-      </c>
-      <c r="D12" s="59" t="s">
-        <v>129</v>
-      </c>
-      <c r="E12" s="59" t="s">
-        <v>183</v>
-      </c>
-      <c r="F12" s="59" t="s">
-        <v>189</v>
-      </c>
-      <c r="G12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L12" s="23" t="str">
-        <f t="shared" si="10"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="M12" s="23" t="str">
-        <f t="shared" si="10"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="N12" s="23" t="str">
-        <f t="shared" si="11"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="O12" s="23" t="str">
-        <f t="shared" si="11"/>
-        <v>É Requisito Sistema Lógico</v>
-      </c>
-      <c r="P12" s="24" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q12" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define un contenedor de información de acuerdo con la norma NBR 19650-1. Requisitos de los sistemas de construcción para el proyecto.</v>
-      </c>
-      <c r="R12" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S12" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Programáticos</v>
-      </c>
-      <c r="T12" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Necessidades</v>
-      </c>
-      <c r="U12" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Requisitadas</v>
-      </c>
-      <c r="V12" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W12" s="52" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-REQ-12</v>
-      </c>
-      <c r="X12" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA12" s="24" t="str">
-        <f t="shared" si="15"/>
-        <v>Defines an information container in accordance with the NBR 19650-1 standard. Building Systems Requirements for the Project.</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="53">
         <v>13</v>
       </c>
@@ -3197,16 +3329,16 @@
         <v>74</v>
       </c>
       <c r="C13" s="58" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D13" s="59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E13" s="59" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F13" s="59" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="G13" s="50" t="s">
         <v>1</v>
@@ -3224,65 +3356,69 @@
         <v>1</v>
       </c>
       <c r="L13" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>De.Necessidades</v>
+      </c>
+      <c r="M13" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Necessidades.Projetuais</v>
+      </c>
+      <c r="N13" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="O13" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>Necessidade Geral</v>
+      </c>
+      <c r="P13" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q13" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R13" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S13" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T13" s="24" t="str">
         <f t="shared" si="10"/>
-        <v>De.Necessidades</v>
-      </c>
-      <c r="M13" s="23" t="str">
+        <v>De Necessidades</v>
+      </c>
+      <c r="U13" s="24" t="str">
         <f t="shared" si="10"/>
-        <v>Necessidades.Projetuais</v>
-      </c>
-      <c r="N13" s="23" t="str">
-        <f t="shared" si="11"/>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V13" s="24" t="str">
+        <f t="shared" si="10"/>
         <v>Atendidas</v>
       </c>
-      <c r="O13" s="23" t="str">
-        <f t="shared" si="11"/>
-        <v>Necessidade Geral</v>
-      </c>
-      <c r="P13" s="24" t="s">
+      <c r="W13" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="Q13" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R13" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S13" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T13" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U13" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V13" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W13" s="52" t="str">
-        <f t="shared" ref="W13:W14" si="26">CONCATENATE("Key-REQ-",A13)</f>
+      <c r="X13" s="52" t="str">
+        <f t="shared" ref="X13:X14" si="20">CONCATENATE("Key-REQ-",A13)</f>
         <v>Key-REQ-13</v>
       </c>
-      <c r="X13" s="24" t="s">
-        <v>1</v>
-      </c>
       <c r="Y13" s="24" t="s">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="Z13" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA13" s="24" t="str">
-        <f t="shared" si="15"/>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="AA13" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB13" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC13" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="53">
         <v>14</v>
       </c>
@@ -3290,16 +3426,16 @@
         <v>74</v>
       </c>
       <c r="C14" s="58" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D14" s="59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F14" s="59" t="s">
-        <v>192</v>
+        <v>179</v>
       </c>
       <c r="G14" s="50" t="s">
         <v>1</v>
@@ -3317,65 +3453,69 @@
         <v>1</v>
       </c>
       <c r="L14" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>De.Necessidades</v>
+      </c>
+      <c r="M14" s="23" t="str">
+        <f t="shared" si="8"/>
+        <v>Necessidades.Projetuais</v>
+      </c>
+      <c r="N14" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="O14" s="23" t="str">
+        <f t="shared" si="9"/>
+        <v>Necessidade Pessoal</v>
+      </c>
+      <c r="P14" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q14" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R14" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S14" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T14" s="24" t="str">
         <f t="shared" si="10"/>
-        <v>De.Necessidades</v>
-      </c>
-      <c r="M14" s="23" t="str">
+        <v>De Necessidades</v>
+      </c>
+      <c r="U14" s="24" t="str">
         <f t="shared" si="10"/>
-        <v>Necessidades.Projetuais</v>
-      </c>
-      <c r="N14" s="23" t="str">
-        <f t="shared" si="11"/>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V14" s="24" t="str">
+        <f t="shared" si="10"/>
         <v>Atendidas</v>
       </c>
-      <c r="O14" s="23" t="str">
-        <f t="shared" si="11"/>
-        <v>Necessidade Pessoal</v>
-      </c>
-      <c r="P14" s="24" t="s">
+      <c r="W14" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="Q14" s="24" t="str">
-        <f t="shared" ref="Q14" si="27">_xlfn.TRANSLATE(P14,"pt","es")</f>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R14" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S14" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T14" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U14" s="24" t="str">
-        <f t="shared" si="13"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V14" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W14" s="52" t="str">
-        <f t="shared" si="26"/>
+      <c r="X14" s="52" t="str">
+        <f t="shared" si="20"/>
         <v>Key-REQ-14</v>
       </c>
-      <c r="X14" s="24" t="s">
-        <v>1</v>
-      </c>
       <c r="Y14" s="24" t="s">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="Z14" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA14" s="24" t="str">
-        <f t="shared" si="15"/>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="AA14" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB14" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC14" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="15" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="53">
         <v>15</v>
       </c>
@@ -3383,16 +3523,16 @@
         <v>74</v>
       </c>
       <c r="C15" s="58" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D15" s="59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E15" s="59" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F15" s="59" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G15" s="50" t="s">
         <v>1</v>
@@ -3410,65 +3550,69 @@
         <v>1</v>
       </c>
       <c r="L15" s="23" t="str">
-        <f t="shared" ref="L15:L18" si="28">CONCATENATE("", C15)</f>
+        <f t="shared" ref="L15:L18" si="21">CONCATENATE("", C15)</f>
         <v>De.Necessidades</v>
       </c>
       <c r="M15" s="23" t="str">
-        <f t="shared" ref="M15:M18" si="29">CONCATENATE("", D15)</f>
+        <f t="shared" ref="M15:M18" si="22">CONCATENATE("", D15)</f>
         <v>Necessidades.Projetuais</v>
       </c>
       <c r="N15" s="23" t="str">
-        <f t="shared" ref="N15:N18" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N15:N18" si="23">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E15),"."," ")," De "," de "))</f>
         <v>Atendidas</v>
       </c>
       <c r="O15" s="23" t="str">
-        <f t="shared" ref="O15:O18" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F15),"."," ")," De "," de "))</f>
+        <f t="shared" ref="O15:O18" si="24">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F15),"."," ")," De "," de "))</f>
         <v>Necessidade Espacial</v>
       </c>
       <c r="P15" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q15" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R15" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S15" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T15" s="24" t="str">
+        <f t="shared" ref="T15:T18" si="25">SUBSTITUTE(C15, ".", " ")</f>
+        <v>De Necessidades</v>
+      </c>
+      <c r="U15" s="24" t="str">
+        <f t="shared" ref="U15:U18" si="26">SUBSTITUTE(D15, ".", " ")</f>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V15" s="24" t="str">
+        <f t="shared" ref="V15:V23" si="27">SUBSTITUTE(E15, ".", " ")</f>
+        <v>Atendidas</v>
+      </c>
+      <c r="W15" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="Q15" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R15" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S15" s="24" t="str">
-        <f t="shared" ref="S15:S18" si="32">SUBSTITUTE(C15, ".", " ")</f>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T15" s="24" t="str">
-        <f t="shared" ref="T15:T18" si="33">SUBSTITUTE(D15, ".", " ")</f>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U15" s="24" t="str">
-        <f t="shared" ref="U15:U23" si="34">SUBSTITUTE(E15, ".", " ")</f>
-        <v>Atendidas</v>
-      </c>
-      <c r="V15" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W15" s="52" t="str">
-        <f t="shared" si="14"/>
+      <c r="X15" s="52" t="str">
+        <f t="shared" si="11"/>
         <v>Key-REQ-15</v>
       </c>
-      <c r="X15" s="24" t="s">
-        <v>1</v>
-      </c>
       <c r="Y15" s="24" t="s">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="Z15" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA15" s="24" t="str">
-        <f t="shared" ref="AA15:AA18" si="35">_xlfn.TRANSLATE(P15,"pt","en")</f>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="AA15" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB15" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC15" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="53">
         <v>16</v>
       </c>
@@ -3476,557 +3620,581 @@
         <v>74</v>
       </c>
       <c r="C16" s="58" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D16" s="59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E16" s="59" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F16" s="59" t="s">
+        <v>130</v>
+      </c>
+      <c r="G16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L16" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>De.Necessidades</v>
+      </c>
+      <c r="M16" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v>Necessidades.Projetuais</v>
+      </c>
+      <c r="N16" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="O16" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v>Necessidade Mobiliário</v>
+      </c>
+      <c r="P16" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q16" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R16" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S16" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="24" t="str">
+        <f t="shared" si="25"/>
+        <v>De Necessidades</v>
+      </c>
+      <c r="U16" s="24" t="str">
+        <f t="shared" si="26"/>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V16" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="W16" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X16" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-REQ-16</v>
+      </c>
+      <c r="Y16" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z16" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA16" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB16" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC16" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="17" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="53">
+        <v>17</v>
+      </c>
+      <c r="B17" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="D17" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="E17" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="F17" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="G16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L16" s="23" t="str">
+      <c r="G17" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L17" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>De.Necessidades</v>
+      </c>
+      <c r="M17" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v>Necessidades.Projetuais</v>
+      </c>
+      <c r="N17" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="O17" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v>Necessidade Equipamento</v>
+      </c>
+      <c r="P17" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q17" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R17" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S17" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="24" t="str">
+        <f t="shared" si="25"/>
+        <v>De Necessidades</v>
+      </c>
+      <c r="U17" s="24" t="str">
+        <f t="shared" si="26"/>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V17" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="W17" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X17" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-REQ-17</v>
+      </c>
+      <c r="Y17" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z17" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA17" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB17" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC17" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="18" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="53">
+        <v>18</v>
+      </c>
+      <c r="B18" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="E18" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="F18" s="59" t="s">
+        <v>193</v>
+      </c>
+      <c r="G18" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L18" s="23" t="str">
+        <f t="shared" si="21"/>
+        <v>De.Necessidades</v>
+      </c>
+      <c r="M18" s="23" t="str">
+        <f t="shared" si="22"/>
+        <v>Necessidades.Projetuais</v>
+      </c>
+      <c r="N18" s="23" t="str">
+        <f t="shared" si="23"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="O18" s="23" t="str">
+        <f t="shared" si="24"/>
+        <v>Necessidade Avac</v>
+      </c>
+      <c r="P18" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q18" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R18" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S18" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="24" t="str">
+        <f t="shared" si="25"/>
+        <v>De Necessidades</v>
+      </c>
+      <c r="U18" s="24" t="str">
+        <f t="shared" si="26"/>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V18" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="W18" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X18" s="52" t="str">
+        <f t="shared" si="11"/>
+        <v>Key-REQ-18</v>
+      </c>
+      <c r="Y18" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z18" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA18" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB18" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC18" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="53">
+        <v>19</v>
+      </c>
+      <c r="B19" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="E19" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="F19" s="59" t="s">
+        <v>195</v>
+      </c>
+      <c r="G19" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L19" s="23" t="str">
+        <f t="shared" ref="L19:L21" si="28">CONCATENATE("", C19)</f>
+        <v>De.Necessidades</v>
+      </c>
+      <c r="M19" s="23" t="str">
+        <f t="shared" ref="M19:M21" si="29">CONCATENATE("", D19)</f>
+        <v>Necessidades.Projetuais</v>
+      </c>
+      <c r="N19" s="23" t="str">
+        <f t="shared" ref="N19:N21" si="30">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
+        <v>Atendidas</v>
+      </c>
+      <c r="O19" s="23" t="str">
+        <f t="shared" ref="O19:O21" si="31">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F19),"."," ")," De "," de "))</f>
+        <v>Necessidade Hidráulica</v>
+      </c>
+      <c r="P19" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q19" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R19" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S19" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="24" t="str">
+        <f t="shared" ref="T19:T21" si="32">SUBSTITUTE(C19, ".", " ")</f>
+        <v>De Necessidades</v>
+      </c>
+      <c r="U19" s="24" t="str">
+        <f t="shared" ref="U19:U21" si="33">SUBSTITUTE(D19, ".", " ")</f>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V19" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="W19" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X19" s="52" t="str">
+        <f t="shared" ref="X19:X21" si="34">CONCATENATE("Key-REQ-",A19)</f>
+        <v>Key-REQ-19</v>
+      </c>
+      <c r="Y19" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z19" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA19" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB19" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC19" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="20" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="53">
+        <v>20</v>
+      </c>
+      <c r="B20" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="D20" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20" s="59" t="s">
+        <v>196</v>
+      </c>
+      <c r="G20" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L20" s="23" t="str">
         <f t="shared" si="28"/>
         <v>De.Necessidades</v>
       </c>
-      <c r="M16" s="23" t="str">
+      <c r="M20" s="23" t="str">
         <f t="shared" si="29"/>
         <v>Necessidades.Projetuais</v>
       </c>
-      <c r="N16" s="23" t="str">
+      <c r="N20" s="23" t="str">
         <f t="shared" si="30"/>
         <v>Atendidas</v>
       </c>
-      <c r="O16" s="23" t="str">
+      <c r="O20" s="23" t="str">
         <f t="shared" si="31"/>
-        <v>Necessidade Mobiliário</v>
-      </c>
-      <c r="P16" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q16" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R16" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S16" s="24" t="str">
+        <v>Necessidade Elétrica</v>
+      </c>
+      <c r="P20" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q20" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R20" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S20" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="24" t="str">
         <f t="shared" si="32"/>
         <v>De Necessidades</v>
       </c>
-      <c r="T16" s="24" t="str">
+      <c r="U20" s="24" t="str">
         <f t="shared" si="33"/>
         <v>Necessidades Projetuais</v>
       </c>
-      <c r="U16" s="24" t="str">
+      <c r="V20" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="W20" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X20" s="52" t="str">
         <f t="shared" si="34"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V16" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W16" s="52" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-REQ-16</v>
-      </c>
-      <c r="X16" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA16" s="24" t="str">
-        <f t="shared" si="35"/>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="17" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="53">
-        <v>17</v>
-      </c>
-      <c r="B17" s="58" t="s">
+        <v>Key-REQ-20</v>
+      </c>
+      <c r="Y20" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="Z20" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AA20" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB20" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC20" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="53">
+        <v>21</v>
+      </c>
+      <c r="B21" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D17" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="E17" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="F17" s="59" t="s">
-        <v>132</v>
-      </c>
-      <c r="G17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L17" s="23" t="str">
+      <c r="C21" s="58" t="s">
+        <v>173</v>
+      </c>
+      <c r="D21" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="E21" s="59" t="s">
+        <v>177</v>
+      </c>
+      <c r="F21" s="59" t="s">
+        <v>194</v>
+      </c>
+      <c r="G21" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="50" t="s">
+        <v>1</v>
+      </c>
+      <c r="L21" s="23" t="str">
         <f t="shared" si="28"/>
         <v>De.Necessidades</v>
       </c>
-      <c r="M17" s="23" t="str">
+      <c r="M21" s="23" t="str">
         <f t="shared" si="29"/>
         <v>Necessidades.Projetuais</v>
       </c>
-      <c r="N17" s="23" t="str">
+      <c r="N21" s="23" t="str">
         <f t="shared" si="30"/>
         <v>Atendidas</v>
       </c>
-      <c r="O17" s="23" t="str">
+      <c r="O21" s="23" t="str">
         <f t="shared" si="31"/>
-        <v>Necessidade Equipamento</v>
-      </c>
-      <c r="P17" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q17" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R17" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S17" s="24" t="str">
+        <v>Necessidade Incêndio</v>
+      </c>
+      <c r="P21" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q21" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R21" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S21" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T21" s="24" t="str">
         <f t="shared" si="32"/>
         <v>De Necessidades</v>
       </c>
-      <c r="T17" s="24" t="str">
+      <c r="U21" s="24" t="str">
         <f t="shared" si="33"/>
         <v>Necessidades Projetuais</v>
       </c>
-      <c r="U17" s="24" t="str">
+      <c r="V21" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="W21" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X21" s="52" t="str">
         <f t="shared" si="34"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V17" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W17" s="52" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-REQ-17</v>
-      </c>
-      <c r="X17" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA17" s="24" t="str">
-        <f t="shared" si="35"/>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="18" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="53">
-        <v>18</v>
-      </c>
-      <c r="B18" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D18" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="E18" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="F18" s="59" t="s">
-        <v>137</v>
-      </c>
-      <c r="G18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L18" s="23" t="str">
-        <f t="shared" si="28"/>
-        <v>De.Necessidades</v>
-      </c>
-      <c r="M18" s="23" t="str">
-        <f t="shared" si="29"/>
-        <v>Necessidades.Projetuais</v>
-      </c>
-      <c r="N18" s="23" t="str">
-        <f t="shared" si="30"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="O18" s="23" t="str">
-        <f t="shared" si="31"/>
-        <v>Necessidade Sistema Avac</v>
-      </c>
-      <c r="P18" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q18" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R18" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S18" s="24" t="str">
-        <f t="shared" si="32"/>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T18" s="24" t="str">
-        <f t="shared" si="33"/>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U18" s="24" t="str">
-        <f t="shared" si="34"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V18" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W18" s="52" t="str">
-        <f t="shared" si="14"/>
-        <v>Key-REQ-18</v>
-      </c>
-      <c r="X18" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA18" s="24" t="str">
-        <f t="shared" si="35"/>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="19" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="53">
-        <v>19</v>
-      </c>
-      <c r="B19" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D19" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="E19" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="F19" s="59" t="s">
-        <v>138</v>
-      </c>
-      <c r="G19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L19" s="23" t="str">
-        <f t="shared" ref="L19:L21" si="36">CONCATENATE("", C19)</f>
-        <v>De.Necessidades</v>
-      </c>
-      <c r="M19" s="23" t="str">
-        <f t="shared" ref="M19:M21" si="37">CONCATENATE("", D19)</f>
-        <v>Necessidades.Projetuais</v>
-      </c>
-      <c r="N19" s="23" t="str">
-        <f t="shared" ref="N19:N21" si="38">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E19),"."," ")," De "," de "))</f>
-        <v>Atendidas</v>
-      </c>
-      <c r="O19" s="23" t="str">
-        <f t="shared" ref="O19:O21" si="39">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F19),"."," ")," De "," de "))</f>
-        <v>Necessidade Sistema Hidráulico</v>
-      </c>
-      <c r="P19" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q19" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R19" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S19" s="24" t="str">
-        <f t="shared" ref="S19:S21" si="40">SUBSTITUTE(C19, ".", " ")</f>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T19" s="24" t="str">
-        <f t="shared" ref="T19:T21" si="41">SUBSTITUTE(D19, ".", " ")</f>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U19" s="24" t="str">
-        <f t="shared" si="34"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V19" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W19" s="52" t="str">
-        <f t="shared" ref="W19:W21" si="42">CONCATENATE("Key-REQ-",A19)</f>
-        <v>Key-REQ-19</v>
-      </c>
-      <c r="X19" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA19" s="24" t="str">
-        <f t="shared" ref="AA19:AA21" si="43">_xlfn.TRANSLATE(P19,"pt","en")</f>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="20" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="53">
-        <v>20</v>
-      </c>
-      <c r="B20" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D20" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="E20" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="F20" s="59" t="s">
-        <v>139</v>
-      </c>
-      <c r="G20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L20" s="23" t="str">
-        <f t="shared" si="36"/>
-        <v>De.Necessidades</v>
-      </c>
-      <c r="M20" s="23" t="str">
-        <f t="shared" si="37"/>
-        <v>Necessidades.Projetuais</v>
-      </c>
-      <c r="N20" s="23" t="str">
-        <f t="shared" si="38"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="O20" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v>Necessidade Sistema Elétrico</v>
-      </c>
-      <c r="P20" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q20" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R20" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S20" s="24" t="str">
-        <f t="shared" si="40"/>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T20" s="24" t="str">
-        <f t="shared" si="41"/>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U20" s="24" t="str">
-        <f t="shared" si="34"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V20" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W20" s="52" t="str">
-        <f t="shared" si="42"/>
-        <v>Key-REQ-20</v>
-      </c>
-      <c r="X20" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA20" s="24" t="str">
-        <f t="shared" si="43"/>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="21" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="53">
-        <v>21</v>
-      </c>
-      <c r="B21" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="58" t="s">
-        <v>180</v>
-      </c>
-      <c r="D21" s="59" t="s">
-        <v>136</v>
-      </c>
-      <c r="E21" s="59" t="s">
-        <v>190</v>
-      </c>
-      <c r="F21" s="59" t="s">
-        <v>140</v>
-      </c>
-      <c r="G21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="L21" s="23" t="str">
-        <f t="shared" si="36"/>
-        <v>De.Necessidades</v>
-      </c>
-      <c r="M21" s="23" t="str">
-        <f t="shared" si="37"/>
-        <v>Necessidades.Projetuais</v>
-      </c>
-      <c r="N21" s="23" t="str">
-        <f t="shared" si="38"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="O21" s="23" t="str">
-        <f t="shared" si="39"/>
-        <v>Necessidade Sistema Incêndio</v>
-      </c>
-      <c r="P21" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="Q21" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R21" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S21" s="24" t="str">
-        <f t="shared" si="40"/>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T21" s="24" t="str">
-        <f t="shared" si="41"/>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U21" s="24" t="str">
-        <f t="shared" si="34"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V21" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W21" s="52" t="str">
-        <f t="shared" si="42"/>
         <v>Key-REQ-21</v>
       </c>
-      <c r="X21" s="24" t="s">
-        <v>1</v>
-      </c>
       <c r="Y21" s="24" t="s">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="Z21" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA21" s="24" t="str">
-        <f t="shared" si="43"/>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="22" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="AA21" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB21" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC21" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="53">
         <v>22</v>
       </c>
@@ -4034,16 +4202,16 @@
         <v>74</v>
       </c>
       <c r="C22" s="58" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F22" s="59" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="G22" s="50" t="s">
         <v>1</v>
@@ -4061,65 +4229,69 @@
         <v>1</v>
       </c>
       <c r="L22" s="23" t="str">
-        <f t="shared" ref="L22:L23" si="44">CONCATENATE("", C22)</f>
+        <f t="shared" ref="L22:L23" si="35">CONCATENATE("", C22)</f>
         <v>De.Necessidades</v>
       </c>
       <c r="M22" s="23" t="str">
-        <f t="shared" ref="M22:M23" si="45">CONCATENATE("", D22)</f>
+        <f t="shared" ref="M22:M23" si="36">CONCATENATE("", D22)</f>
         <v>Necessidades.Projetuais</v>
       </c>
       <c r="N22" s="23" t="str">
-        <f t="shared" ref="N22:N23" si="46">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E22),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N22:N23" si="37">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E22),"."," ")," De "," de "))</f>
         <v>Atendidas</v>
       </c>
       <c r="O22" s="23" t="str">
-        <f t="shared" ref="O22:O23" si="47">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F22),"."," ")," De "," de "))</f>
-        <v>Necessidade Sistema Sanitário</v>
+        <f t="shared" ref="O22:O23" si="38">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",F22),"."," ")," De "," de "))</f>
+        <v>Necessidade Sanitária</v>
       </c>
       <c r="P22" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q22" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R22" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S22" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T22" s="24" t="str">
+        <f t="shared" ref="T22:T23" si="39">SUBSTITUTE(C22, ".", " ")</f>
+        <v>De Necessidades</v>
+      </c>
+      <c r="U22" s="24" t="str">
+        <f t="shared" ref="U22:U23" si="40">SUBSTITUTE(D22, ".", " ")</f>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V22" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="W22" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="Q22" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R22" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S22" s="24" t="str">
-        <f t="shared" ref="S22:S23" si="48">SUBSTITUTE(C22, ".", " ")</f>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T22" s="24" t="str">
-        <f t="shared" ref="T22:T23" si="49">SUBSTITUTE(D22, ".", " ")</f>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U22" s="24" t="str">
-        <f t="shared" si="34"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V22" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W22" s="52" t="str">
-        <f t="shared" ref="W22:W23" si="50">CONCATENATE("Key-REQ-",A22)</f>
+      <c r="X22" s="52" t="str">
+        <f t="shared" ref="X22:X23" si="41">CONCATENATE("Key-REQ-",A22)</f>
         <v>Key-REQ-22</v>
       </c>
-      <c r="X22" s="24" t="s">
-        <v>1</v>
-      </c>
       <c r="Y22" s="24" t="s">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="Z22" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA22" s="24" t="str">
-        <f t="shared" ref="AA22:AA23" si="51">_xlfn.TRANSLATE(P22,"pt","en")</f>
-        <v>Defines the Project-Specific Requirements Program.</v>
-      </c>
-    </row>
-    <row r="23" spans="1:27" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>215</v>
+      </c>
+      <c r="AA22" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB22" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC22" s="24" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="23" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="53">
         <v>23</v>
       </c>
@@ -4127,16 +4299,16 @@
         <v>74</v>
       </c>
       <c r="C23" s="58" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>190</v>
+        <v>177</v>
       </c>
       <c r="F23" s="59" t="s">
-        <v>142</v>
+        <v>198</v>
       </c>
       <c r="G23" s="50" t="s">
         <v>1</v>
@@ -4154,76 +4326,85 @@
         <v>1</v>
       </c>
       <c r="L23" s="23" t="str">
-        <f t="shared" si="44"/>
+        <f t="shared" si="35"/>
         <v>De.Necessidades</v>
       </c>
       <c r="M23" s="23" t="str">
-        <f t="shared" si="45"/>
+        <f t="shared" si="36"/>
         <v>Necessidades.Projetuais</v>
       </c>
       <c r="N23" s="23" t="str">
-        <f t="shared" si="46"/>
+        <f t="shared" si="37"/>
         <v>Atendidas</v>
       </c>
       <c r="O23" s="23" t="str">
-        <f t="shared" si="47"/>
-        <v>Necessidade Sistema Lógico</v>
+        <f t="shared" si="38"/>
+        <v>Necessidade Lógica</v>
       </c>
       <c r="P23" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="Q23" s="24" t="s">
+        <v>211</v>
+      </c>
+      <c r="R23" s="24" t="s">
+        <v>205</v>
+      </c>
+      <c r="S23" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T23" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>De Necessidades</v>
+      </c>
+      <c r="U23" s="24" t="str">
+        <f t="shared" si="40"/>
+        <v>Necessidades Projetuais</v>
+      </c>
+      <c r="V23" s="24" t="str">
+        <f t="shared" si="27"/>
+        <v>Atendidas</v>
+      </c>
+      <c r="W23" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="Q23" s="24" t="str">
-        <f t="shared" si="12"/>
-        <v>Define el Programa de Requisitos Específicos del Proyecto.</v>
-      </c>
-      <c r="R23" s="24" t="s">
-        <v>1</v>
-      </c>
-      <c r="S23" s="24" t="str">
-        <f t="shared" si="48"/>
-        <v>De Necessidades</v>
-      </c>
-      <c r="T23" s="24" t="str">
-        <f t="shared" si="49"/>
-        <v>Necessidades Projetuais</v>
-      </c>
-      <c r="U23" s="24" t="str">
-        <f t="shared" si="34"/>
-        <v>Atendidas</v>
-      </c>
-      <c r="V23" s="24" t="s">
-        <v>134</v>
-      </c>
-      <c r="W23" s="52" t="str">
-        <f t="shared" si="50"/>
+      <c r="X23" s="52" t="str">
+        <f t="shared" si="41"/>
         <v>Key-REQ-23</v>
       </c>
-      <c r="X23" s="24" t="s">
-        <v>1</v>
-      </c>
       <c r="Y23" s="24" t="s">
-        <v>1</v>
+        <v>215</v>
       </c>
       <c r="Z23" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="AA23" s="24" t="str">
-        <f t="shared" si="51"/>
-        <v>Defines the Project-Specific Requirements Program.</v>
+        <v>215</v>
+      </c>
+      <c r="AA23" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AB23" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="AC23" s="24" t="s">
+        <v>124</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:C1 L1:W1 Y1:Z1 AB1:XFD1 A24:C1048576 L24:W1048576 Y24:XFD1048576">
-    <cfRule type="cellIs" dxfId="11" priority="429" operator="equal">
+  <conditionalFormatting sqref="A1:C1 L1:Q1 A24:C1048576 S1:X1 L24:X1048576 AA1:XFD1 AA24:XFD1048576">
+    <cfRule type="cellIs" dxfId="14" priority="430" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="10" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA1:AA23 A2:B23">
-    <cfRule type="cellIs" dxfId="9" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B23">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R23">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4235,15 +4416,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.3046875" style="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
@@ -4308,7 +4489,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -4376,7 +4557,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="8" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4389,14 +4570,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3828125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18">
         <v>1</v>
       </c>
@@ -4410,7 +4591,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -4424,7 +4605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -4438,7 +4619,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -4452,13 +4633,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" s="29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" s="29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" s="29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -4466,7 +4647,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="7" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4478,88 +4659,89 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BE003-A289-428E-9141-72F001D0AED0}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:U15"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.3" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.140625" style="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9" style="49" customWidth="1"/>
-    <col min="3" max="3" width="13.85546875" style="49" customWidth="1"/>
-    <col min="4" max="4" width="7.28515625" style="49" customWidth="1"/>
-    <col min="5" max="5" width="5.85546875" style="49" customWidth="1"/>
-    <col min="6" max="7" width="3" style="49" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" style="49" customWidth="1"/>
-    <col min="9" max="9" width="10.42578125" style="49" customWidth="1"/>
-    <col min="10" max="10" width="5.7109375" style="49" customWidth="1"/>
-    <col min="11" max="11" width="19.5703125" style="49" customWidth="1"/>
-    <col min="12" max="12" width="7.140625" style="49" customWidth="1"/>
-    <col min="13" max="13" width="39.5703125" style="49" customWidth="1"/>
-    <col min="14" max="14" width="5.7109375" style="49" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="49" customWidth="1"/>
-    <col min="16" max="16" width="5.7109375" style="49" customWidth="1"/>
-    <col min="17" max="17" width="7.42578125" style="63" customWidth="1"/>
-    <col min="18" max="18" width="4.28515625" style="49" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.7109375" style="49" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="4.28515625" style="49" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="3.85546875" style="49" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.28515625" style="49"/>
+    <col min="1" max="1" width="2.15234375" style="49" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.15234375" style="49" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3046875" style="49" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.53515625" style="49" customWidth="1"/>
+    <col min="5" max="5" width="4.765625" style="49" customWidth="1"/>
+    <col min="6" max="6" width="2.61328125" style="49" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4" style="49" customWidth="1"/>
+    <col min="8" max="8" width="7.15234375" style="49" customWidth="1"/>
+    <col min="9" max="9" width="10" style="49" customWidth="1"/>
+    <col min="10" max="10" width="4.07421875" style="49" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.53515625" style="49" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="6.23046875" style="49" customWidth="1"/>
+    <col min="13" max="13" width="36.921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="3.921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.07421875" style="49" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.921875" style="49" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="7.07421875" style="63" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="2.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="2.84375" style="49" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="2.3828125" style="49" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="2.23046875" style="49" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="9.3046875" style="49"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.899999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="16.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>1</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C1" s="39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D1" s="39" t="s">
         <v>33</v>
       </c>
       <c r="E1" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>33</v>
       </c>
       <c r="G1" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H1" s="17" t="s">
         <v>33</v>
       </c>
       <c r="I1" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>33</v>
       </c>
       <c r="K1" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L1" s="17" t="s">
         <v>33</v>
       </c>
       <c r="M1" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N1" s="39" t="s">
         <v>33</v>
       </c>
       <c r="O1" s="38" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="P1" s="39" t="s">
         <v>33</v>
       </c>
       <c r="Q1" s="61" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="R1" s="17" t="s">
         <v>33</v>
       </c>
       <c r="S1" s="44" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="T1" s="17" t="s">
         <v>33</v>
@@ -4568,15 +4750,15 @@
         <v>73</v>
       </c>
     </row>
-    <row r="2" spans="1:21" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="31">
         <v>2</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>152</v>
+        <v>134</v>
       </c>
       <c r="C2" s="26" t="s">
-        <v>181</v>
+        <v>74</v>
       </c>
       <c r="D2" s="48" t="s">
         <v>1</v>
@@ -4591,34 +4773,34 @@
         <v>1</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>156</v>
+        <v>1</v>
       </c>
       <c r="I2" s="25" t="s">
-        <v>157</v>
+        <v>1</v>
       </c>
       <c r="J2" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K2" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="L2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="25" t="s">
-        <v>1</v>
+        <v>163</v>
+      </c>
+      <c r="L2" s="27" t="s">
+        <v>136</v>
+      </c>
+      <c r="M2" s="34" t="s">
+        <v>137</v>
+      </c>
+      <c r="N2" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="O2" s="32" t="s">
+        <v>139</v>
       </c>
       <c r="P2" s="27" t="s">
-        <v>1</v>
+        <v>182</v>
       </c>
       <c r="Q2" s="62" t="s">
-        <v>1</v>
+        <v>183</v>
       </c>
       <c r="R2" s="27" t="s">
         <v>1</v>
@@ -4633,21 +4815,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:21" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="31">
         <v>3</v>
       </c>
       <c r="B3" s="33" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="C3" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D3" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="D3" s="48" t="s">
-        <v>1</v>
-      </c>
       <c r="E3" s="43" t="s">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="F3" s="48" t="s">
         <v>1</v>
@@ -4656,16 +4838,16 @@
         <v>1</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J3" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="L3" s="37" t="s">
         <v>1</v>
@@ -4698,21 +4880,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:21" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="31">
         <v>4</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="C4" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D4" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="D4" s="48" t="s">
-        <v>1</v>
-      </c>
       <c r="E4" s="43" t="s">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="F4" s="48" t="s">
         <v>1</v>
@@ -4721,16 +4903,16 @@
         <v>1</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J4" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="L4" s="37" t="s">
         <v>1</v>
@@ -4763,21 +4945,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:21" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="31">
         <v>5</v>
       </c>
       <c r="B5" s="33" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="C5" s="26" t="s">
+        <v>174</v>
+      </c>
+      <c r="D5" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="D5" s="48" t="s">
-        <v>1</v>
-      </c>
       <c r="E5" s="43" t="s">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="F5" s="48" t="s">
         <v>1</v>
@@ -4786,16 +4968,16 @@
         <v>1</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="J5" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="L5" s="37" t="s">
         <v>1</v>
@@ -4828,21 +5010,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:21" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="31">
         <v>6</v>
       </c>
       <c r="B6" s="33" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="D6" s="48" t="s">
-        <v>1</v>
+        <v>181</v>
       </c>
       <c r="E6" s="43" t="s">
-        <v>1</v>
+        <v>134</v>
       </c>
       <c r="F6" s="48" t="s">
         <v>1</v>
@@ -4851,34 +5033,34 @@
         <v>1</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>1</v>
+        <v>149</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>1</v>
+        <v>150</v>
       </c>
       <c r="J6" s="37" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>170</v>
-      </c>
-      <c r="L6" s="27" t="s">
-        <v>143</v>
-      </c>
-      <c r="M6" s="34" t="s">
-        <v>144</v>
-      </c>
-      <c r="N6" s="27" t="s">
-        <v>145</v>
-      </c>
-      <c r="O6" s="32" t="s">
-        <v>146</v>
+        <v>162</v>
+      </c>
+      <c r="L6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="M6" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N6" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="O6" s="25" t="s">
+        <v>1</v>
       </c>
       <c r="P6" s="27" t="s">
-        <v>195</v>
+        <v>1</v>
       </c>
       <c r="Q6" s="62" t="s">
-        <v>196</v>
+        <v>1</v>
       </c>
       <c r="R6" s="27" t="s">
         <v>1</v>
@@ -4893,39 +5075,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="31">
         <v>7</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="C7" s="59" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D7" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F7" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G7" s="43" t="s">
-        <v>1</v>
+        <v>199</v>
+      </c>
+      <c r="G7" s="64" t="s">
+        <v>145</v>
       </c>
       <c r="H7" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="J7" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="L7" s="37" t="s">
         <v>1</v>
@@ -4958,39 +5140,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="31">
         <v>8</v>
       </c>
       <c r="B8" s="33" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="C8" s="59" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D8" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F8" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G8" s="43" t="s">
-        <v>1</v>
+        <v>199</v>
+      </c>
+      <c r="G8" s="64" t="s">
+        <v>146</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="J8" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="L8" s="37" t="s">
         <v>1</v>
@@ -5023,39 +5205,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="31">
         <v>9</v>
       </c>
       <c r="B9" s="33" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="C9" s="59" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
       <c r="D9" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E9" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F9" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G9" s="43" t="s">
-        <v>1</v>
+        <v>199</v>
+      </c>
+      <c r="G9" s="64" t="s">
+        <v>147</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="J9" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="L9" s="37" t="s">
         <v>1</v>
@@ -5088,39 +5270,39 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="31">
         <v>10</v>
       </c>
       <c r="B10" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" s="59" t="s">
         <v>178</v>
       </c>
-      <c r="C10" s="59" t="s">
-        <v>191</v>
-      </c>
       <c r="D10" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E10" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F10" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G10" s="43" t="s">
-        <v>1</v>
+        <v>199</v>
+      </c>
+      <c r="G10" s="64" t="s">
+        <v>148</v>
       </c>
       <c r="H10" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>198</v>
+        <v>185</v>
       </c>
       <c r="J10" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="L10" s="37" t="s">
         <v>1</v>
@@ -5153,21 +5335,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="31">
         <v>11</v>
       </c>
       <c r="B11" s="33" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>137</v>
+        <v>193</v>
       </c>
       <c r="D11" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E11" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F11" s="48" t="s">
         <v>1</v>
@@ -5176,16 +5358,16 @@
         <v>1</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J11" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K11" s="25" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="L11" s="37" t="s">
         <v>1</v>
@@ -5218,21 +5400,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="31">
         <v>12</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>138</v>
+        <v>195</v>
       </c>
       <c r="D12" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E12" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F12" s="48" t="s">
         <v>1</v>
@@ -5241,16 +5423,16 @@
         <v>1</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J12" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="L12" s="37" t="s">
         <v>1</v>
@@ -5283,21 +5465,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="31">
         <v>13</v>
       </c>
       <c r="B13" s="33" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="D13" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F13" s="48" t="s">
         <v>1</v>
@@ -5306,16 +5488,16 @@
         <v>1</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J13" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="L13" s="37" t="s">
         <v>1</v>
@@ -5348,21 +5530,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="31">
         <v>14</v>
       </c>
       <c r="B14" s="33" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>140</v>
+        <v>194</v>
       </c>
       <c r="D14" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E14" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F14" s="48" t="s">
         <v>1</v>
@@ -5371,16 +5553,16 @@
         <v>1</v>
       </c>
       <c r="H14" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J14" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K14" s="25" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="L14" s="37" t="s">
         <v>1</v>
@@ -5413,21 +5595,21 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="31">
         <v>15</v>
       </c>
       <c r="B15" s="33" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>141</v>
+        <v>197</v>
       </c>
       <c r="D15" s="48" t="s">
-        <v>194</v>
+        <v>181</v>
       </c>
       <c r="E15" s="43" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F15" s="48" t="s">
         <v>1</v>
@@ -5436,16 +5618,16 @@
         <v>1</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>199</v>
+        <v>186</v>
       </c>
       <c r="J15" s="27" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="L15" s="37" t="s">
         <v>1</v>
@@ -5483,28 +5665,32 @@
     <sortCondition ref="A1:A13"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:B15 F2:G14 D1:U1 H2:U15">
-    <cfRule type="cellIs" dxfId="6" priority="16" operator="equal">
+  <conditionalFormatting sqref="B2:B6">
+    <cfRule type="duplicateValues" dxfId="8" priority="1969"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="1970"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B7:B15 B1">
+    <cfRule type="duplicateValues" dxfId="6" priority="1965"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1966"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:E15 F15:H15">
+    <cfRule type="cellIs" dxfId="4" priority="41" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B1 B7:B15">
-    <cfRule type="duplicateValues" dxfId="5" priority="1963"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="1964"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B2:B6">
-    <cfRule type="duplicateValues" dxfId="3" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="29"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D6">
-    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
+  <conditionalFormatting sqref="D1:U1 F2:U2">
+    <cfRule type="cellIs" dxfId="3" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D7:E15 F15:H15">
-    <cfRule type="cellIs" dxfId="0" priority="39" operator="equal">
+  <conditionalFormatting sqref="F3:G14 A1:B15 D2 H3:U15">
+    <cfRule type="cellIs" dxfId="2" priority="21" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G7:G10">
+    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/PRO/Ontologia_Requisitos.xlsx
+++ b/Versão5/PRO/Ontologia_Requisitos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA7C9B6-780D-47E1-9329-50D7A4D9652F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86934C0F-1BB5-4CDF-9DB2-47E59DD38D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="933" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="245">
   <si>
     <t>Key</t>
   </si>
@@ -718,14 +718,101 @@
     <t>Classe IFC</t>
   </si>
   <si>
-    <t>[ - ]</t>
+    <t>De.API</t>
+  </si>
+  <si>
+    <t>Métodos</t>
+  </si>
+  <si>
+    <t>Macros</t>
+  </si>
+  <si>
+    <t>API.Revit</t>
+  </si>
+  <si>
+    <t>Aplicação Revit</t>
+  </si>
+  <si>
+    <t>Aplicativo Revit</t>
+  </si>
+  <si>
+    <t>Revit Aplication</t>
+  </si>
+  <si>
+    <t>API_Ambiente</t>
+  </si>
+  <si>
+    <t>tema</t>
+  </si>
+  <si>
+    <t>"API"</t>
+  </si>
+  <si>
+    <t>subtema</t>
+  </si>
+  <si>
+    <t>"Elementos Ambientes"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar ambientes do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Ambientes ]"</t>
+  </si>
+  <si>
+    <t>API_Andar</t>
+  </si>
+  <si>
+    <t>"Elementos Andares"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar andares do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Pavimentos ]"</t>
+  </si>
+  <si>
+    <t>API_Instância</t>
+  </si>
+  <si>
+    <t>"Elementos Instanciados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar instâncias do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Elementos ]"</t>
+  </si>
+  <si>
+    <t>API_Simbolo</t>
+  </si>
+  <si>
+    <t>"Elementos Tipificados"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar elementos tipificados do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Tipos ]"</t>
+  </si>
+  <si>
+    <t>API_Material</t>
+  </si>
+  <si>
+    <t>"Elementos Materiais"</t>
+  </si>
+  <si>
+    <t>"Individuo indicador de método API para selecionar materiais do projeto"</t>
+  </si>
+  <si>
+    <t>"[ Materiais ]"</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,8 +933,14 @@
       <name val="Arial Nova Cond Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="Arial Nova Cond"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -980,6 +1073,42 @@
         <bgColor rgb="FFD9F2D0"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE79D"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF99FF"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FFFEF2CB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1033,7 +1162,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1107,9 +1236,6 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1207,24 +1333,193 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
+  <dxfs count="32">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1335,11 +1630,13 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
+        <color rgb="FF9C0006"/>
       </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1355,6 +1652,14 @@
       <font>
         <b val="0"/>
         <i/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
@@ -1676,15 +1981,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="68.84375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="47" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="6"/>
+    <col min="2" max="2" width="68.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
@@ -1695,40 +2000,40 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
       <c r="B2" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="46" t="s">
+      <c r="C2" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
       <c r="B3" s="9" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
       <c r="B4" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="46" t="s">
+      <c r="C4" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -1736,11 +2041,11 @@
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="46" t="s">
+      <c r="C5" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -1748,210 +2053,210 @@
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="46" t="s">
+      <c r="C6" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="C7" s="46" t="s">
+      <c r="C7" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="46" t="s">
+      <c r="C8" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
       <c r="B9" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="46" t="s">
+      <c r="C10" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="46" t="s">
+      <c r="C11" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="46" t="s">
+      <c r="C12" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="46" t="s">
+      <c r="C13" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="46" t="s">
+      <c r="C14" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="46" t="s">
+      <c r="C16" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="46" t="s">
+      <c r="C17" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="B18" s="41">
+      <c r="B18" s="40">
         <f ca="1">NOW()</f>
-        <v>46253.78771365741</v>
-      </c>
-      <c r="C18" s="46" t="s">
+        <v>46259.689952546294</v>
+      </c>
+      <c r="C18" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>99</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="46" t="s">
+      <c r="C19" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>98</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="46" t="s">
+      <c r="C20" s="45" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>100</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="46" t="s">
+      <c r="C21" s="45" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>56</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="46" t="s">
+      <c r="C22" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="46" t="s">
+      <c r="C23" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="C24" s="46" t="s">
+      <c r="C24" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
@@ -1959,11 +2264,11 @@
         <f>_xlfn.TRANSLATE(B24,"pt","es")</f>
         <v>Formalizar los conceptos de los elementos de Requisitos del Proyecto.</v>
       </c>
-      <c r="C25" s="46" t="s">
+      <c r="C25" s="45" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>92</v>
       </c>
@@ -1971,150 +2276,150 @@
         <f>_xlfn.TRANSLATE(B25,"pt","en")</f>
         <v>Formalizar los conceptos de los elementos de Requisitos del Proyecto.</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="45" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="B27" s="54" t="s">
+      <c r="B27" s="53" t="s">
         <v>106</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="55" t="s">
+      <c r="B28" s="54" t="s">
         <v>108</v>
       </c>
-      <c r="C28" s="46" t="s">
+      <c r="C28" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="55" t="s">
+      <c r="B29" s="54" t="s">
         <v>110</v>
       </c>
-      <c r="C29" s="46" t="s">
+      <c r="C29" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="B30" s="40" t="s">
+      <c r="B30" s="39" t="s">
         <v>85</v>
       </c>
-      <c r="C30" s="46" t="s">
+      <c r="C30" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="B31" s="40" t="s">
+      <c r="B31" s="39" t="s">
         <v>84</v>
       </c>
-      <c r="C31" s="46" t="s">
+      <c r="C31" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="B32" s="40" t="s">
+      <c r="B32" s="39" t="s">
         <v>87</v>
       </c>
-      <c r="C32" s="46" t="s">
+      <c r="C32" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="B33" s="42" t="s">
+      <c r="B33" s="41" t="s">
         <v>83</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B34" s="42" t="s">
+      <c r="B34" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="46" t="s">
+      <c r="C34" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="B35" s="40" t="s">
+      <c r="B35" s="39" t="s">
         <v>86</v>
       </c>
-      <c r="C35" s="46" t="s">
+      <c r="C35" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="B36" s="42" t="s">
+      <c r="B36" s="41" t="s">
         <v>81</v>
       </c>
-      <c r="C36" s="46" t="s">
+      <c r="C36" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B37" s="40" t="s">
+      <c r="B37" s="39" t="s">
         <v>89</v>
       </c>
-      <c r="C37" s="46" t="s">
+      <c r="C37" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="B38" s="56" t="s">
+      <c r="B38" s="55" t="s">
         <v>120</v>
       </c>
-      <c r="C38" s="46" t="s">
+      <c r="C38" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="B39" s="57" t="s">
+      <c r="B39" s="56" t="s">
         <v>122</v>
       </c>
-      <c r="C39" s="46" t="s">
+      <c r="C39" s="45" t="s">
         <v>96</v>
       </c>
     </row>
@@ -2134,38 +2439,38 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC23"/>
-  <sheetFormatPr defaultColWidth="32.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AC24"/>
+  <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.4609375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.23046875" style="28" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" style="28" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.765625" style="28" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.15234375" style="28" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.4609375" style="28" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.4609375" style="28" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" style="28" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.765625" style="28" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.3046875" style="28" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.53515625" style="28" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.61328125" style="28" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="54.15234375" style="28" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="49.69140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.07421875" style="28" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.765625" style="28" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.3046875" style="28" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6.07421875" style="28" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="5.23046875" style="28" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="6.15234375" style="28" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="6.765625" style="28" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.3828125" style="28" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.07421875" style="28" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.69140625" style="28" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="32.15234375" style="28"/>
+    <col min="1" max="1" width="1.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="54.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="49.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.140625" style="27" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" style="27" customWidth="1"/>
+    <col min="25" max="25" width="6.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.140625" style="27" customWidth="1"/>
+    <col min="27" max="27" width="5.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="27" customWidth="1"/>
+    <col min="29" max="29" width="20.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="32.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="40.299999999999997" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:29" ht="40.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -2184,19 +2489,19 @@
       <c r="F1" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="G1" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="H1" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="I1" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="J1" s="30" t="s">
+      <c r="J1" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="K1" s="30" t="s">
+      <c r="K1" s="29" t="s">
         <v>28</v>
       </c>
       <c r="L1" s="15" t="s">
@@ -2217,7 +2522,7 @@
       <c r="Q1" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="R1" s="45" t="s">
+      <c r="R1" s="44" t="s">
         <v>91</v>
       </c>
       <c r="S1" s="15" t="s">
@@ -2235,7 +2540,7 @@
       <c r="W1" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="X1" s="51" t="s">
+      <c r="X1" s="50" t="s">
         <v>0</v>
       </c>
       <c r="Y1" s="16" t="s">
@@ -2254,38 +2559,38 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="53">
+    <row r="2" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="52">
         <v>2</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="58" t="s">
+      <c r="C2" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="59" t="s">
+      <c r="D2" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="59" t="s">
+      <c r="E2" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F2" s="59" t="s">
+      <c r="F2" s="58" t="s">
         <v>174</v>
       </c>
-      <c r="G2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="50" t="s">
+      <c r="G2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="23" t="str">
@@ -2331,58 +2636,58 @@
       <c r="W2" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X2" s="52" t="str">
+      <c r="X2" s="51" t="str">
         <f t="shared" ref="X2:X3" si="7">CONCATENATE("Key-REQ-",A2)</f>
         <v>Key-REQ-2</v>
       </c>
-      <c r="Y2" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z2" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA2" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB2" s="24" t="s">
-        <v>215</v>
+      <c r="Y2" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC2" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="53">
+    <row r="3" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="52">
         <v>3</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="58" t="s">
+      <c r="C3" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D3" s="59" t="s">
+      <c r="D3" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="59" t="s">
+      <c r="E3" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="58" t="s">
         <v>180</v>
       </c>
-      <c r="G3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="50" t="s">
+      <c r="G3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="23" t="str">
@@ -2428,58 +2733,58 @@
       <c r="W3" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X3" s="52" t="str">
+      <c r="X3" s="51" t="str">
         <f t="shared" si="7"/>
         <v>Key-REQ-3</v>
       </c>
-      <c r="Y3" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z3" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA3" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB3" s="24" t="s">
-        <v>215</v>
+      <c r="Y3" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC3" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="53">
+    <row r="4" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="52">
         <v>4</v>
       </c>
-      <c r="B4" s="58" t="s">
+      <c r="B4" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="58" t="s">
+      <c r="C4" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="59" t="s">
+      <c r="D4" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="59" t="s">
+      <c r="E4" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F4" s="59" t="s">
+      <c r="F4" s="58" t="s">
         <v>151</v>
       </c>
-      <c r="G4" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="50" t="s">
+      <c r="G4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L4" s="23" t="str">
@@ -2525,58 +2830,58 @@
       <c r="W4" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X4" s="52" t="str">
+      <c r="X4" s="51" t="str">
         <f t="shared" ref="X4:X18" si="11">CONCATENATE("Key-REQ-",A4)</f>
         <v>Key-REQ-4</v>
       </c>
-      <c r="Y4" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z4" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA4" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB4" s="24" t="s">
-        <v>215</v>
+      <c r="Y4" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC4" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="53">
+    <row r="5" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="52">
         <v>5</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="B5" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="C5" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="59" t="s">
+      <c r="D5" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="59" t="s">
+      <c r="E5" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F5" s="59" t="s">
+      <c r="F5" s="58" t="s">
         <v>152</v>
       </c>
-      <c r="G5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="50" t="s">
+      <c r="G5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L5" s="23" t="str">
@@ -2622,58 +2927,58 @@
       <c r="W5" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X5" s="52" t="str">
+      <c r="X5" s="51" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-5</v>
       </c>
-      <c r="Y5" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z5" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA5" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB5" s="24" t="s">
-        <v>215</v>
+      <c r="Y5" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC5" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="53">
+    <row r="6" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="52">
         <v>6</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="B6" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="C6" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="59" t="s">
+      <c r="D6" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="59" t="s">
+      <c r="E6" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F6" s="59" t="s">
+      <c r="F6" s="58" t="s">
         <v>153</v>
       </c>
-      <c r="G6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="50" t="s">
+      <c r="G6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L6" s="23" t="str">
@@ -2719,58 +3024,58 @@
       <c r="W6" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X6" s="52" t="str">
+      <c r="X6" s="51" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-6</v>
       </c>
-      <c r="Y6" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z6" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA6" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB6" s="24" t="s">
-        <v>215</v>
+      <c r="Y6" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC6" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="53">
+    <row r="7" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="52">
         <v>7</v>
       </c>
-      <c r="B7" s="58" t="s">
+      <c r="B7" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="58" t="s">
+      <c r="C7" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="59" t="s">
+      <c r="D7" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="59" t="s">
+      <c r="E7" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F7" s="59" t="s">
+      <c r="F7" s="58" t="s">
         <v>187</v>
       </c>
-      <c r="G7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="50" t="s">
+      <c r="G7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L7" s="23" t="str">
@@ -2816,58 +3121,58 @@
       <c r="W7" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X7" s="52" t="str">
+      <c r="X7" s="51" t="str">
         <f t="shared" ref="X7:X11" si="19">CONCATENATE("Key-REQ-",A7)</f>
         <v>Key-REQ-7</v>
       </c>
-      <c r="Y7" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z7" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA7" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB7" s="24" t="s">
-        <v>215</v>
+      <c r="Y7" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC7" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="53">
+    <row r="8" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="52">
         <v>8</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B8" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="58" t="s">
+      <c r="C8" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="59" t="s">
+      <c r="D8" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="59" t="s">
+      <c r="E8" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F8" s="59" t="s">
+      <c r="F8" s="58" t="s">
         <v>188</v>
       </c>
-      <c r="G8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="50" t="s">
+      <c r="G8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="23" t="str">
@@ -2913,58 +3218,58 @@
       <c r="W8" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X8" s="52" t="str">
+      <c r="X8" s="51" t="str">
         <f t="shared" si="19"/>
         <v>Key-REQ-8</v>
       </c>
-      <c r="Y8" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z8" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA8" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB8" s="24" t="s">
-        <v>215</v>
+      <c r="Y8" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC8" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="53">
+    <row r="9" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="52">
         <v>9</v>
       </c>
-      <c r="B9" s="58" t="s">
+      <c r="B9" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="58" t="s">
+      <c r="C9" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="59" t="s">
+      <c r="D9" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="59" t="s">
+      <c r="E9" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F9" s="59" t="s">
+      <c r="F9" s="58" t="s">
         <v>189</v>
       </c>
-      <c r="G9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="50" t="s">
+      <c r="G9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L9" s="23" t="str">
@@ -3010,58 +3315,58 @@
       <c r="W9" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X9" s="52" t="str">
+      <c r="X9" s="51" t="str">
         <f t="shared" si="19"/>
         <v>Key-REQ-9</v>
       </c>
-      <c r="Y9" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z9" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA9" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB9" s="24" t="s">
-        <v>215</v>
+      <c r="Y9" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC9" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="53">
+    <row r="10" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="52">
         <v>10</v>
       </c>
-      <c r="B10" s="58" t="s">
+      <c r="B10" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="58" t="s">
+      <c r="C10" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="59" t="s">
+      <c r="D10" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="59" t="s">
+      <c r="E10" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F10" s="59" t="s">
+      <c r="F10" s="58" t="s">
         <v>190</v>
       </c>
-      <c r="G10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="50" t="s">
+      <c r="G10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L10" s="23" t="str">
@@ -3107,58 +3412,58 @@
       <c r="W10" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X10" s="52" t="str">
+      <c r="X10" s="51" t="str">
         <f t="shared" si="19"/>
         <v>Key-REQ-10</v>
       </c>
-      <c r="Y10" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z10" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA10" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB10" s="24" t="s">
-        <v>215</v>
+      <c r="Y10" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC10" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="53">
+    <row r="11" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="52">
         <v>11</v>
       </c>
-      <c r="B11" s="58" t="s">
+      <c r="B11" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="58" t="s">
+      <c r="C11" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="59" t="s">
+      <c r="D11" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="59" t="s">
+      <c r="E11" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="59" t="s">
+      <c r="F11" s="58" t="s">
         <v>191</v>
       </c>
-      <c r="G11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="50" t="s">
+      <c r="G11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L11" s="23" t="str">
@@ -3204,58 +3509,58 @@
       <c r="W11" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X11" s="52" t="str">
+      <c r="X11" s="51" t="str">
         <f t="shared" si="19"/>
         <v>Key-REQ-11</v>
       </c>
-      <c r="Y11" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z11" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA11" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB11" s="24" t="s">
-        <v>215</v>
+      <c r="Y11" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC11" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="53">
+    <row r="12" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="52">
         <v>12</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="57" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="C12" s="57" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="D12" s="58" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="59" t="s">
+      <c r="E12" s="58" t="s">
         <v>176</v>
       </c>
-      <c r="F12" s="59" t="s">
+      <c r="F12" s="58" t="s">
         <v>192</v>
       </c>
-      <c r="G12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="50" t="s">
+      <c r="G12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L12" s="23" t="str">
@@ -3301,58 +3606,58 @@
       <c r="W12" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X12" s="52" t="str">
+      <c r="X12" s="51" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-12</v>
       </c>
-      <c r="Y12" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z12" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA12" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB12" s="24" t="s">
-        <v>215</v>
+      <c r="Y12" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC12" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="53">
+    <row r="13" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="52">
         <v>13</v>
       </c>
-      <c r="B13" s="58" t="s">
+      <c r="B13" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="58" t="s">
+      <c r="C13" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D13" s="59" t="s">
+      <c r="D13" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="59" t="s">
+      <c r="E13" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F13" s="59" t="s">
+      <c r="F13" s="58" t="s">
         <v>178</v>
       </c>
-      <c r="G13" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="50" t="s">
+      <c r="G13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L13" s="23" t="str">
@@ -3398,58 +3703,58 @@
       <c r="W13" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X13" s="52" t="str">
+      <c r="X13" s="51" t="str">
         <f t="shared" ref="X13:X14" si="20">CONCATENATE("Key-REQ-",A13)</f>
         <v>Key-REQ-13</v>
       </c>
-      <c r="Y13" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z13" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA13" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB13" s="24" t="s">
-        <v>215</v>
+      <c r="Y13" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC13" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="53">
+    <row r="14" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="52">
         <v>14</v>
       </c>
-      <c r="B14" s="58" t="s">
+      <c r="B14" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="58" t="s">
+      <c r="C14" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D14" s="59" t="s">
+      <c r="D14" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="E14" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F14" s="59" t="s">
+      <c r="F14" s="58" t="s">
         <v>179</v>
       </c>
-      <c r="G14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="50" t="s">
+      <c r="G14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L14" s="23" t="str">
@@ -3495,58 +3800,58 @@
       <c r="W14" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X14" s="52" t="str">
+      <c r="X14" s="51" t="str">
         <f t="shared" si="20"/>
         <v>Key-REQ-14</v>
       </c>
-      <c r="Y14" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z14" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA14" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB14" s="24" t="s">
-        <v>215</v>
+      <c r="Y14" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC14" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="53">
+    <row r="15" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="52">
         <v>15</v>
       </c>
-      <c r="B15" s="58" t="s">
+      <c r="B15" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="58" t="s">
+      <c r="C15" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D15" s="59" t="s">
+      <c r="D15" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="59" t="s">
+      <c r="E15" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F15" s="59" t="s">
+      <c r="F15" s="58" t="s">
         <v>129</v>
       </c>
-      <c r="G15" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="50" t="s">
+      <c r="G15" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L15" s="23" t="str">
@@ -3592,58 +3897,58 @@
       <c r="W15" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X15" s="52" t="str">
+      <c r="X15" s="51" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-15</v>
       </c>
-      <c r="Y15" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z15" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA15" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB15" s="24" t="s">
-        <v>215</v>
+      <c r="Y15" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC15" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="53">
+    <row r="16" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="52">
         <v>16</v>
       </c>
-      <c r="B16" s="58" t="s">
+      <c r="B16" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D16" s="59" t="s">
+      <c r="D16" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E16" s="59" t="s">
+      <c r="E16" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F16" s="59" t="s">
+      <c r="F16" s="58" t="s">
         <v>130</v>
       </c>
-      <c r="G16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="50" t="s">
+      <c r="G16" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L16" s="23" t="str">
@@ -3689,58 +3994,58 @@
       <c r="W16" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X16" s="52" t="str">
+      <c r="X16" s="51" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-16</v>
       </c>
-      <c r="Y16" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z16" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA16" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB16" s="24" t="s">
-        <v>215</v>
+      <c r="Y16" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC16" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="53">
+    <row r="17" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="52">
         <v>17</v>
       </c>
-      <c r="B17" s="58" t="s">
+      <c r="B17" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="58" t="s">
+      <c r="C17" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D17" s="59" t="s">
+      <c r="D17" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="59" t="s">
+      <c r="E17" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F17" s="59" t="s">
+      <c r="F17" s="58" t="s">
         <v>131</v>
       </c>
-      <c r="G17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="50" t="s">
+      <c r="G17" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L17" s="23" t="str">
@@ -3786,58 +4091,58 @@
       <c r="W17" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X17" s="52" t="str">
+      <c r="X17" s="51" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-17</v>
       </c>
-      <c r="Y17" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z17" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA17" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB17" s="24" t="s">
-        <v>215</v>
+      <c r="Y17" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC17" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="53">
+    <row r="18" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="52">
         <v>18</v>
       </c>
-      <c r="B18" s="58" t="s">
+      <c r="B18" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="58" t="s">
+      <c r="C18" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="59" t="s">
+      <c r="D18" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E18" s="59" t="s">
+      <c r="E18" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="59" t="s">
+      <c r="F18" s="58" t="s">
         <v>193</v>
       </c>
-      <c r="G18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="50" t="s">
+      <c r="G18" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L18" s="23" t="str">
@@ -3883,58 +4188,58 @@
       <c r="W18" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X18" s="52" t="str">
+      <c r="X18" s="51" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-18</v>
       </c>
-      <c r="Y18" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z18" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA18" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB18" s="24" t="s">
-        <v>215</v>
+      <c r="Y18" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC18" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="53">
+    <row r="19" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="52">
         <v>19</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="58" t="s">
+      <c r="C19" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D19" s="59" t="s">
+      <c r="D19" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E19" s="59" t="s">
+      <c r="E19" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F19" s="59" t="s">
+      <c r="F19" s="58" t="s">
         <v>195</v>
       </c>
-      <c r="G19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="50" t="s">
+      <c r="G19" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L19" s="23" t="str">
@@ -3980,58 +4285,58 @@
       <c r="W19" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X19" s="52" t="str">
-        <f t="shared" ref="X19:X21" si="34">CONCATENATE("Key-REQ-",A19)</f>
+      <c r="X19" s="51" t="str">
+        <f t="shared" ref="X19:X24" si="34">CONCATENATE("Key-REQ-",A19)</f>
         <v>Key-REQ-19</v>
       </c>
-      <c r="Y19" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z19" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA19" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB19" s="24" t="s">
-        <v>215</v>
+      <c r="Y19" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC19" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="53">
+    <row r="20" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="52">
         <v>20</v>
       </c>
-      <c r="B20" s="58" t="s">
+      <c r="B20" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="58" t="s">
+      <c r="C20" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D20" s="59" t="s">
+      <c r="D20" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="59" t="s">
+      <c r="E20" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F20" s="59" t="s">
+      <c r="F20" s="58" t="s">
         <v>196</v>
       </c>
-      <c r="G20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="50" t="s">
+      <c r="G20" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L20" s="23" t="str">
@@ -4077,58 +4382,58 @@
       <c r="W20" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X20" s="52" t="str">
+      <c r="X20" s="51" t="str">
         <f t="shared" si="34"/>
         <v>Key-REQ-20</v>
       </c>
-      <c r="Y20" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z20" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA20" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB20" s="24" t="s">
-        <v>215</v>
+      <c r="Y20" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC20" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="53">
+    <row r="21" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="52">
         <v>21</v>
       </c>
-      <c r="B21" s="58" t="s">
+      <c r="B21" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D21" s="59" t="s">
+      <c r="D21" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E21" s="59" t="s">
+      <c r="E21" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F21" s="59" t="s">
+      <c r="F21" s="58" t="s">
         <v>194</v>
       </c>
-      <c r="G21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="50" t="s">
+      <c r="G21" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L21" s="23" t="str">
@@ -4174,58 +4479,58 @@
       <c r="W21" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X21" s="52" t="str">
+      <c r="X21" s="51" t="str">
         <f t="shared" si="34"/>
         <v>Key-REQ-21</v>
       </c>
-      <c r="Y21" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z21" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA21" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB21" s="24" t="s">
-        <v>215</v>
+      <c r="Y21" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC21" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="53">
+    <row r="22" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="52">
         <v>22</v>
       </c>
-      <c r="B22" s="58" t="s">
+      <c r="B22" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="58" t="s">
+      <c r="C22" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D22" s="59" t="s">
+      <c r="D22" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="59" t="s">
+      <c r="E22" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F22" s="59" t="s">
+      <c r="F22" s="58" t="s">
         <v>197</v>
       </c>
-      <c r="G22" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="50" t="s">
+      <c r="G22" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L22" s="23" t="str">
@@ -4257,7 +4562,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="24" t="str">
-        <f t="shared" ref="T22:T23" si="39">SUBSTITUTE(C22, ".", " ")</f>
+        <f t="shared" ref="T22:V24" si="39">SUBSTITUTE(C22, ".", " ")</f>
         <v>De Necessidades</v>
       </c>
       <c r="U22" s="24" t="str">
@@ -4271,58 +4576,58 @@
       <c r="W22" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X22" s="52" t="str">
-        <f t="shared" ref="X22:X23" si="41">CONCATENATE("Key-REQ-",A22)</f>
+      <c r="X22" s="51" t="str">
+        <f t="shared" si="34"/>
         <v>Key-REQ-22</v>
       </c>
-      <c r="Y22" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z22" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA22" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB22" s="24" t="s">
-        <v>215</v>
+      <c r="Y22" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC22" s="24" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="60" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="53">
+    <row r="23" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="52">
         <v>23</v>
       </c>
-      <c r="B23" s="58" t="s">
+      <c r="B23" s="57" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="57" t="s">
         <v>173</v>
       </c>
-      <c r="D23" s="59" t="s">
+      <c r="D23" s="58" t="s">
         <v>135</v>
       </c>
-      <c r="E23" s="59" t="s">
+      <c r="E23" s="58" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="59" t="s">
+      <c r="F23" s="58" t="s">
         <v>198</v>
       </c>
-      <c r="G23" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="50" t="s">
+      <c r="G23" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="49" t="s">
         <v>1</v>
       </c>
       <c r="L23" s="23" t="str">
@@ -4368,43 +4673,143 @@
       <c r="W23" s="24" t="s">
         <v>133</v>
       </c>
-      <c r="X23" s="52" t="str">
-        <f t="shared" si="41"/>
+      <c r="X23" s="51" t="str">
+        <f t="shared" si="34"/>
         <v>Key-REQ-23</v>
       </c>
-      <c r="Y23" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="Z23" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AA23" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="AB23" s="24" t="s">
-        <v>215</v>
+      <c r="Y23" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="64" t="s">
+        <v>1</v>
       </c>
       <c r="AC23" s="24" t="s">
         <v>124</v>
       </c>
     </row>
+    <row r="24" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="52">
+        <v>24</v>
+      </c>
+      <c r="B24" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="D24" s="62" t="s">
+        <v>216</v>
+      </c>
+      <c r="E24" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="F24" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="G24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="23" t="str">
+        <f t="shared" ref="L24:O24" si="41">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
+        <v>De API</v>
+      </c>
+      <c r="M24" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Métodos</v>
+      </c>
+      <c r="N24" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="O24" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>API Revit</v>
+      </c>
+      <c r="P24" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q24" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="R24" s="24" t="s">
+        <v>221</v>
+      </c>
+      <c r="S24" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T24" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>De API</v>
+      </c>
+      <c r="U24" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>Métodos</v>
+      </c>
+      <c r="V24" s="63" t="str">
+        <f t="shared" si="39"/>
+        <v>Macros</v>
+      </c>
+      <c r="W24" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X24" s="51" t="str">
+        <f t="shared" si="34"/>
+        <v>Key-REQ-24</v>
+      </c>
+      <c r="Y24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="64" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="64" t="s">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A1:C1 L1:Q1 A24:C1048576 S1:X1 L24:X1048576 AA1:XFD1 AA24:XFD1048576">
-    <cfRule type="cellIs" dxfId="14" priority="430" operator="equal">
+  <conditionalFormatting sqref="A2:B24">
+    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F1048576">
-    <cfRule type="duplicateValues" dxfId="13" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A2:B23">
-    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
+  <conditionalFormatting sqref="A1:C1 L1:Q1 S1:X1 AA1:XFD1 A25:C1048576 L25:X1048576 AA25:XFD1048576">
+    <cfRule type="cellIs" dxfId="30" priority="434" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+  <conditionalFormatting sqref="F1:F23 F25:F1048576">
+    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24">
+    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R24">
+    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4416,15 +4821,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3046875" style="1" customWidth="1"/>
-    <col min="2" max="10" width="5.15234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.53515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
+    <col min="2" max="10" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
@@ -4489,7 +4894,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -4557,7 +4962,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4570,14 +4975,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="3.3828125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18">
         <v>1</v>
       </c>
@@ -4591,55 +4996,55 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="12">
         <v>2</v>
       </c>
-      <c r="B2" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="36" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12">
         <v>3</v>
       </c>
-      <c r="B3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="36" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="29" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12">
         <v>4</v>
       </c>
-      <c r="B4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="36" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="34" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="35" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" s="29" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -4647,7 +5052,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="9" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="25" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4658,1039 +5063,2169 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BE003-A289-428E-9141-72F001D0AED0}">
   <sheetPr codeName="Planilha5"/>
-  <dimension ref="A1:U15"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.3" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AG20"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.15234375" style="49" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.15234375" style="49" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3046875" style="49" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.53515625" style="49" customWidth="1"/>
-    <col min="5" max="5" width="4.765625" style="49" customWidth="1"/>
-    <col min="6" max="6" width="2.61328125" style="49" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4" style="49" customWidth="1"/>
-    <col min="8" max="8" width="7.15234375" style="49" customWidth="1"/>
-    <col min="9" max="9" width="10" style="49" customWidth="1"/>
-    <col min="10" max="10" width="4.07421875" style="49" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.53515625" style="49" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.23046875" style="49" customWidth="1"/>
-    <col min="13" max="13" width="36.921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="3.921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.07421875" style="49" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.921875" style="49" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.07421875" style="63" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="2.3828125" style="49" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="2.84375" style="49" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="2.3828125" style="49" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="2.23046875" style="49" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.3046875" style="49"/>
+    <col min="1" max="1" width="2.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="48" customWidth="1"/>
+    <col min="4" max="4" width="8" style="48" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="48" customWidth="1"/>
+    <col min="6" max="6" width="4.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" style="48" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" style="48" customWidth="1"/>
+    <col min="9" max="9" width="11" style="48" customWidth="1"/>
+    <col min="10" max="10" width="6" style="48" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="46.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" style="48" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="40.7109375" style="59" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.28515625" style="48" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="3.85546875" style="65" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="71" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" style="71" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" style="71" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="71" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.28515625" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="16.3" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:33" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22">
         <v>1</v>
       </c>
       <c r="B1" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="38" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="39" t="s">
+      <c r="D1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="44" t="s">
+      <c r="E1" s="43" t="s">
         <v>88</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="44" t="s">
+      <c r="G1" s="43" t="s">
         <v>88</v>
       </c>
       <c r="H1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="I1" s="38" t="s">
+      <c r="I1" s="37" t="s">
         <v>88</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="K1" s="38" t="s">
+      <c r="K1" s="37" t="s">
         <v>88</v>
       </c>
       <c r="L1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="M1" s="38" t="s">
+      <c r="M1" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="N1" s="39" t="s">
+      <c r="N1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="O1" s="38" t="s">
+      <c r="O1" s="37" t="s">
         <v>88</v>
       </c>
-      <c r="P1" s="39" t="s">
+      <c r="P1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="61" t="s">
+      <c r="Q1" s="43" t="s">
         <v>88</v>
       </c>
-      <c r="R1" s="17" t="s">
+      <c r="R1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="44" t="s">
+      <c r="S1" s="43" t="s">
         <v>88</v>
       </c>
       <c r="T1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="44" t="s">
+      <c r="U1" s="43" t="s">
+        <v>88</v>
+      </c>
+      <c r="V1" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="W1" s="43" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="31">
+      <c r="X1" s="72" t="s">
+        <v>33</v>
+      </c>
+      <c r="Y1" s="73" t="s">
+        <v>34</v>
+      </c>
+      <c r="Z1" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AA1" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="AB1" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AC1" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD1" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AE1" s="38" t="s">
+        <v>34</v>
+      </c>
+      <c r="AF1" s="38" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG1" s="38" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="30">
         <v>2</v>
       </c>
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="26" t="s">
+      <c r="C2" s="74" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="37" t="s">
+      <c r="D2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="36" t="s">
         <v>1</v>
       </c>
       <c r="I2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J2" s="37" t="s">
+      <c r="J2" s="36" t="s">
         <v>79</v>
       </c>
       <c r="K2" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="M2" s="34" t="s">
+      <c r="S2" s="33" t="s">
         <v>137</v>
       </c>
-      <c r="N2" s="27" t="s">
+      <c r="T2" s="26" t="s">
         <v>138</v>
       </c>
-      <c r="O2" s="32" t="s">
+      <c r="U2" s="31" t="s">
         <v>139</v>
       </c>
-      <c r="P2" s="27" t="s">
+      <c r="V2" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="Q2" s="62" t="s">
+      <c r="W2" s="25" t="s">
         <v>183</v>
       </c>
-      <c r="R2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="S2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="T2" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="U2" s="25" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="31">
+      <c r="X2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="30">
         <v>3</v>
       </c>
-      <c r="B3" s="33" t="s">
+      <c r="B3" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="D3" s="48" t="s">
+      <c r="D3" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E3" s="43" t="s">
+      <c r="E3" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="37" t="s">
+      <c r="F3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="36" t="s">
         <v>149</v>
       </c>
       <c r="I3" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="J3" s="37" t="s">
+      <c r="J3" s="36" t="s">
         <v>79</v>
       </c>
       <c r="K3" s="25" t="s">
         <v>159</v>
       </c>
-      <c r="L3" s="37" t="s">
+      <c r="L3" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="37" t="s">
+      <c r="N3" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P3" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q3" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R3" s="27" t="s">
+      <c r="P3" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R3" s="26" t="s">
         <v>1</v>
       </c>
       <c r="S3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T3" s="27" t="s">
+      <c r="T3" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U3" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="31">
+      <c r="V3" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W3" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="30">
         <v>4</v>
       </c>
-      <c r="B4" s="33" t="s">
+      <c r="B4" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F4" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="37" t="s">
+      <c r="F4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="36" t="s">
         <v>149</v>
       </c>
       <c r="I4" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="J4" s="37" t="s">
+      <c r="J4" s="36" t="s">
         <v>79</v>
       </c>
       <c r="K4" s="25" t="s">
         <v>160</v>
       </c>
-      <c r="L4" s="37" t="s">
+      <c r="L4" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N4" s="37" t="s">
+      <c r="N4" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P4" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q4" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R4" s="27" t="s">
+      <c r="P4" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R4" s="26" t="s">
         <v>1</v>
       </c>
       <c r="S4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T4" s="27" t="s">
+      <c r="T4" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U4" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="5" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="31">
+      <c r="V4" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="30">
         <v>5</v>
       </c>
-      <c r="B5" s="33" t="s">
+      <c r="B5" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F5" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="37" t="s">
+      <c r="F5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="36" t="s">
         <v>149</v>
       </c>
       <c r="I5" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="J5" s="37" t="s">
+      <c r="J5" s="36" t="s">
         <v>79</v>
       </c>
       <c r="K5" s="25" t="s">
         <v>161</v>
       </c>
-      <c r="L5" s="37" t="s">
+      <c r="L5" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M5" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N5" s="37" t="s">
+      <c r="N5" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O5" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P5" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q5" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R5" s="27" t="s">
+      <c r="P5" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R5" s="26" t="s">
         <v>1</v>
       </c>
       <c r="S5" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T5" s="27" t="s">
+      <c r="T5" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U5" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="6" spans="1:21" customFormat="1" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="31">
+      <c r="V5" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W5" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="30">
         <v>6</v>
       </c>
-      <c r="B6" s="33" t="s">
+      <c r="B6" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="74" t="s">
         <v>174</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F6" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="37" t="s">
+      <c r="F6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="36" t="s">
         <v>149</v>
       </c>
       <c r="I6" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="J6" s="37" t="s">
+      <c r="J6" s="36" t="s">
         <v>79</v>
       </c>
       <c r="K6" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="L6" s="37" t="s">
+      <c r="L6" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M6" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N6" s="37" t="s">
+      <c r="N6" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O6" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P6" s="27" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q6" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R6" s="27" t="s">
+      <c r="P6" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R6" s="26" t="s">
         <v>1</v>
       </c>
       <c r="S6" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T6" s="27" t="s">
+      <c r="T6" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U6" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="7" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="31">
+      <c r="V6" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W6" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="30">
         <v>7</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="59" t="s">
+      <c r="C7" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F7" s="48" t="s">
+      <c r="F7" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="G7" s="64" t="s">
+      <c r="G7" s="60" t="s">
         <v>145</v>
       </c>
-      <c r="H7" s="37" t="s">
+      <c r="H7" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I7" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K7" s="25" t="s">
         <v>164</v>
       </c>
-      <c r="L7" s="37" t="s">
+      <c r="L7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N7" s="37" t="s">
+      <c r="N7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P7" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q7" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R7" s="27" t="s">
+      <c r="P7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R7" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T7" s="27" t="s">
+      <c r="T7" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U7" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="8" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="31">
+      <c r="V7" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W7" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="30">
         <v>8</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="59" t="s">
+      <c r="C8" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F8" s="48" t="s">
+      <c r="F8" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="G8" s="64" t="s">
+      <c r="G8" s="60" t="s">
         <v>146</v>
       </c>
-      <c r="H8" s="37" t="s">
+      <c r="H8" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I8" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="J8" s="27" t="s">
+      <c r="J8" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K8" s="25" t="s">
         <v>165</v>
       </c>
-      <c r="L8" s="37" t="s">
+      <c r="L8" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M8" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N8" s="37" t="s">
+      <c r="N8" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O8" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P8" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q8" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R8" s="27" t="s">
+      <c r="P8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R8" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T8" s="27" t="s">
+      <c r="T8" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U8" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="31">
+      <c r="V8" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W8" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="30">
         <v>9</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="59" t="s">
+      <c r="C9" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="48" t="s">
+      <c r="F9" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="G9" s="64" t="s">
+      <c r="G9" s="60" t="s">
         <v>147</v>
       </c>
-      <c r="H9" s="37" t="s">
+      <c r="H9" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I9" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="J9" s="27" t="s">
+      <c r="J9" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K9" s="25" t="s">
         <v>166</v>
       </c>
-      <c r="L9" s="37" t="s">
+      <c r="L9" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M9" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N9" s="37" t="s">
+      <c r="N9" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O9" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P9" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q9" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R9" s="27" t="s">
+      <c r="P9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R9" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S9" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T9" s="27" t="s">
+      <c r="T9" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U9" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="10" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="31">
+      <c r="V9" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W9" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="30">
         <v>10</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="59" t="s">
+      <c r="C10" s="75" t="s">
         <v>178</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F10" s="48" t="s">
+      <c r="F10" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="G10" s="64" t="s">
+      <c r="G10" s="60" t="s">
         <v>148</v>
       </c>
-      <c r="H10" s="37" t="s">
+      <c r="H10" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I10" s="25" t="s">
         <v>185</v>
       </c>
-      <c r="J10" s="27" t="s">
+      <c r="J10" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K10" s="25" t="s">
         <v>167</v>
       </c>
-      <c r="L10" s="37" t="s">
+      <c r="L10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N10" s="37" t="s">
+      <c r="N10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P10" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q10" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R10" s="27" t="s">
+      <c r="P10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R10" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T10" s="27" t="s">
+      <c r="T10" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U10" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="11" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="31">
+      <c r="V10" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W10" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="30">
         <v>11</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="74" t="s">
         <v>193</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="37" t="s">
+      <c r="F11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I11" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="J11" s="27" t="s">
+      <c r="J11" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K11" s="25" t="s">
         <v>140</v>
       </c>
-      <c r="L11" s="37" t="s">
+      <c r="L11" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M11" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N11" s="37" t="s">
+      <c r="N11" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O11" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P11" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q11" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R11" s="27" t="s">
+      <c r="P11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R11" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S11" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T11" s="27" t="s">
+      <c r="T11" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U11" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="31">
+      <c r="V11" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W11" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="30">
         <v>12</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="74" t="s">
         <v>195</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F12" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="37" t="s">
+      <c r="F12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I12" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="J12" s="27" t="s">
+      <c r="J12" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K12" s="25" t="s">
         <v>141</v>
       </c>
-      <c r="L12" s="37" t="s">
+      <c r="L12" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M12" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N12" s="37" t="s">
+      <c r="N12" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O12" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P12" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q12" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R12" s="27" t="s">
+      <c r="P12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R12" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S12" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T12" s="27" t="s">
+      <c r="T12" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U12" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="31">
+      <c r="V12" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W12" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="30">
         <v>13</v>
       </c>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="26" t="s">
+      <c r="C13" s="74" t="s">
         <v>196</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="E13" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F13" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="37" t="s">
+      <c r="F13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I13" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="J13" s="27" t="s">
+      <c r="J13" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K13" s="25" t="s">
         <v>142</v>
       </c>
-      <c r="L13" s="37" t="s">
+      <c r="L13" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N13" s="37" t="s">
+      <c r="N13" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P13" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q13" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R13" s="27" t="s">
+      <c r="P13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R13" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T13" s="27" t="s">
+      <c r="T13" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U13" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="31">
+      <c r="V13" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W13" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="30">
         <v>14</v>
       </c>
-      <c r="B14" s="33" t="s">
+      <c r="B14" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="C14" s="26" t="s">
+      <c r="C14" s="74" t="s">
         <v>194</v>
       </c>
-      <c r="D14" s="48" t="s">
+      <c r="D14" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E14" s="43" t="s">
+      <c r="E14" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="37" t="s">
+      <c r="F14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I14" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="J14" s="27" t="s">
+      <c r="J14" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K14" s="25" t="s">
         <v>143</v>
       </c>
-      <c r="L14" s="37" t="s">
+      <c r="L14" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M14" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N14" s="37" t="s">
+      <c r="N14" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O14" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P14" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q14" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R14" s="27" t="s">
+      <c r="P14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R14" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S14" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T14" s="27" t="s">
+      <c r="T14" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U14" s="25" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="15" spans="1:21" ht="7.3" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="31">
+      <c r="V14" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W14" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="30">
         <v>15</v>
       </c>
-      <c r="B15" s="33" t="s">
+      <c r="B15" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="74" t="s">
         <v>197</v>
       </c>
-      <c r="D15" s="48" t="s">
+      <c r="D15" s="47" t="s">
         <v>181</v>
       </c>
-      <c r="E15" s="43" t="s">
+      <c r="E15" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F15" s="48" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="43" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="37" t="s">
+      <c r="F15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="36" t="s">
         <v>184</v>
       </c>
       <c r="I15" s="25" t="s">
         <v>186</v>
       </c>
-      <c r="J15" s="27" t="s">
+      <c r="J15" s="26" t="s">
         <v>79</v>
       </c>
       <c r="K15" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="L15" s="37" t="s">
+      <c r="L15" s="36" t="s">
         <v>1</v>
       </c>
       <c r="M15" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="N15" s="37" t="s">
+      <c r="N15" s="36" t="s">
         <v>1</v>
       </c>
       <c r="O15" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="P15" s="37" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q15" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="R15" s="27" t="s">
+      <c r="P15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R15" s="36" t="s">
         <v>1</v>
       </c>
       <c r="S15" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T15" s="27" t="s">
+      <c r="T15" s="26" t="s">
         <v>1</v>
       </c>
       <c r="U15" s="25" t="s">
         <v>1</v>
       </c>
+      <c r="V15" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="W15" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="30">
+        <v>16</v>
+      </c>
+      <c r="B16" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="C16" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="L16" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="N16" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="O16" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="P16" s="69" t="str">
+        <f t="shared" ref="P16:P20" si="0">IF(Q16="null", "null", "método.revit")</f>
+        <v>método.revit</v>
+      </c>
+      <c r="Q16" s="70" t="s">
+        <v>228</v>
+      </c>
+      <c r="R16" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="T16" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="U16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="V16" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="W16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="30">
+        <v>17</v>
+      </c>
+      <c r="B17" s="66" t="s">
+        <v>229</v>
+      </c>
+      <c r="C17" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="D17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="K17" s="25" t="s">
+        <v>231</v>
+      </c>
+      <c r="L17" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="M17" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="N17" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="O17" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="P17" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q17" s="70" t="s">
+        <v>232</v>
+      </c>
+      <c r="R17" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S17" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="T17" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="U17" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="V17" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="W17" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="30">
+        <v>18</v>
+      </c>
+      <c r="B18" s="66" t="s">
+        <v>233</v>
+      </c>
+      <c r="C18" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="K18" s="25" t="s">
+        <v>235</v>
+      </c>
+      <c r="L18" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="M18" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="N18" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="O18" s="25" t="s">
+        <v>234</v>
+      </c>
+      <c r="P18" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q18" s="70" t="s">
+        <v>236</v>
+      </c>
+      <c r="R18" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S18" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="T18" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="U18" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="V18" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="W18" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="30">
+        <v>19</v>
+      </c>
+      <c r="B19" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="C19" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="D19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="L19" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="M19" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="N19" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="O19" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="P19" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q19" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="R19" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S19" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="T19" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="U19" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="V19" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="W19" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="30">
+        <v>20</v>
+      </c>
+      <c r="B20" s="66" t="s">
+        <v>241</v>
+      </c>
+      <c r="C20" s="62" t="s">
+        <v>218</v>
+      </c>
+      <c r="D20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="68" t="s">
+        <v>79</v>
+      </c>
+      <c r="K20" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="L20" s="67" t="s">
+        <v>223</v>
+      </c>
+      <c r="M20" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="N20" s="67" t="s">
+        <v>225</v>
+      </c>
+      <c r="O20" s="25" t="s">
+        <v>242</v>
+      </c>
+      <c r="P20" s="69" t="str">
+        <f t="shared" si="0"/>
+        <v>método.revit</v>
+      </c>
+      <c r="Q20" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="R20" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="S20" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="T20" s="67" t="s">
+        <v>1</v>
+      </c>
+      <c r="U20" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="V20" s="76" t="s">
+        <v>1</v>
+      </c>
+      <c r="W20" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="X20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="42" t="s">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:U13">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A10:W13">
     <sortCondition ref="A1:A13"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2:B6">
-    <cfRule type="duplicateValues" dxfId="8" priority="1969"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="1970"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="1988"/>
+    <cfRule type="duplicateValues" dxfId="23" priority="1989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B15 B1">
-    <cfRule type="duplicateValues" dxfId="6" priority="1965"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1966"/>
+    <cfRule type="duplicateValues" dxfId="22" priority="1984"/>
+    <cfRule type="duplicateValues" dxfId="21" priority="1985"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:E15 F15:H15">
-    <cfRule type="cellIs" dxfId="4" priority="41" operator="equal">
+  <conditionalFormatting sqref="D3:E15 F15:H15 X1:Y1 F16:G20 X21:Y1048576">
+    <cfRule type="cellIs" dxfId="20" priority="60" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D1:U1 F2:U2">
-    <cfRule type="cellIs" dxfId="3" priority="18" operator="equal">
+  <conditionalFormatting sqref="F2:K2 D1:W1 R2:W2">
+    <cfRule type="cellIs" dxfId="19" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:G14 A1:B15 D2 H3:U15">
-    <cfRule type="cellIs" dxfId="2" priority="21" operator="equal">
+  <conditionalFormatting sqref="F3:G14 A1:B15 D2 A16:A20 H3:W15 L2:Q2 R16:S20">
+    <cfRule type="cellIs" dxfId="18" priority="40" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G10">
-    <cfRule type="duplicateValues" dxfId="1" priority="1"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B16:B20">
+    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="T16:W20">
+    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1">
+    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z1:AG1">
+    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB1">
+    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD1">
+    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF1">
+    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D16:E20">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="Z2:AA20">
+    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AB2:AC20">
+    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AD2:AE20">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AF2:AG20">
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="X2:Y20">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H16:I20">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/Versão5/PRO/Ontologia_Requisitos.xlsx
+++ b/Versão5/PRO/Ontologia_Requisitos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86934C0F-1BB5-4CDF-9DB2-47E59DD38D50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDD9C66-4588-4987-B7B8-46EC17FD7669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="4" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -1387,7 +1387,31 @@
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="32">
+  <dxfs count="28">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1395,6 +1419,50 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1446,62 +1514,6 @@
     </dxf>
     <dxf>
       <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C0006"/>
       </font>
       <fill>
@@ -1519,50 +1531,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1981,15 +1949,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.28515625" style="6"/>
+    <col min="2" max="2" width="68.84375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.3828125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.3046875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
@@ -2000,7 +1968,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
@@ -2011,7 +1979,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
@@ -2022,7 +1990,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -2033,7 +2001,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -2045,7 +2013,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -2057,7 +2025,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -2068,7 +2036,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
@@ -2079,7 +2047,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -2090,7 +2058,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
@@ -2101,7 +2069,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -2112,7 +2080,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
@@ -2123,7 +2091,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
@@ -2134,7 +2102,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
@@ -2145,7 +2113,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -2156,7 +2124,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
@@ -2167,7 +2135,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
@@ -2178,19 +2146,19 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="40">
         <f ca="1">NOW()</f>
-        <v>46259.689952546294</v>
+        <v>46264.568761111113</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="8" t="s">
         <v>99</v>
       </c>
@@ -2201,7 +2169,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="8" t="s">
         <v>98</v>
       </c>
@@ -2212,7 +2180,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="8" t="s">
         <v>100</v>
       </c>
@@ -2223,7 +2191,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="8" t="s">
         <v>56</v>
       </c>
@@ -2234,7 +2202,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
@@ -2245,7 +2213,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="10" t="s">
         <v>58</v>
       </c>
@@ -2256,7 +2224,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
@@ -2268,7 +2236,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A26" s="10" t="s">
         <v>92</v>
       </c>
@@ -2280,7 +2248,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A27" s="8" t="s">
         <v>105</v>
       </c>
@@ -2291,7 +2259,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A28" s="8" t="s">
         <v>107</v>
       </c>
@@ -2302,7 +2270,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A29" s="8" t="s">
         <v>109</v>
       </c>
@@ -2313,7 +2281,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="8" t="s">
         <v>111</v>
       </c>
@@ -2324,7 +2292,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="8" t="s">
         <v>112</v>
       </c>
@@ -2335,7 +2303,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="8" t="s">
         <v>113</v>
       </c>
@@ -2346,7 +2314,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="8" t="s">
         <v>114</v>
       </c>
@@ -2357,7 +2325,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="8" t="s">
         <v>115</v>
       </c>
@@ -2368,7 +2336,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="8" t="s">
         <v>116</v>
       </c>
@@ -2379,7 +2347,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="8" t="s">
         <v>117</v>
       </c>
@@ -2390,7 +2358,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="8" t="s">
         <v>118</v>
       </c>
@@ -2401,7 +2369,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="10" t="s">
         <v>119</v>
       </c>
@@ -2412,7 +2380,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:3" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="8" t="s">
         <v>121</v>
       </c>
@@ -2440,37 +2408,37 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A1:AC24"/>
-  <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="32.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="1.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="1.3828125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.3046875" style="27" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="7" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.15234375" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="6.3828125" style="27" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="54.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="49.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.140625" style="27" customWidth="1"/>
-    <col min="24" max="24" width="7.5703125" style="27" customWidth="1"/>
-    <col min="25" max="25" width="6.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.140625" style="27" customWidth="1"/>
-    <col min="27" max="27" width="5.42578125" style="27" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.85546875" style="27" customWidth="1"/>
-    <col min="29" max="29" width="20.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="32.140625" style="27"/>
+    <col min="13" max="13" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.3046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="47.53515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="54.15234375" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="49.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="7.15234375" style="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="5.3046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.15234375" style="27" customWidth="1"/>
+    <col min="24" max="24" width="7.53515625" style="27" customWidth="1"/>
+    <col min="25" max="25" width="6.3046875" style="27" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="9.15234375" style="27" customWidth="1"/>
+    <col min="27" max="27" width="5.3828125" style="27" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.84375" style="27" customWidth="1"/>
+    <col min="29" max="29" width="20.69140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="32.15234375" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="40.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" ht="40.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -2559,7 +2527,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="52">
         <v>2</v>
       </c>
@@ -2656,7 +2624,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="3" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="52">
         <v>3</v>
       </c>
@@ -2753,7 +2721,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="4" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="52">
         <v>4</v>
       </c>
@@ -2850,7 +2818,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="52">
         <v>5</v>
       </c>
@@ -2947,7 +2915,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="6" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="52">
         <v>6</v>
       </c>
@@ -3044,7 +3012,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="7" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="52">
         <v>7</v>
       </c>
@@ -3141,7 +3109,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="52">
         <v>8</v>
       </c>
@@ -3238,7 +3206,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="52">
         <v>9</v>
       </c>
@@ -3335,7 +3303,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="10" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="52">
         <v>10</v>
       </c>
@@ -3432,7 +3400,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="11" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="52">
         <v>11</v>
       </c>
@@ -3529,7 +3497,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="52">
         <v>12</v>
       </c>
@@ -3626,7 +3594,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="13" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="52">
         <v>13</v>
       </c>
@@ -3723,7 +3691,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="14" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="52">
         <v>14</v>
       </c>
@@ -3820,7 +3788,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="15" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="52">
         <v>15</v>
       </c>
@@ -3917,7 +3885,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="16" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="52">
         <v>16</v>
       </c>
@@ -4014,7 +3982,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="52">
         <v>17</v>
       </c>
@@ -4111,7 +4079,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="18" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="52">
         <v>18</v>
       </c>
@@ -4208,7 +4176,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="19" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="52">
         <v>19</v>
       </c>
@@ -4305,7 +4273,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="20" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="52">
         <v>20</v>
       </c>
@@ -4402,7 +4370,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="52">
         <v>21</v>
       </c>
@@ -4499,7 +4467,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="22" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="52">
         <v>22</v>
       </c>
@@ -4596,7 +4564,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="23" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="52">
         <v>23</v>
       </c>
@@ -4693,7 +4661,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="24" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="52">
         <v>24</v>
       </c>
@@ -4704,10 +4672,10 @@
         <v>215</v>
       </c>
       <c r="D24" s="62" t="s">
+        <v>217</v>
+      </c>
+      <c r="E24" s="62" t="s">
         <v>216</v>
-      </c>
-      <c r="E24" s="62" t="s">
-        <v>217</v>
       </c>
       <c r="F24" s="62" t="s">
         <v>218</v>
@@ -4733,11 +4701,11 @@
       </c>
       <c r="M24" s="23" t="str">
         <f t="shared" si="41"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="N24" s="23" t="str">
         <f t="shared" si="41"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="O24" s="23" t="str">
         <f t="shared" si="41"/>
@@ -4761,11 +4729,11 @@
       </c>
       <c r="U24" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>Métodos</v>
+        <v>Macros</v>
       </c>
       <c r="V24" s="63" t="str">
         <f t="shared" si="39"/>
-        <v>Macros</v>
+        <v>Métodos</v>
       </c>
       <c r="W24" s="24" t="s">
         <v>133</v>
@@ -4793,23 +4761,23 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B24">
-    <cfRule type="cellIs" dxfId="31" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:C1 L1:Q1 S1:X1 AA1:XFD1 A25:C1048576 L25:X1048576 AA25:XFD1048576">
-    <cfRule type="cellIs" dxfId="30" priority="434" operator="equal">
+    <cfRule type="cellIs" dxfId="26" priority="434" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23 F25:F1048576">
-    <cfRule type="duplicateValues" dxfId="29" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="25" priority="11"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24">
-    <cfRule type="duplicateValues" dxfId="28" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R24">
-    <cfRule type="cellIs" dxfId="27" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4821,15 +4789,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
-    <col min="2" max="10" width="5.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.140625" style="5"/>
+    <col min="1" max="1" width="2.3046875" style="1" customWidth="1"/>
+    <col min="2" max="10" width="5.15234375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.53515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.15234375" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
@@ -4894,7 +4862,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -4962,7 +4930,7 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="cellIs" dxfId="26" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="22" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4975,14 +4943,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="3.3828125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="18">
         <v>1</v>
       </c>
@@ -4996,7 +4964,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -5010,7 +4978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -5024,7 +4992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -5038,13 +5006,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -5052,7 +5020,7 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4">
-    <cfRule type="cellIs" dxfId="25" priority="32" operator="equal">
+    <cfRule type="cellIs" dxfId="21" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5064,44 +5032,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BE003-A289-428E-9141-72F001D0AED0}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG20"/>
-  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="48" customWidth="1"/>
+    <col min="1" max="1" width="2.3828125" style="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.69140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.69140625" style="48" customWidth="1"/>
     <col min="4" max="4" width="8" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" style="48" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" style="48" customWidth="1"/>
+    <col min="5" max="5" width="4.69140625" style="48" customWidth="1"/>
+    <col min="6" max="6" width="4.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.53515625" style="48" customWidth="1"/>
+    <col min="8" max="8" width="7.84375" style="48" customWidth="1"/>
     <col min="9" max="9" width="11" style="48" customWidth="1"/>
     <col min="10" max="10" width="6" style="48" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="46.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" style="48" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.42578125" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="40.7109375" style="59" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.28515625" style="48" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="3.85546875" style="65" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="71" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="71" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="71" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="71" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="71" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.28515625" style="48"/>
+    <col min="11" max="11" width="46.3828125" style="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.69140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.84375" style="48" customWidth="1"/>
+    <col min="16" max="16" width="8.3828125" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.3828125" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.3828125" style="48" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="40.69140625" style="59" customWidth="1"/>
+    <col min="20" max="20" width="5.69140625" style="48" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.3046875" style="48" customWidth="1"/>
+    <col min="22" max="22" width="7.3046875" style="48" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.84375" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="3.84375" style="65" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.3046875" style="71" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.84375" style="71" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.3046875" style="71" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.84375" style="71" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.3046875" style="71" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.84375" style="71" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.3046875" style="71" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.84375" style="71" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.3046875" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:33" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -5202,7 +5170,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="30">
         <v>2</v>
       </c>
@@ -5303,7 +5271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A3" s="30">
         <v>3</v>
       </c>
@@ -5404,7 +5372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A4" s="30">
         <v>4</v>
       </c>
@@ -5505,7 +5473,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A5" s="30">
         <v>5</v>
       </c>
@@ -5606,7 +5574,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="30">
         <v>6</v>
       </c>
@@ -5707,7 +5675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="30">
         <v>7</v>
       </c>
@@ -5808,7 +5776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="30">
         <v>8</v>
       </c>
@@ -5909,7 +5877,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="30">
         <v>9</v>
       </c>
@@ -6010,7 +5978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="30">
         <v>10</v>
       </c>
@@ -6111,7 +6079,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A11" s="30">
         <v>11</v>
       </c>
@@ -6212,7 +6180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="30">
         <v>12</v>
       </c>
@@ -6313,7 +6281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="30">
         <v>13</v>
       </c>
@@ -6414,7 +6382,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="30">
         <v>14</v>
       </c>
@@ -6515,7 +6483,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="30">
         <v>15</v>
       </c>
@@ -6616,7 +6584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="30">
         <v>16</v>
       </c>
@@ -6718,7 +6686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="30">
         <v>17</v>
       </c>
@@ -6820,7 +6788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="30">
         <v>18</v>
       </c>
@@ -6922,7 +6890,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="30">
         <v>19</v>
       </c>
@@ -7024,7 +6992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="30">
         <v>20</v>
       </c>
@@ -7132,98 +7100,83 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2:B6">
-    <cfRule type="duplicateValues" dxfId="24" priority="1988"/>
-    <cfRule type="duplicateValues" dxfId="23" priority="1989"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1988"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1989"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B15 B1">
-    <cfRule type="duplicateValues" dxfId="22" priority="1984"/>
-    <cfRule type="duplicateValues" dxfId="21" priority="1985"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1984"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1985"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D3:E15 F15:H15 X1:Y1 F16:G20 X21:Y1048576">
-    <cfRule type="cellIs" dxfId="20" priority="60" operator="equal">
+  <conditionalFormatting sqref="B16:B20">
+    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="D3:E20">
+    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F2:K2 D1:W1 R2:W2">
-    <cfRule type="cellIs" dxfId="19" priority="37" operator="equal">
+  <conditionalFormatting sqref="D1:AG1">
+    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F3:G14 A1:B15 D2 A16:A20 H3:W15 L2:Q2 R16:S20">
-    <cfRule type="cellIs" dxfId="18" priority="40" operator="equal">
+  <conditionalFormatting sqref="F3:G14 A1:B15 D2 H3:W15 A16:A20">
+    <cfRule type="cellIs" dxfId="12" priority="40" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F15:H15">
+    <cfRule type="cellIs" dxfId="11" priority="60" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F16:I20">
+    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F2:W2">
+    <cfRule type="cellIs" dxfId="9" priority="37" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G10">
-    <cfRule type="duplicateValues" dxfId="17" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="16" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B16:B20">
-    <cfRule type="duplicateValues" dxfId="15" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="19"/>
+  <conditionalFormatting sqref="R16:W20">
+    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="T16:W20">
-    <cfRule type="cellIs" dxfId="13" priority="17" operator="equal">
+  <conditionalFormatting sqref="X2:Y1048576">
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="12" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="Z1:AG1">
-    <cfRule type="cellIs" dxfId="11" priority="14" operator="equal">
+  <conditionalFormatting sqref="Z2:AG20">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="9" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="8" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="7" priority="10" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D16:E20">
-    <cfRule type="cellIs" dxfId="6" priority="7" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="Z2:AA20">
-    <cfRule type="cellIs" dxfId="5" priority="6" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AB2:AC20">
-    <cfRule type="cellIs" dxfId="4" priority="5" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD2:AE20">
-    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AF2:AG20">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="X2:Y20">
-    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H16:I20">
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/PRO/Ontologia_Requisitos.xlsx
+++ b/Versão5/PRO/Ontologia_Requisitos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFDD9C66-4588-4987-B7B8-46EC17FD7669}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235B5ECB-2E94-4161-BC41-313197BA62E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="22149" windowHeight="13200" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1288" uniqueCount="245">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="263">
   <si>
     <t>Key</t>
   </si>
@@ -727,18 +727,6 @@
     <t>Macros</t>
   </si>
   <si>
-    <t>API.Revit</t>
-  </si>
-  <si>
-    <t>Aplicação Revit</t>
-  </si>
-  <si>
-    <t>Aplicativo Revit</t>
-  </si>
-  <si>
-    <t>Revit Aplication</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -806,6 +794,72 @@
   </si>
   <si>
     <t>"[ Materiais ]"</t>
+  </si>
+  <si>
+    <t>Função.Auxiliar</t>
+  </si>
+  <si>
+    <t>Define uma Função Auxiliar (helper) numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol de ayudante en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Helper Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Global</t>
+  </si>
+  <si>
+    <t>Define uma Função Global numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol global en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Global Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Local</t>
+  </si>
+  <si>
+    <t>Define uma Função Local numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina un rol local en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Local Role in an application</t>
+  </si>
+  <si>
+    <t>Função.Filtro</t>
+  </si>
+  <si>
+    <t>Define uma Função para filtrar objetos numa aplicação</t>
+  </si>
+  <si>
+    <t>Defina una función para filtrar objetos en una aplicación</t>
+  </si>
+  <si>
+    <t>Define a Function to filter objects in an application</t>
+  </si>
+  <si>
+    <t>Códigos.Visuais</t>
+  </si>
+  <si>
+    <t>Bloco.de.Código</t>
+  </si>
+  <si>
+    <t>Define um Código escrito em sistemas de programação visual</t>
+  </si>
+  <si>
+    <t>Define un código escrito en sistemas de programación visual</t>
+  </si>
+  <si>
+    <t>Defines a Code written in visual programming systems</t>
+  </si>
+  <si>
+    <t>KML</t>
   </si>
 </sst>
 </file>
@@ -940,7 +994,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="29">
+  <fills count="30">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1107,6 +1161,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
         <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE89F"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1336,12 +1396,6 @@
     <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1382,12 +1436,18 @@
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="29">
     <dxf>
       <font>
         <b val="0"/>
@@ -1595,6 +1655,16 @@
         <strike val="0"/>
         <color theme="0" tint="-0.499984740745262"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1949,15 +2019,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="3.3046875" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="68.84375" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.3828125" style="46" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="3.3046875" style="6"/>
+    <col min="2" max="2" width="68.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="4" max="16384" width="3.28515625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>35</v>
       </c>
@@ -1968,7 +2038,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="8" t="s">
         <v>44</v>
       </c>
@@ -1979,7 +2049,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
         <v>45</v>
       </c>
@@ -1990,7 +2060,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
         <v>36</v>
       </c>
@@ -2001,7 +2071,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -2013,7 +2083,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
         <v>38</v>
       </c>
@@ -2025,7 +2095,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
         <v>39</v>
       </c>
@@ -2036,7 +2106,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
@@ -2047,7 +2117,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
         <v>48</v>
       </c>
@@ -2058,7 +2128,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
         <v>50</v>
       </c>
@@ -2069,7 +2139,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
         <v>41</v>
       </c>
@@ -2080,7 +2150,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
         <v>42</v>
       </c>
@@ -2091,7 +2161,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
         <v>51</v>
       </c>
@@ -2102,7 +2172,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
         <v>52</v>
       </c>
@@ -2113,7 +2183,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
         <v>53</v>
       </c>
@@ -2124,7 +2194,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
         <v>54</v>
       </c>
@@ -2135,7 +2205,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
         <v>43</v>
       </c>
@@ -2146,19 +2216,19 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
         <v>55</v>
       </c>
       <c r="B18" s="40">
         <f ca="1">NOW()</f>
-        <v>46264.568761111113</v>
+        <v>46268.698654282409</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>99</v>
       </c>
@@ -2169,7 +2239,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>98</v>
       </c>
@@ -2180,7 +2250,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
         <v>100</v>
       </c>
@@ -2191,7 +2261,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
         <v>56</v>
       </c>
@@ -2202,7 +2272,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>57</v>
       </c>
@@ -2213,7 +2283,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
         <v>58</v>
       </c>
@@ -2224,7 +2294,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>59</v>
       </c>
@@ -2236,7 +2306,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
         <v>92</v>
       </c>
@@ -2248,7 +2318,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
         <v>105</v>
       </c>
@@ -2259,7 +2329,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
         <v>107</v>
       </c>
@@ -2270,7 +2340,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
         <v>109</v>
       </c>
@@ -2281,7 +2351,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A30" s="8" t="s">
         <v>111</v>
       </c>
@@ -2292,7 +2362,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A31" s="8" t="s">
         <v>112</v>
       </c>
@@ -2303,7 +2373,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="8" t="s">
         <v>113</v>
       </c>
@@ -2314,7 +2384,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A33" s="8" t="s">
         <v>114</v>
       </c>
@@ -2325,7 +2395,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A34" s="8" t="s">
         <v>115</v>
       </c>
@@ -2336,7 +2406,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A35" s="8" t="s">
         <v>116</v>
       </c>
@@ -2347,7 +2417,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A36" s="8" t="s">
         <v>117</v>
       </c>
@@ -2358,7 +2428,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A37" s="8" t="s">
         <v>118</v>
       </c>
@@ -2369,7 +2439,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
         <v>119</v>
       </c>
@@ -2380,7 +2450,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="39" spans="1:3" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:3" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
         <v>121</v>
       </c>
@@ -2407,38 +2477,39 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{375F50FD-D5BA-45CD-9CBD-E4284A1EA77F}">
   <sheetPr codeName="Planilha2"/>
-  <dimension ref="A1:AC24"/>
-  <sheetFormatPr defaultColWidth="32.15234375" defaultRowHeight="6.65" customHeight="1" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:AD28"/>
+  <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="1.3828125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="4.3046875" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.15234375" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="7" max="11" width="6.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="7" style="27" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.3046875" style="27" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.53515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="47.53515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="54.15234375" style="27" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="49.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="7.15234375" style="27" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="5.3046875" style="27" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8.15234375" style="27" customWidth="1"/>
-    <col min="24" max="24" width="7.53515625" style="27" customWidth="1"/>
-    <col min="25" max="25" width="6.3046875" style="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="9.15234375" style="27" customWidth="1"/>
-    <col min="27" max="27" width="5.3828125" style="27" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="6.84375" style="27" customWidth="1"/>
-    <col min="29" max="29" width="20.69140625" style="27" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="32.15234375" style="27"/>
+    <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="7" max="11" width="10.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="64.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="73.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="67.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="3.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="13.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="9.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="8.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="7.5703125" style="27" customWidth="1"/>
+    <col min="25" max="25" width="6.28515625" style="27" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="7.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="5.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="6.85546875" style="27" customWidth="1"/>
+    <col min="29" max="29" width="20.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.140625" style="27" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="32.140625" style="27"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="40.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:30" ht="40.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13">
         <v>1</v>
       </c>
@@ -2526,8 +2597,11 @@
       <c r="AC1" s="15" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="2" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD1" s="15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="52">
         <v>2</v>
       </c>
@@ -2608,23 +2682,26 @@
         <f t="shared" ref="X2:X3" si="7">CONCATENATE("Key-REQ-",A2)</f>
         <v>Key-REQ-2</v>
       </c>
-      <c r="Y2" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="64" t="s">
+      <c r="Y2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC2" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="3" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD2" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="52">
         <v>3</v>
       </c>
@@ -2705,23 +2782,26 @@
         <f t="shared" si="7"/>
         <v>Key-REQ-3</v>
       </c>
-      <c r="Y3" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="64" t="s">
+      <c r="Y3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC3" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="4" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD3" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="52">
         <v>4</v>
       </c>
@@ -2802,23 +2882,26 @@
         <f t="shared" ref="X4:X18" si="11">CONCATENATE("Key-REQ-",A4)</f>
         <v>Key-REQ-4</v>
       </c>
-      <c r="Y4" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="64" t="s">
+      <c r="Y4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC4" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="5" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD4" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="52">
         <v>5</v>
       </c>
@@ -2899,23 +2982,26 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-5</v>
       </c>
-      <c r="Y5" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="64" t="s">
+      <c r="Y5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC5" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="6" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD5" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52">
         <v>6</v>
       </c>
@@ -2996,23 +3082,26 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-6</v>
       </c>
-      <c r="Y6" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="64" t="s">
+      <c r="Y6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC6" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="7" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD6" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="52">
         <v>7</v>
       </c>
@@ -3093,23 +3182,26 @@
         <f t="shared" ref="X7:X11" si="19">CONCATENATE("Key-REQ-",A7)</f>
         <v>Key-REQ-7</v>
       </c>
-      <c r="Y7" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="64" t="s">
+      <c r="Y7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC7" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="8" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD7" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52">
         <v>8</v>
       </c>
@@ -3190,23 +3282,26 @@
         <f t="shared" si="19"/>
         <v>Key-REQ-8</v>
       </c>
-      <c r="Y8" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="64" t="s">
+      <c r="Y8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC8" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="9" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD8" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52">
         <v>9</v>
       </c>
@@ -3287,23 +3382,26 @@
         <f t="shared" si="19"/>
         <v>Key-REQ-9</v>
       </c>
-      <c r="Y9" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="64" t="s">
+      <c r="Y9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC9" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="10" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD9" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="52">
         <v>10</v>
       </c>
@@ -3384,23 +3482,26 @@
         <f t="shared" si="19"/>
         <v>Key-REQ-10</v>
       </c>
-      <c r="Y10" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="64" t="s">
+      <c r="Y10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC10" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="11" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD10" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="52">
         <v>11</v>
       </c>
@@ -3481,23 +3582,26 @@
         <f t="shared" si="19"/>
         <v>Key-REQ-11</v>
       </c>
-      <c r="Y11" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="64" t="s">
+      <c r="Y11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC11" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="12" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD11" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="52">
         <v>12</v>
       </c>
@@ -3578,23 +3682,26 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-12</v>
       </c>
-      <c r="Y12" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="64" t="s">
+      <c r="Y12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC12" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="13" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD12" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="52">
         <v>13</v>
       </c>
@@ -3675,23 +3782,26 @@
         <f t="shared" ref="X13:X14" si="20">CONCATENATE("Key-REQ-",A13)</f>
         <v>Key-REQ-13</v>
       </c>
-      <c r="Y13" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="64" t="s">
+      <c r="Y13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC13" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="14" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD13" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="52">
         <v>14</v>
       </c>
@@ -3772,23 +3882,26 @@
         <f t="shared" si="20"/>
         <v>Key-REQ-14</v>
       </c>
-      <c r="Y14" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="64" t="s">
+      <c r="Y14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC14" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="15" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD14" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="52">
         <v>15</v>
       </c>
@@ -3869,23 +3982,26 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-15</v>
       </c>
-      <c r="Y15" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="64" t="s">
+      <c r="Y15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC15" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="16" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD15" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="52">
         <v>16</v>
       </c>
@@ -3966,23 +4082,26 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-16</v>
       </c>
-      <c r="Y16" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="64" t="s">
+      <c r="Y16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC16" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="17" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD16" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="52">
         <v>17</v>
       </c>
@@ -4063,23 +4182,26 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-17</v>
       </c>
-      <c r="Y17" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="64" t="s">
+      <c r="Y17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC17" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="18" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD17" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52">
         <v>18</v>
       </c>
@@ -4160,23 +4282,26 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-18</v>
       </c>
-      <c r="Y18" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="64" t="s">
+      <c r="Y18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC18" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="19" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD18" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="52">
         <v>19</v>
       </c>
@@ -4254,26 +4379,29 @@
         <v>133</v>
       </c>
       <c r="X19" s="51" t="str">
-        <f t="shared" ref="X19:X24" si="34">CONCATENATE("Key-REQ-",A19)</f>
+        <f t="shared" ref="X19:X28" si="34">CONCATENATE("Key-REQ-",A19)</f>
         <v>Key-REQ-19</v>
       </c>
-      <c r="Y19" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="64" t="s">
+      <c r="Y19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC19" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="20" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD19" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="52">
         <v>20</v>
       </c>
@@ -4354,23 +4482,26 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-20</v>
       </c>
-      <c r="Y20" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="64" t="s">
+      <c r="Y20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC20" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="21" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD20" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="52">
         <v>21</v>
       </c>
@@ -4451,23 +4582,26 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-21</v>
       </c>
-      <c r="Y21" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="64" t="s">
+      <c r="Y21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC21" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="22" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD21" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="52">
         <v>22</v>
       </c>
@@ -4530,7 +4664,7 @@
         <v>1</v>
       </c>
       <c r="T22" s="24" t="str">
-        <f t="shared" ref="T22:V24" si="39">SUBSTITUTE(C22, ".", " ")</f>
+        <f t="shared" ref="T22:V28" si="39">SUBSTITUTE(C22, ".", " ")</f>
         <v>De Necessidades</v>
       </c>
       <c r="U22" s="24" t="str">
@@ -4548,23 +4682,26 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-22</v>
       </c>
-      <c r="Y22" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="64" t="s">
+      <c r="Y22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC22" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="23" spans="1:29" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="AD22" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="52">
         <v>23</v>
       </c>
@@ -4645,40 +4782,43 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-23</v>
       </c>
-      <c r="Y23" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="64" t="s">
+      <c r="Y23" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="62" t="s">
         <v>1</v>
       </c>
       <c r="AC23" s="24" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="24" spans="1:29" s="65" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AD23" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="52">
         <v>24</v>
       </c>
-      <c r="B24" s="61" t="s">
+      <c r="B24" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C24" s="62" t="s">
+      <c r="C24" s="76" t="s">
         <v>215</v>
       </c>
-      <c r="D24" s="62" t="s">
+      <c r="D24" s="76" t="s">
         <v>217</v>
       </c>
-      <c r="E24" s="62" t="s">
+      <c r="E24" s="76" t="s">
         <v>216</v>
       </c>
-      <c r="F24" s="62" t="s">
-        <v>218</v>
+      <c r="F24" s="76" t="s">
+        <v>241</v>
       </c>
       <c r="G24" s="49" t="s">
         <v>1</v>
@@ -4696,7 +4836,7 @@
         <v>1</v>
       </c>
       <c r="L24" s="23" t="str">
-        <f t="shared" ref="L24:O24" si="41">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
+        <f t="shared" ref="L24:O28" si="41">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
         <v>De API</v>
       </c>
       <c r="M24" s="23" t="str">
@@ -4709,16 +4849,16 @@
       </c>
       <c r="O24" s="23" t="str">
         <f t="shared" si="41"/>
-        <v>API Revit</v>
+        <v>Função Auxiliar</v>
       </c>
       <c r="P24" s="24" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="Q24" s="24" t="s">
-        <v>220</v>
+        <v>243</v>
       </c>
       <c r="R24" s="24" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="S24" s="24" t="s">
         <v>1</v>
@@ -4731,7 +4871,7 @@
         <f t="shared" si="39"/>
         <v>Macros</v>
       </c>
-      <c r="V24" s="63" t="str">
+      <c r="V24" s="61" t="str">
         <f t="shared" si="39"/>
         <v>Métodos</v>
       </c>
@@ -4742,42 +4882,448 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-24</v>
       </c>
-      <c r="Y24" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="64" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="64" t="s">
+      <c r="Y24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="52">
+        <v>25</v>
+      </c>
+      <c r="B25" s="75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="D25" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="E25" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="F25" s="76" t="s">
+        <v>245</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>De API</v>
+      </c>
+      <c r="M25" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="N25" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O25" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P25" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q25" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="R25" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="S25" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T25" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>De API</v>
+      </c>
+      <c r="U25" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>Macros</v>
+      </c>
+      <c r="V25" s="61" t="str">
+        <f t="shared" si="39"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W25" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X25" s="51" t="str">
+        <f t="shared" si="34"/>
+        <v>Key-REQ-25</v>
+      </c>
+      <c r="Y25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="52">
+        <v>26</v>
+      </c>
+      <c r="B26" s="75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="D26" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="E26" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26" s="76" t="s">
+        <v>249</v>
+      </c>
+      <c r="G26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>De API</v>
+      </c>
+      <c r="M26" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="N26" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O26" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P26" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q26" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="R26" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="S26" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T26" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>De API</v>
+      </c>
+      <c r="U26" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>Macros</v>
+      </c>
+      <c r="V26" s="61" t="str">
+        <f t="shared" si="39"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W26" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X26" s="51" t="str">
+        <f t="shared" si="34"/>
+        <v>Key-REQ-26</v>
+      </c>
+      <c r="Y26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="52">
+        <v>27</v>
+      </c>
+      <c r="B27" s="75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="D27" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="E27" s="76" t="s">
+        <v>216</v>
+      </c>
+      <c r="F27" s="76" t="s">
+        <v>253</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>De API</v>
+      </c>
+      <c r="M27" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="N27" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Métodos</v>
+      </c>
+      <c r="O27" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P27" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q27" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="R27" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="S27" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T27" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>De API</v>
+      </c>
+      <c r="U27" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>Macros</v>
+      </c>
+      <c r="V27" s="61" t="str">
+        <f t="shared" si="39"/>
+        <v>Métodos</v>
+      </c>
+      <c r="W27" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X27" s="51" t="str">
+        <f t="shared" si="34"/>
+        <v>Key-REQ-27</v>
+      </c>
+      <c r="Y27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="24" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="52">
+        <v>28</v>
+      </c>
+      <c r="B28" s="75" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="76" t="s">
+        <v>215</v>
+      </c>
+      <c r="D28" s="76" t="s">
+        <v>217</v>
+      </c>
+      <c r="E28" s="76" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" s="76" t="s">
+        <v>258</v>
+      </c>
+      <c r="G28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L28" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>De API</v>
+      </c>
+      <c r="M28" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Macros</v>
+      </c>
+      <c r="N28" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="O28" s="23" t="str">
+        <f t="shared" si="41"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P28" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="Q28" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="R28" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="S28" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="T28" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>De API</v>
+      </c>
+      <c r="U28" s="24" t="str">
+        <f t="shared" si="39"/>
+        <v>Macros</v>
+      </c>
+      <c r="V28" s="61" t="str">
+        <f t="shared" si="39"/>
+        <v>Códigos Visuais</v>
+      </c>
+      <c r="W28" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="X28" s="51" t="str">
+        <f t="shared" si="34"/>
+        <v>Key-REQ-28</v>
+      </c>
+      <c r="Y28" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="62" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="24" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B24">
-    <cfRule type="cellIs" dxfId="27" priority="2" operator="equal">
+  <conditionalFormatting sqref="A2:B28">
+    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:C1 L1:Q1 S1:X1 AA1:XFD1 A25:C1048576 L25:X1048576 AA25:XFD1048576">
-    <cfRule type="cellIs" dxfId="26" priority="434" operator="equal">
+  <conditionalFormatting sqref="A1:C1 L1:Q1 S1:X1 AA1:XFD1 A29:C1048576 L29:X1048576 AA29:XFD1048576">
+    <cfRule type="cellIs" dxfId="27" priority="437" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F23 F25:F1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="11"/>
+  <conditionalFormatting sqref="E28:F28">
+    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24">
+  <conditionalFormatting sqref="F1:F23 F29:F1048576">
+    <cfRule type="duplicateValues" dxfId="25" priority="14"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F27">
     <cfRule type="duplicateValues" dxfId="24" priority="3"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R24">
-    <cfRule type="cellIs" dxfId="23" priority="1" operator="equal">
+  <conditionalFormatting sqref="R1:R23">
+    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4789,15 +5335,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{402BD1C2-A59C-4020-8FC9-E5402FE7B33F}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A1:U2"/>
-  <sheetFormatPr defaultColWidth="11.15234375" defaultRowHeight="7.95" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.140625" defaultRowHeight="7.9" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="2.3046875" style="1" customWidth="1"/>
-    <col min="2" max="10" width="5.15234375" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="21" width="5.53515625" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="11.15234375" style="5"/>
+    <col min="1" max="1" width="2.28515625" style="1" customWidth="1"/>
+    <col min="2" max="10" width="5.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="21" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="22" max="16384" width="11.140625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="20" t="s">
         <v>22</v>
       </c>
@@ -4862,7 +5408,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" ht="9" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="20">
         <v>2</v>
       </c>
@@ -4943,14 +5489,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
   <dimension ref="A1:D6"/>
-  <sheetFormatPr defaultColWidth="3.3828125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.69140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="12.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="18">
         <v>1</v>
       </c>
@@ -4964,7 +5510,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="12">
         <v>2</v>
       </c>
@@ -4978,7 +5524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="12">
         <v>3</v>
       </c>
@@ -4992,7 +5538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A4" s="12">
         <v>4</v>
       </c>
@@ -5006,13 +5552,13 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5"/>
       <c r="D5"/>
     </row>
-    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6"/>
@@ -5032,44 +5578,44 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC9BE003-A289-428E-9141-72F001D0AED0}">
   <sheetPr codeName="Planilha5"/>
   <dimension ref="A1:AG20"/>
-  <sheetFormatPr defaultColWidth="9.3046875" defaultRowHeight="7.4" customHeight="1" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.3828125" style="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.69140625" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.69140625" style="48" customWidth="1"/>
+    <col min="1" max="1" width="2.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.7109375" style="48" customWidth="1"/>
     <col min="4" max="4" width="8" style="48" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.69140625" style="48" customWidth="1"/>
-    <col min="6" max="6" width="4.3046875" style="48" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4.53515625" style="48" customWidth="1"/>
-    <col min="8" max="8" width="7.84375" style="48" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="48" customWidth="1"/>
+    <col min="6" max="6" width="4.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" style="48" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" style="48" customWidth="1"/>
     <col min="9" max="9" width="11" style="48" customWidth="1"/>
     <col min="10" max="10" width="6" style="48" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="46.3828125" style="48" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.3046875" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.69140625" style="48" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.3046875" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.84375" style="48" customWidth="1"/>
-    <col min="16" max="16" width="8.3828125" style="48" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.3828125" style="59" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.3828125" style="48" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="40.69140625" style="59" customWidth="1"/>
-    <col min="20" max="20" width="5.69140625" style="48" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.3046875" style="48" customWidth="1"/>
-    <col min="22" max="22" width="7.3046875" style="48" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.84375" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="3.84375" style="65" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.3046875" style="71" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.84375" style="71" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.3046875" style="71" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.84375" style="71" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.3046875" style="71" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.84375" style="71" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.3046875" style="71" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.84375" style="71" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.3046875" style="48"/>
+    <col min="11" max="11" width="46.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" style="48" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="40.7109375" style="59" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" style="48" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.28515625" style="48" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.85546875" style="59" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="3.85546875" style="63" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.28515625" style="48"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" ht="16.399999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:33" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="22">
         <v>1</v>
       </c>
@@ -5139,10 +5685,10 @@
       <c r="W1" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="X1" s="72" t="s">
+      <c r="X1" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="73" t="s">
+      <c r="Y1" s="71" t="s">
         <v>34</v>
       </c>
       <c r="Z1" s="38" t="s">
@@ -5170,14 +5716,14 @@
         <v>34</v>
       </c>
     </row>
-    <row r="2" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="30">
         <v>2</v>
       </c>
       <c r="B2" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="74" t="s">
+      <c r="C2" s="72" t="s">
         <v>74</v>
       </c>
       <c r="D2" s="47" t="s">
@@ -5271,14 +5817,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="30">
         <v>3</v>
       </c>
       <c r="B3" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="74" t="s">
+      <c r="C3" s="72" t="s">
         <v>174</v>
       </c>
       <c r="D3" s="47" t="s">
@@ -5372,14 +5918,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="30">
         <v>4</v>
       </c>
       <c r="B4" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="74" t="s">
+      <c r="C4" s="72" t="s">
         <v>174</v>
       </c>
       <c r="D4" s="47" t="s">
@@ -5473,14 +6019,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="30">
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="74" t="s">
+      <c r="C5" s="72" t="s">
         <v>174</v>
       </c>
       <c r="D5" s="47" t="s">
@@ -5574,14 +6120,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:33" customFormat="1" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:33" customFormat="1" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="30">
         <v>6</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="74" t="s">
+      <c r="C6" s="72" t="s">
         <v>174</v>
       </c>
       <c r="D6" s="47" t="s">
@@ -5675,14 +6221,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="30">
         <v>7</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="75" t="s">
+      <c r="C7" s="73" t="s">
         <v>178</v>
       </c>
       <c r="D7" s="47" t="s">
@@ -5776,14 +6322,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="30">
         <v>8</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="75" t="s">
+      <c r="C8" s="73" t="s">
         <v>178</v>
       </c>
       <c r="D8" s="47" t="s">
@@ -5877,14 +6423,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="30">
         <v>9</v>
       </c>
       <c r="B9" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="75" t="s">
+      <c r="C9" s="73" t="s">
         <v>178</v>
       </c>
       <c r="D9" s="47" t="s">
@@ -5978,14 +6524,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="30">
         <v>10</v>
       </c>
       <c r="B10" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="75" t="s">
+      <c r="C10" s="73" t="s">
         <v>178</v>
       </c>
       <c r="D10" s="47" t="s">
@@ -6079,14 +6625,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="30">
         <v>11</v>
       </c>
       <c r="B11" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="74" t="s">
+      <c r="C11" s="72" t="s">
         <v>193</v>
       </c>
       <c r="D11" s="47" t="s">
@@ -6180,14 +6726,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="30">
         <v>12</v>
       </c>
       <c r="B12" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="C12" s="74" t="s">
+      <c r="C12" s="72" t="s">
         <v>195</v>
       </c>
       <c r="D12" s="47" t="s">
@@ -6281,14 +6827,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="30">
         <v>13</v>
       </c>
       <c r="B13" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="74" t="s">
+      <c r="C13" s="72" t="s">
         <v>196</v>
       </c>
       <c r="D13" s="47" t="s">
@@ -6382,14 +6928,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="30">
         <v>14</v>
       </c>
       <c r="B14" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="C14" s="74" t="s">
+      <c r="C14" s="72" t="s">
         <v>194</v>
       </c>
       <c r="D14" s="47" t="s">
@@ -6483,14 +7029,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:33" ht="7.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:33" ht="7.35" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="30">
         <v>15</v>
       </c>
       <c r="B15" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C15" s="74" t="s">
+      <c r="C15" s="72" t="s">
         <v>197</v>
       </c>
       <c r="D15" s="47" t="s">
@@ -6584,58 +7130,58 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="30">
         <v>16</v>
       </c>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="64" t="s">
+        <v>218</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>253</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="66" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="L16" s="65" t="s">
+        <v>219</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="N16" s="65" t="s">
+        <v>221</v>
+      </c>
+      <c r="O16" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="C16" s="62" t="s">
-        <v>218</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="68" t="s">
-        <v>79</v>
-      </c>
-      <c r="K16" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="L16" s="67" t="s">
-        <v>223</v>
-      </c>
-      <c r="M16" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="N16" s="67" t="s">
-        <v>225</v>
-      </c>
-      <c r="O16" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="P16" s="69" t="str">
+      <c r="P16" s="67" t="str">
         <f t="shared" ref="P16:P20" si="0">IF(Q16="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="Q16" s="70" t="s">
-        <v>228</v>
+      <c r="Q16" s="68" t="s">
+        <v>224</v>
       </c>
       <c r="R16" s="36" t="s">
         <v>1</v>
@@ -6643,13 +7189,13 @@
       <c r="S16" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T16" s="67" t="s">
+      <c r="T16" s="65" t="s">
         <v>1</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V16" s="76" t="s">
+      <c r="V16" s="74" t="s">
         <v>1</v>
       </c>
       <c r="W16" s="25" t="s">
@@ -6686,15 +7232,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="30">
         <v>17</v>
       </c>
-      <c r="B17" s="66" t="s">
-        <v>229</v>
-      </c>
-      <c r="C17" s="62" t="s">
-        <v>218</v>
+      <c r="B17" s="64" t="s">
+        <v>225</v>
+      </c>
+      <c r="C17" s="76" t="s">
+        <v>253</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>1</v>
@@ -6714,30 +7260,30 @@
       <c r="I17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J17" s="68" t="s">
+      <c r="J17" s="66" t="s">
         <v>79</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="L17" s="67" t="s">
-        <v>223</v>
+        <v>227</v>
+      </c>
+      <c r="L17" s="65" t="s">
+        <v>219</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="N17" s="67" t="s">
-        <v>225</v>
+        <v>220</v>
+      </c>
+      <c r="N17" s="65" t="s">
+        <v>221</v>
       </c>
       <c r="O17" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="P17" s="69" t="str">
+        <v>226</v>
+      </c>
+      <c r="P17" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q17" s="70" t="s">
-        <v>232</v>
+      <c r="Q17" s="68" t="s">
+        <v>228</v>
       </c>
       <c r="R17" s="36" t="s">
         <v>1</v>
@@ -6745,13 +7291,13 @@
       <c r="S17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T17" s="67" t="s">
+      <c r="T17" s="65" t="s">
         <v>1</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V17" s="76" t="s">
+      <c r="V17" s="74" t="s">
         <v>1</v>
       </c>
       <c r="W17" s="25" t="s">
@@ -6788,15 +7334,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="30">
         <v>18</v>
       </c>
-      <c r="B18" s="66" t="s">
-        <v>233</v>
-      </c>
-      <c r="C18" s="62" t="s">
-        <v>218</v>
+      <c r="B18" s="64" t="s">
+        <v>229</v>
+      </c>
+      <c r="C18" s="76" t="s">
+        <v>253</v>
       </c>
       <c r="D18" s="47" t="s">
         <v>1</v>
@@ -6816,30 +7362,30 @@
       <c r="I18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J18" s="68" t="s">
+      <c r="J18" s="66" t="s">
         <v>79</v>
       </c>
       <c r="K18" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="L18" s="67" t="s">
-        <v>223</v>
+        <v>231</v>
+      </c>
+      <c r="L18" s="65" t="s">
+        <v>219</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="N18" s="67" t="s">
-        <v>225</v>
+        <v>220</v>
+      </c>
+      <c r="N18" s="65" t="s">
+        <v>221</v>
       </c>
       <c r="O18" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="P18" s="69" t="str">
+        <v>230</v>
+      </c>
+      <c r="P18" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q18" s="70" t="s">
-        <v>236</v>
+      <c r="Q18" s="68" t="s">
+        <v>232</v>
       </c>
       <c r="R18" s="36" t="s">
         <v>1</v>
@@ -6847,13 +7393,13 @@
       <c r="S18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T18" s="67" t="s">
+      <c r="T18" s="65" t="s">
         <v>1</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V18" s="76" t="s">
+      <c r="V18" s="74" t="s">
         <v>1</v>
       </c>
       <c r="W18" s="25" t="s">
@@ -6890,15 +7436,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="30">
         <v>19</v>
       </c>
-      <c r="B19" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="C19" s="62" t="s">
-        <v>218</v>
+      <c r="B19" s="64" t="s">
+        <v>233</v>
+      </c>
+      <c r="C19" s="76" t="s">
+        <v>253</v>
       </c>
       <c r="D19" s="47" t="s">
         <v>1</v>
@@ -6918,30 +7464,30 @@
       <c r="I19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J19" s="68" t="s">
+      <c r="J19" s="66" t="s">
         <v>79</v>
       </c>
       <c r="K19" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="L19" s="67" t="s">
-        <v>223</v>
+        <v>235</v>
+      </c>
+      <c r="L19" s="65" t="s">
+        <v>219</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="N19" s="67" t="s">
-        <v>225</v>
+        <v>220</v>
+      </c>
+      <c r="N19" s="65" t="s">
+        <v>221</v>
       </c>
       <c r="O19" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P19" s="69" t="str">
+        <v>234</v>
+      </c>
+      <c r="P19" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q19" s="70" t="s">
-        <v>240</v>
+      <c r="Q19" s="68" t="s">
+        <v>236</v>
       </c>
       <c r="R19" s="36" t="s">
         <v>1</v>
@@ -6949,13 +7495,13 @@
       <c r="S19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T19" s="67" t="s">
+      <c r="T19" s="65" t="s">
         <v>1</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V19" s="76" t="s">
+      <c r="V19" s="74" t="s">
         <v>1</v>
       </c>
       <c r="W19" s="25" t="s">
@@ -6992,15 +7538,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:33" s="71" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="30">
         <v>20</v>
       </c>
-      <c r="B20" s="66" t="s">
-        <v>241</v>
-      </c>
-      <c r="C20" s="62" t="s">
-        <v>218</v>
+      <c r="B20" s="64" t="s">
+        <v>237</v>
+      </c>
+      <c r="C20" s="76" t="s">
+        <v>253</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>1</v>
@@ -7020,30 +7566,30 @@
       <c r="I20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J20" s="68" t="s">
+      <c r="J20" s="66" t="s">
         <v>79</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="L20" s="67" t="s">
-        <v>223</v>
+        <v>239</v>
+      </c>
+      <c r="L20" s="65" t="s">
+        <v>219</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="N20" s="67" t="s">
-        <v>225</v>
+        <v>220</v>
+      </c>
+      <c r="N20" s="65" t="s">
+        <v>221</v>
       </c>
       <c r="O20" s="25" t="s">
-        <v>242</v>
-      </c>
-      <c r="P20" s="69" t="str">
+        <v>238</v>
+      </c>
+      <c r="P20" s="67" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q20" s="70" t="s">
-        <v>244</v>
+      <c r="Q20" s="68" t="s">
+        <v>240</v>
       </c>
       <c r="R20" s="36" t="s">
         <v>1</v>
@@ -7051,13 +7597,13 @@
       <c r="S20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T20" s="67" t="s">
+      <c r="T20" s="65" t="s">
         <v>1</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V20" s="76" t="s">
+      <c r="V20" s="74" t="s">
         <v>1</v>
       </c>
       <c r="W20" s="25" t="s">
@@ -7100,83 +7646,83 @@
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="B2:B6">
-    <cfRule type="duplicateValues" dxfId="20" priority="1988"/>
-    <cfRule type="duplicateValues" dxfId="19" priority="1989"/>
+    <cfRule type="duplicateValues" dxfId="20" priority="1989"/>
+    <cfRule type="duplicateValues" dxfId="19" priority="1990"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B7:B15 B1">
-    <cfRule type="duplicateValues" dxfId="18" priority="1984"/>
-    <cfRule type="duplicateValues" dxfId="17" priority="1985"/>
+    <cfRule type="duplicateValues" dxfId="18" priority="1985"/>
+    <cfRule type="duplicateValues" dxfId="17" priority="1986"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="B16:B20">
-    <cfRule type="duplicateValues" dxfId="16" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="15" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="16" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="15" priority="20"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:E20">
-    <cfRule type="cellIs" dxfId="14" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:AG1">
-    <cfRule type="cellIs" dxfId="13" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="13" priority="15" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:G14 A1:B15 D2 H3:W15 A16:A20">
-    <cfRule type="cellIs" dxfId="12" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="41" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F15:H15">
-    <cfRule type="cellIs" dxfId="11" priority="60" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="61" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F16:I20">
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F2:W2">
-    <cfRule type="cellIs" dxfId="9" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="38" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="G7:G10">
-    <cfRule type="duplicateValues" dxfId="8" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="22"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R16:W20">
-    <cfRule type="cellIs" dxfId="6" priority="17" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="18" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="X2:Y1048576">
-    <cfRule type="cellIs" dxfId="5" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="5" priority="3" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z1">
-    <cfRule type="cellIs" dxfId="4" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="14" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="Z2:AG20">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="4" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AB1">
-    <cfRule type="cellIs" dxfId="2" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AD1">
-    <cfRule type="cellIs" dxfId="1" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="12" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AF1">
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="11" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/Versão5/PRO/Ontologia_Requisitos.xlsx
+++ b/Versão5/PRO/Ontologia_Requisitos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{235B5ECB-2E94-4161-BC41-313197BA62E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB26850B-E4E6-4F2D-AF2A-2798A1E8DEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1396" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="265">
   <si>
     <t>Key</t>
   </si>
@@ -718,15 +718,6 @@
     <t>Classe IFC</t>
   </si>
   <si>
-    <t>De.API</t>
-  </si>
-  <si>
-    <t>Métodos</t>
-  </si>
-  <si>
-    <t>Macros</t>
-  </si>
-  <si>
     <t>API_Ambiente</t>
   </si>
   <si>
@@ -844,9 +835,6 @@
     <t>Define a Function to filter objects in an application</t>
   </si>
   <si>
-    <t>Códigos.Visuais</t>
-  </si>
-  <si>
     <t>Bloco.de.Código</t>
   </si>
   <si>
@@ -860,6 +848,24 @@
   </si>
   <si>
     <t>KML</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>API.Plataforma</t>
+  </si>
+  <si>
+    <t>API.Macros</t>
+  </si>
+  <si>
+    <t>API.Método</t>
+  </si>
+  <si>
+    <t>API.Macros.Visuais</t>
+  </si>
+  <si>
+    <t>API.Método.Visual</t>
   </si>
 </sst>
 </file>
@@ -994,7 +1000,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="30">
+  <fills count="28">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1016,12 +1022,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1163,12 +1163,6 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE89F"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1222,7 +1216,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1240,13 +1234,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1255,28 +1249,28 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1285,16 +1279,16 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1304,48 +1298,48 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="12" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="22" fontId="12" fillId="20" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="22" fontId="12" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1354,19 +1348,19 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1384,31 +1378,28 @@
     <xf numFmtId="22" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="26" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1417,37 +1408,46 @@
     <xf numFmtId="0" fontId="12" fillId="27" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="29">
+  <dxfs count="33">
     <dxf>
       <font>
         <b val="0"/>
@@ -1646,6 +1646,42 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i/>
+        <strike val="0"/>
+        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2222,7 +2258,7 @@
       </c>
       <c r="B18" s="40">
         <f ca="1">NOW()</f>
-        <v>46268.698654282409</v>
+        <v>46274.402743634259</v>
       </c>
       <c r="C18" s="45" t="s">
         <v>95</v>
@@ -2481,11 +2517,11 @@
   <sheetFormatPr defaultColWidth="32.140625" defaultRowHeight="6.6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.5703125" style="27" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" style="27" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" style="27" customWidth="1"/>
+    <col min="4" max="4" width="11.5703125" style="27" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" style="27" customWidth="1"/>
+    <col min="6" max="6" width="12.42578125" style="27" customWidth="1"/>
     <col min="7" max="11" width="10.140625" style="27" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.7109375" style="27" bestFit="1" customWidth="1"/>
@@ -2494,17 +2530,17 @@
     <col min="16" max="16" width="64.5703125" style="27" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="73.42578125" style="27" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="67.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="3.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="4.140625" style="78" customWidth="1"/>
     <col min="20" max="20" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.7109375" style="27" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.5703125" style="27" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="8.5703125" style="27" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="7.5703125" style="27" customWidth="1"/>
-    <col min="25" max="25" width="6.28515625" style="27" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="7.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="5.5703125" style="27" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="7.140625" style="27" customWidth="1"/>
+    <col min="26" max="26" width="8.28515625" style="27" customWidth="1"/>
+    <col min="27" max="27" width="6.5703125" style="27" customWidth="1"/>
     <col min="28" max="28" width="6.85546875" style="27" customWidth="1"/>
-    <col min="29" max="29" width="20.7109375" style="27" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="17.85546875" style="27" customWidth="1"/>
     <col min="30" max="30" width="4.140625" style="27" bestFit="1" customWidth="1"/>
     <col min="31" max="16384" width="32.140625" style="27"/>
   </cols>
@@ -2564,7 +2600,7 @@
       <c r="R1" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="S1" s="15" t="s">
+      <c r="S1" s="77" t="s">
         <v>71</v>
       </c>
       <c r="T1" s="15" t="s">
@@ -2598,26 +2634,26 @@
         <v>90</v>
       </c>
       <c r="AD1" s="15" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="52">
         <v>2</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="57" t="s">
+      <c r="C2" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D2" s="58" t="s">
+      <c r="D2" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F2" s="58" t="s">
+      <c r="F2" s="71" t="s">
         <v>174</v>
       </c>
       <c r="G2" s="49" t="s">
@@ -2660,7 +2696,7 @@
       <c r="R2" s="24" t="s">
         <v>200</v>
       </c>
-      <c r="S2" s="24" t="s">
+      <c r="S2" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T2" s="24" t="str">
@@ -2682,16 +2718,16 @@
         <f t="shared" ref="X2:X3" si="7">CONCATENATE("Key-REQ-",A2)</f>
         <v>Key-REQ-2</v>
       </c>
-      <c r="Y2" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="62" t="s">
+      <c r="Y2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC2" s="24" t="s">
@@ -2701,23 +2737,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="52">
         <v>3</v>
       </c>
-      <c r="B3" s="57" t="s">
+      <c r="B3" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="57" t="s">
+      <c r="C3" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="E3" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F3" s="58" t="s">
+      <c r="F3" s="71" t="s">
         <v>180</v>
       </c>
       <c r="G3" s="49" t="s">
@@ -2760,7 +2796,7 @@
       <c r="R3" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="S3" s="24" t="s">
+      <c r="S3" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T3" s="24" t="str">
@@ -2782,16 +2818,16 @@
         <f t="shared" si="7"/>
         <v>Key-REQ-3</v>
       </c>
-      <c r="Y3" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="62" t="s">
+      <c r="Y3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC3" s="24" t="s">
@@ -2801,23 +2837,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="52">
         <v>4</v>
       </c>
-      <c r="B4" s="57" t="s">
+      <c r="B4" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="57" t="s">
+      <c r="C4" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D4" s="58" t="s">
+      <c r="D4" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E4" s="58" t="s">
+      <c r="E4" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F4" s="58" t="s">
+      <c r="F4" s="71" t="s">
         <v>151</v>
       </c>
       <c r="G4" s="49" t="s">
@@ -2860,7 +2896,7 @@
       <c r="R4" s="24" t="s">
         <v>201</v>
       </c>
-      <c r="S4" s="24" t="s">
+      <c r="S4" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T4" s="24" t="str">
@@ -2882,16 +2918,16 @@
         <f t="shared" ref="X4:X18" si="11">CONCATENATE("Key-REQ-",A4)</f>
         <v>Key-REQ-4</v>
       </c>
-      <c r="Y4" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="62" t="s">
+      <c r="Y4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC4" s="24" t="s">
@@ -2901,23 +2937,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="52">
         <v>5</v>
       </c>
-      <c r="B5" s="57" t="s">
+      <c r="B5" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C5" s="57" t="s">
+      <c r="C5" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D5" s="58" t="s">
+      <c r="D5" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="58" t="s">
+      <c r="E5" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="F5" s="71" t="s">
         <v>152</v>
       </c>
       <c r="G5" s="49" t="s">
@@ -2960,7 +2996,7 @@
       <c r="R5" s="24" t="s">
         <v>202</v>
       </c>
-      <c r="S5" s="24" t="s">
+      <c r="S5" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T5" s="24" t="str">
@@ -2982,16 +3018,16 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-5</v>
       </c>
-      <c r="Y5" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="62" t="s">
+      <c r="Y5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC5" s="24" t="s">
@@ -3001,23 +3037,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="52">
         <v>6</v>
       </c>
-      <c r="B6" s="57" t="s">
+      <c r="B6" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C6" s="57" t="s">
+      <c r="C6" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D6" s="58" t="s">
+      <c r="D6" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="E6" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="F6" s="71" t="s">
         <v>153</v>
       </c>
       <c r="G6" s="49" t="s">
@@ -3060,7 +3096,7 @@
       <c r="R6" s="24" t="s">
         <v>203</v>
       </c>
-      <c r="S6" s="24" t="s">
+      <c r="S6" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T6" s="24" t="str">
@@ -3082,16 +3118,16 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-6</v>
       </c>
-      <c r="Y6" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="62" t="s">
+      <c r="Y6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC6" s="24" t="s">
@@ -3101,23 +3137,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="52">
         <v>7</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="57" t="s">
+      <c r="C7" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D7" s="58" t="s">
+      <c r="D7" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E7" s="58" t="s">
+      <c r="E7" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F7" s="58" t="s">
+      <c r="F7" s="71" t="s">
         <v>187</v>
       </c>
       <c r="G7" s="49" t="s">
@@ -3160,7 +3196,7 @@
       <c r="R7" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="S7" s="24" t="s">
+      <c r="S7" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T7" s="24" t="str">
@@ -3182,16 +3218,16 @@
         <f t="shared" ref="X7:X11" si="19">CONCATENATE("Key-REQ-",A7)</f>
         <v>Key-REQ-7</v>
       </c>
-      <c r="Y7" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="62" t="s">
+      <c r="Y7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC7" s="24" t="s">
@@ -3201,23 +3237,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="52">
         <v>8</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C8" s="57" t="s">
+      <c r="C8" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D8" s="58" t="s">
+      <c r="D8" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E8" s="58" t="s">
+      <c r="E8" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F8" s="58" t="s">
+      <c r="F8" s="71" t="s">
         <v>188</v>
       </c>
       <c r="G8" s="49" t="s">
@@ -3260,7 +3296,7 @@
       <c r="R8" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="S8" s="24" t="s">
+      <c r="S8" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T8" s="24" t="str">
@@ -3282,16 +3318,16 @@
         <f t="shared" si="19"/>
         <v>Key-REQ-8</v>
       </c>
-      <c r="Y8" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="62" t="s">
+      <c r="Y8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC8" s="24" t="s">
@@ -3301,23 +3337,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="52">
         <v>9</v>
       </c>
-      <c r="B9" s="57" t="s">
+      <c r="B9" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C9" s="57" t="s">
+      <c r="C9" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D9" s="58" t="s">
+      <c r="D9" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="58" t="s">
+      <c r="E9" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F9" s="58" t="s">
+      <c r="F9" s="71" t="s">
         <v>189</v>
       </c>
       <c r="G9" s="49" t="s">
@@ -3360,7 +3396,7 @@
       <c r="R9" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="S9" s="24" t="s">
+      <c r="S9" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T9" s="24" t="str">
@@ -3382,16 +3418,16 @@
         <f t="shared" si="19"/>
         <v>Key-REQ-9</v>
       </c>
-      <c r="Y9" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="62" t="s">
+      <c r="Y9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC9" s="24" t="s">
@@ -3401,23 +3437,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="52">
         <v>10</v>
       </c>
-      <c r="B10" s="57" t="s">
+      <c r="B10" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C10" s="57" t="s">
+      <c r="C10" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E10" s="58" t="s">
+      <c r="E10" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="71" t="s">
         <v>190</v>
       </c>
       <c r="G10" s="49" t="s">
@@ -3460,7 +3496,7 @@
       <c r="R10" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="S10" s="24" t="s">
+      <c r="S10" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="24" t="str">
@@ -3482,16 +3518,16 @@
         <f t="shared" si="19"/>
         <v>Key-REQ-10</v>
       </c>
-      <c r="Y10" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="62" t="s">
+      <c r="Y10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC10" s="24" t="s">
@@ -3501,23 +3537,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="52">
         <v>11</v>
       </c>
-      <c r="B11" s="57" t="s">
+      <c r="B11" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C11" s="57" t="s">
+      <c r="C11" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D11" s="58" t="s">
+      <c r="D11" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E11" s="58" t="s">
+      <c r="E11" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F11" s="58" t="s">
+      <c r="F11" s="71" t="s">
         <v>191</v>
       </c>
       <c r="G11" s="49" t="s">
@@ -3560,7 +3596,7 @@
       <c r="R11" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="S11" s="24" t="s">
+      <c r="S11" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T11" s="24" t="str">
@@ -3582,16 +3618,16 @@
         <f t="shared" si="19"/>
         <v>Key-REQ-11</v>
       </c>
-      <c r="Y11" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="62" t="s">
+      <c r="Y11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC11" s="24" t="s">
@@ -3601,23 +3637,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="52">
         <v>12</v>
       </c>
-      <c r="B12" s="57" t="s">
+      <c r="B12" s="75" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="57" t="s">
+      <c r="C12" s="75" t="s">
         <v>175</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="D12" s="71" t="s">
         <v>128</v>
       </c>
-      <c r="E12" s="58" t="s">
+      <c r="E12" s="71" t="s">
         <v>176</v>
       </c>
-      <c r="F12" s="58" t="s">
+      <c r="F12" s="71" t="s">
         <v>192</v>
       </c>
       <c r="G12" s="49" t="s">
@@ -3660,7 +3696,7 @@
       <c r="R12" s="24" t="s">
         <v>204</v>
       </c>
-      <c r="S12" s="24" t="s">
+      <c r="S12" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T12" s="24" t="str">
@@ -3682,16 +3718,16 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-12</v>
       </c>
-      <c r="Y12" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="62" t="s">
+      <c r="Y12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC12" s="24" t="s">
@@ -3701,23 +3737,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="52">
         <v>13</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C13" s="57" t="s">
+      <c r="C13" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D13" s="58" t="s">
+      <c r="D13" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E13" s="58" t="s">
+      <c r="E13" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F13" s="58" t="s">
+      <c r="F13" s="71" t="s">
         <v>178</v>
       </c>
       <c r="G13" s="49" t="s">
@@ -3760,7 +3796,7 @@
       <c r="R13" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S13" s="24" t="s">
+      <c r="S13" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T13" s="24" t="str">
@@ -3782,16 +3818,16 @@
         <f t="shared" ref="X13:X14" si="20">CONCATENATE("Key-REQ-",A13)</f>
         <v>Key-REQ-13</v>
       </c>
-      <c r="Y13" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="62" t="s">
+      <c r="Y13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC13" s="24" t="s">
@@ -3801,23 +3837,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="52">
         <v>14</v>
       </c>
-      <c r="B14" s="57" t="s">
+      <c r="B14" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="57" t="s">
+      <c r="C14" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D14" s="58" t="s">
+      <c r="D14" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E14" s="58" t="s">
+      <c r="E14" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F14" s="58" t="s">
+      <c r="F14" s="71" t="s">
         <v>179</v>
       </c>
       <c r="G14" s="49" t="s">
@@ -3860,7 +3896,7 @@
       <c r="R14" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S14" s="24" t="s">
+      <c r="S14" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T14" s="24" t="str">
@@ -3882,16 +3918,16 @@
         <f t="shared" si="20"/>
         <v>Key-REQ-14</v>
       </c>
-      <c r="Y14" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="62" t="s">
+      <c r="Y14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC14" s="24" t="s">
@@ -3901,23 +3937,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="52">
         <v>15</v>
       </c>
-      <c r="B15" s="57" t="s">
+      <c r="B15" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="57" t="s">
+      <c r="C15" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D15" s="58" t="s">
+      <c r="D15" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E15" s="58" t="s">
+      <c r="E15" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F15" s="58" t="s">
+      <c r="F15" s="71" t="s">
         <v>129</v>
       </c>
       <c r="G15" s="49" t="s">
@@ -3960,7 +3996,7 @@
       <c r="R15" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S15" s="24" t="s">
+      <c r="S15" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T15" s="24" t="str">
@@ -3982,16 +4018,16 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-15</v>
       </c>
-      <c r="Y15" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="62" t="s">
+      <c r="Y15" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC15" s="24" t="s">
@@ -4001,23 +4037,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="52">
         <v>16</v>
       </c>
-      <c r="B16" s="57" t="s">
+      <c r="B16" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C16" s="57" t="s">
+      <c r="C16" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D16" s="58" t="s">
+      <c r="D16" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E16" s="58" t="s">
+      <c r="E16" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F16" s="58" t="s">
+      <c r="F16" s="71" t="s">
         <v>130</v>
       </c>
       <c r="G16" s="49" t="s">
@@ -4060,7 +4096,7 @@
       <c r="R16" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S16" s="24" t="s">
+      <c r="S16" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T16" s="24" t="str">
@@ -4082,16 +4118,16 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-16</v>
       </c>
-      <c r="Y16" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="62" t="s">
+      <c r="Y16" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC16" s="24" t="s">
@@ -4101,23 +4137,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="52">
         <v>17</v>
       </c>
-      <c r="B17" s="57" t="s">
+      <c r="B17" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C17" s="57" t="s">
+      <c r="C17" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D17" s="58" t="s">
+      <c r="D17" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E17" s="58" t="s">
+      <c r="E17" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F17" s="58" t="s">
+      <c r="F17" s="71" t="s">
         <v>131</v>
       </c>
       <c r="G17" s="49" t="s">
@@ -4160,7 +4196,7 @@
       <c r="R17" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S17" s="24" t="s">
+      <c r="S17" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T17" s="24" t="str">
@@ -4182,16 +4218,16 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-17</v>
       </c>
-      <c r="Y17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="62" t="s">
+      <c r="Y17" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC17" s="24" t="s">
@@ -4201,23 +4237,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="52">
         <v>18</v>
       </c>
-      <c r="B18" s="57" t="s">
+      <c r="B18" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C18" s="57" t="s">
+      <c r="C18" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="58" t="s">
+      <c r="D18" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E18" s="58" t="s">
+      <c r="E18" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F18" s="58" t="s">
+      <c r="F18" s="71" t="s">
         <v>193</v>
       </c>
       <c r="G18" s="49" t="s">
@@ -4260,7 +4296,7 @@
       <c r="R18" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S18" s="24" t="s">
+      <c r="S18" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T18" s="24" t="str">
@@ -4282,16 +4318,16 @@
         <f t="shared" si="11"/>
         <v>Key-REQ-18</v>
       </c>
-      <c r="Y18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="62" t="s">
+      <c r="Y18" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC18" s="24" t="s">
@@ -4301,23 +4337,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="52">
         <v>19</v>
       </c>
-      <c r="B19" s="57" t="s">
+      <c r="B19" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C19" s="57" t="s">
+      <c r="C19" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D19" s="58" t="s">
+      <c r="D19" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E19" s="58" t="s">
+      <c r="E19" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F19" s="58" t="s">
+      <c r="F19" s="71" t="s">
         <v>195</v>
       </c>
       <c r="G19" s="49" t="s">
@@ -4360,7 +4396,7 @@
       <c r="R19" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S19" s="24" t="s">
+      <c r="S19" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T19" s="24" t="str">
@@ -4382,16 +4418,16 @@
         <f t="shared" ref="X19:X28" si="34">CONCATENATE("Key-REQ-",A19)</f>
         <v>Key-REQ-19</v>
       </c>
-      <c r="Y19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="62" t="s">
+      <c r="Y19" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC19" s="24" t="s">
@@ -4401,23 +4437,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="52">
         <v>20</v>
       </c>
-      <c r="B20" s="57" t="s">
+      <c r="B20" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C20" s="57" t="s">
+      <c r="C20" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D20" s="58" t="s">
+      <c r="D20" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E20" s="58" t="s">
+      <c r="E20" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F20" s="58" t="s">
+      <c r="F20" s="71" t="s">
         <v>196</v>
       </c>
       <c r="G20" s="49" t="s">
@@ -4460,7 +4496,7 @@
       <c r="R20" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S20" s="24" t="s">
+      <c r="S20" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T20" s="24" t="str">
@@ -4482,16 +4518,16 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-20</v>
       </c>
-      <c r="Y20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="62" t="s">
+      <c r="Y20" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC20" s="24" t="s">
@@ -4501,23 +4537,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="52">
         <v>21</v>
       </c>
-      <c r="B21" s="57" t="s">
+      <c r="B21" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C21" s="57" t="s">
+      <c r="C21" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D21" s="58" t="s">
+      <c r="D21" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E21" s="58" t="s">
+      <c r="E21" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F21" s="58" t="s">
+      <c r="F21" s="71" t="s">
         <v>194</v>
       </c>
       <c r="G21" s="49" t="s">
@@ -4560,7 +4596,7 @@
       <c r="R21" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S21" s="24" t="s">
+      <c r="S21" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T21" s="24" t="str">
@@ -4582,16 +4618,16 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-21</v>
       </c>
-      <c r="Y21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="62" t="s">
+      <c r="Y21" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC21" s="24" t="s">
@@ -4601,23 +4637,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="52">
         <v>22</v>
       </c>
-      <c r="B22" s="57" t="s">
+      <c r="B22" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C22" s="57" t="s">
+      <c r="C22" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D22" s="58" t="s">
+      <c r="D22" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E22" s="58" t="s">
+      <c r="E22" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F22" s="58" t="s">
+      <c r="F22" s="71" t="s">
         <v>197</v>
       </c>
       <c r="G22" s="49" t="s">
@@ -4636,7 +4672,7 @@
         <v>1</v>
       </c>
       <c r="L22" s="23" t="str">
-        <f t="shared" ref="L22:L23" si="35">CONCATENATE("", C22)</f>
+        <f t="shared" ref="L22:M28" si="35">CONCATENATE("", C22)</f>
         <v>De.Necessidades</v>
       </c>
       <c r="M22" s="23" t="str">
@@ -4644,7 +4680,7 @@
         <v>Necessidades.Projetuais</v>
       </c>
       <c r="N22" s="23" t="str">
-        <f t="shared" ref="N22:N23" si="37">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E22),"."," ")," De "," de "))</f>
+        <f t="shared" ref="N22:O28" si="37">(SUBSTITUTE(SUBSTITUTE(CONCATENATE("",E22),"."," ")," De "," de "))</f>
         <v>Atendidas</v>
       </c>
       <c r="O22" s="23" t="str">
@@ -4660,7 +4696,7 @@
       <c r="R22" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S22" s="24" t="s">
+      <c r="S22" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T22" s="24" t="str">
@@ -4682,16 +4718,16 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-22</v>
       </c>
-      <c r="Y22" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="62" t="s">
+      <c r="Y22" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC22" s="24" t="s">
@@ -4701,23 +4737,23 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:30" s="59" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="52">
         <v>23</v>
       </c>
-      <c r="B23" s="57" t="s">
+      <c r="B23" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C23" s="57" t="s">
+      <c r="C23" s="75" t="s">
         <v>173</v>
       </c>
-      <c r="D23" s="58" t="s">
+      <c r="D23" s="71" t="s">
         <v>135</v>
       </c>
-      <c r="E23" s="58" t="s">
+      <c r="E23" s="71" t="s">
         <v>177</v>
       </c>
-      <c r="F23" s="58" t="s">
+      <c r="F23" s="71" t="s">
         <v>198</v>
       </c>
       <c r="G23" s="49" t="s">
@@ -4760,7 +4796,7 @@
       <c r="R23" s="24" t="s">
         <v>205</v>
       </c>
-      <c r="S23" s="24" t="s">
+      <c r="S23" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T23" s="24" t="str">
@@ -4782,16 +4818,16 @@
         <f t="shared" si="34"/>
         <v>Key-REQ-23</v>
       </c>
-      <c r="Y23" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="62" t="s">
+      <c r="Y23" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AC23" s="24" t="s">
@@ -4801,531 +4837,529 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="52">
         <v>24</v>
       </c>
       <c r="B24" s="75" t="s">
-        <v>74</v>
+        <v>259</v>
       </c>
       <c r="C24" s="76" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="D24" s="76" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="E24" s="76" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F24" s="76" t="s">
+        <v>238</v>
+      </c>
+      <c r="G24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L24" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M24" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N24" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>API Método</v>
+      </c>
+      <c r="O24" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>Função Auxiliar</v>
+      </c>
+      <c r="P24" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q24" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="R24" s="24" t="s">
         <v>241</v>
       </c>
-      <c r="G24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L24" s="23" t="str">
-        <f t="shared" ref="L24:O28" si="41">SUBSTITUTE(CONCATENATE("", C24), ".", " ")</f>
-        <v>De API</v>
-      </c>
-      <c r="M24" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N24" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O24" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Função Auxiliar</v>
-      </c>
-      <c r="P24" s="24" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q24" s="24" t="s">
-        <v>243</v>
-      </c>
-      <c r="R24" s="24" t="s">
-        <v>244</v>
-      </c>
-      <c r="S24" s="24" t="s">
+      <c r="S24" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T24" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U24" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>Macros</v>
-      </c>
-      <c r="V24" s="61" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V24" s="59" t="str">
         <f t="shared" si="39"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W24" s="24" t="s">
         <v>133</v>
       </c>
       <c r="X24" s="51" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" ref="X24:X28" si="41">CONCATENATE("Key-REQ-",A24)</f>
         <v>Key-REQ-24</v>
       </c>
-      <c r="Y24" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD24" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y24" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="52">
         <v>25</v>
       </c>
       <c r="B25" s="75" t="s">
-        <v>74</v>
+        <v>259</v>
       </c>
       <c r="C25" s="76" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="D25" s="76" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="E25" s="76" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F25" s="76" t="s">
+        <v>242</v>
+      </c>
+      <c r="G25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L25" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M25" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N25" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>API Método</v>
+      </c>
+      <c r="O25" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>Função Global</v>
+      </c>
+      <c r="P25" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="Q25" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="R25" s="24" t="s">
         <v>245</v>
       </c>
-      <c r="G25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L25" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>De API</v>
-      </c>
-      <c r="M25" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N25" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O25" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Função Global</v>
-      </c>
-      <c r="P25" s="24" t="s">
-        <v>246</v>
-      </c>
-      <c r="Q25" s="24" t="s">
-        <v>247</v>
-      </c>
-      <c r="R25" s="24" t="s">
-        <v>248</v>
-      </c>
-      <c r="S25" s="24" t="s">
+      <c r="S25" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T25" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U25" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>Macros</v>
-      </c>
-      <c r="V25" s="61" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V25" s="59" t="str">
         <f t="shared" si="39"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W25" s="24" t="s">
         <v>133</v>
       </c>
       <c r="X25" s="51" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v>Key-REQ-25</v>
       </c>
-      <c r="Y25" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD25" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y25" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="52">
         <v>26</v>
       </c>
       <c r="B26" s="75" t="s">
-        <v>74</v>
+        <v>259</v>
       </c>
       <c r="C26" s="76" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="D26" s="76" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="E26" s="76" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F26" s="76" t="s">
+        <v>246</v>
+      </c>
+      <c r="G26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L26" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M26" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N26" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>API Método</v>
+      </c>
+      <c r="O26" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>Função Local</v>
+      </c>
+      <c r="P26" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="Q26" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="R26" s="24" t="s">
         <v>249</v>
       </c>
-      <c r="G26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L26" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>De API</v>
-      </c>
-      <c r="M26" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N26" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O26" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Função Local</v>
-      </c>
-      <c r="P26" s="24" t="s">
-        <v>250</v>
-      </c>
-      <c r="Q26" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="R26" s="24" t="s">
-        <v>252</v>
-      </c>
-      <c r="S26" s="24" t="s">
+      <c r="S26" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U26" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>Macros</v>
-      </c>
-      <c r="V26" s="61" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V26" s="59" t="str">
         <f t="shared" si="39"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W26" s="24" t="s">
         <v>133</v>
       </c>
       <c r="X26" s="51" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v>Key-REQ-26</v>
       </c>
-      <c r="Y26" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD26" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y26" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="52">
         <v>27</v>
       </c>
       <c r="B27" s="75" t="s">
-        <v>74</v>
+        <v>259</v>
       </c>
       <c r="C27" s="76" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="D27" s="76" t="s">
-        <v>217</v>
+        <v>261</v>
       </c>
       <c r="E27" s="76" t="s">
-        <v>216</v>
+        <v>262</v>
       </c>
       <c r="F27" s="76" t="s">
+        <v>250</v>
+      </c>
+      <c r="G27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L27" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M27" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Macros</v>
+      </c>
+      <c r="N27" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>API Método</v>
+      </c>
+      <c r="O27" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>Função Filtro</v>
+      </c>
+      <c r="P27" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="Q27" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="R27" s="24" t="s">
         <v>253</v>
       </c>
-      <c r="G27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L27" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>De API</v>
-      </c>
-      <c r="M27" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N27" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Métodos</v>
-      </c>
-      <c r="O27" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Função Filtro</v>
-      </c>
-      <c r="P27" s="24" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q27" s="24" t="s">
-        <v>255</v>
-      </c>
-      <c r="R27" s="24" t="s">
-        <v>256</v>
-      </c>
-      <c r="S27" s="24" t="s">
+      <c r="S27" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T27" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U27" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>Macros</v>
-      </c>
-      <c r="V27" s="61" t="str">
+        <v>API Macros</v>
+      </c>
+      <c r="V27" s="59" t="str">
         <f t="shared" si="39"/>
-        <v>Métodos</v>
+        <v>API Método</v>
       </c>
       <c r="W27" s="24" t="s">
         <v>133</v>
       </c>
       <c r="X27" s="51" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v>Key-REQ-27</v>
       </c>
-      <c r="Y27" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD27" s="24" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" s="63" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="Y27" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="60" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="52">
         <v>28</v>
       </c>
       <c r="B28" s="75" t="s">
-        <v>74</v>
+        <v>259</v>
       </c>
       <c r="C28" s="76" t="s">
-        <v>215</v>
+        <v>260</v>
       </c>
       <c r="D28" s="76" t="s">
-        <v>217</v>
+        <v>263</v>
       </c>
       <c r="E28" s="76" t="s">
+        <v>264</v>
+      </c>
+      <c r="F28" s="76" t="s">
+        <v>254</v>
+      </c>
+      <c r="G28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="K28" s="49" t="s">
+        <v>1</v>
+      </c>
+      <c r="L28" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Plataforma</v>
+      </c>
+      <c r="M28" s="23" t="str">
+        <f t="shared" si="35"/>
+        <v>API.Macros.Visuais</v>
+      </c>
+      <c r="N28" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>API Método Visual</v>
+      </c>
+      <c r="O28" s="23" t="str">
+        <f t="shared" si="37"/>
+        <v>Bloco de Código</v>
+      </c>
+      <c r="P28" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q28" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="R28" s="24" t="s">
         <v>257</v>
       </c>
-      <c r="F28" s="76" t="s">
-        <v>258</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="L28" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>De API</v>
-      </c>
-      <c r="M28" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Macros</v>
-      </c>
-      <c r="N28" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Códigos Visuais</v>
-      </c>
-      <c r="O28" s="23" t="str">
-        <f t="shared" si="41"/>
-        <v>Bloco de Código</v>
-      </c>
-      <c r="P28" s="24" t="s">
-        <v>259</v>
-      </c>
-      <c r="Q28" s="24" t="s">
-        <v>260</v>
-      </c>
-      <c r="R28" s="24" t="s">
-        <v>261</v>
-      </c>
-      <c r="S28" s="24" t="s">
+      <c r="S28" s="73" t="s">
         <v>1</v>
       </c>
       <c r="T28" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>De API</v>
+        <v>API Plataforma</v>
       </c>
       <c r="U28" s="24" t="str">
         <f t="shared" si="39"/>
-        <v>Macros</v>
-      </c>
-      <c r="V28" s="61" t="str">
+        <v>API Macros Visuais</v>
+      </c>
+      <c r="V28" s="59" t="str">
         <f t="shared" si="39"/>
-        <v>Códigos Visuais</v>
+        <v>API Método Visual</v>
       </c>
       <c r="W28" s="24" t="s">
         <v>133</v>
       </c>
       <c r="X28" s="51" t="str">
-        <f t="shared" si="34"/>
+        <f t="shared" si="41"/>
         <v>Key-REQ-28</v>
       </c>
-      <c r="Y28" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="62" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD28" s="24" t="s">
+      <c r="Y28" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="60" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="60" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <conditionalFormatting sqref="A2:B28">
-    <cfRule type="cellIs" dxfId="28" priority="1" operator="equal">
+  <conditionalFormatting sqref="A2:B23 A24:A28">
+    <cfRule type="cellIs" dxfId="32" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:C1 L1:Q1 S1:X1 AA1:XFD1 A29:C1048576 L29:X1048576 AA29:XFD1048576">
-    <cfRule type="cellIs" dxfId="27" priority="437" operator="equal">
+    <cfRule type="cellIs" dxfId="31" priority="441" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E28:F28">
-    <cfRule type="duplicateValues" dxfId="26" priority="2"/>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23 F29:F1048576">
-    <cfRule type="duplicateValues" dxfId="25" priority="14"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F24:F27">
-    <cfRule type="duplicateValues" dxfId="24" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="29" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="23" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
       <formula>"null"</formula>
     </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F24:F28">
+    <cfRule type="duplicateValues" dxfId="25" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="24" priority="2"/>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5488,12 +5522,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7BFE13-E93E-488C-9C8F-4E4982DFBAE7}">
   <sheetPr codeName="Planilha4"/>
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultColWidth="3.42578125" defaultRowHeight="6" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5703125" customWidth="1"/>
+    <col min="3" max="3" width="8" customWidth="1"/>
+    <col min="4" max="4" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
@@ -5524,48 +5559,20 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="12">
-        <v>3</v>
-      </c>
-      <c r="B3" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="35" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="12">
-        <v>4</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="35" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="35" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5"/>
-      <c r="D5"/>
-    </row>
-    <row r="6" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6"/>
-      <c r="D6"/>
+    <row r="3" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3"/>
+      <c r="B3"/>
+      <c r="C3"/>
+      <c r="D3"/>
+    </row>
+    <row r="4" spans="1:4" s="28" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4"/>
+      <c r="B4"/>
+      <c r="C4"/>
+      <c r="D4"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:A4">
+  <conditionalFormatting sqref="A1:A2">
     <cfRule type="cellIs" dxfId="21" priority="32" operator="equal">
       <formula>"null"</formula>
     </cfRule>
@@ -5582,10 +5589,10 @@
   <cols>
     <col min="1" max="1" width="2.42578125" style="48" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" style="48" customWidth="1"/>
-    <col min="4" max="4" width="8" style="48" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="48" customWidth="1"/>
+    <col min="4" max="4" width="7" style="48" customWidth="1"/>
     <col min="5" max="5" width="4.7109375" style="48" customWidth="1"/>
-    <col min="6" max="6" width="4.28515625" style="48" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="3.42578125" style="48" customWidth="1"/>
     <col min="7" max="7" width="4.5703125" style="48" customWidth="1"/>
     <col min="8" max="8" width="7.85546875" style="48" customWidth="1"/>
     <col min="9" max="9" width="11" style="48" customWidth="1"/>
@@ -5596,22 +5603,22 @@
     <col min="14" max="14" width="5.28515625" style="48" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.85546875" style="48" customWidth="1"/>
     <col min="16" max="16" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.42578125" style="59" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" style="57" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="40.7109375" style="59" customWidth="1"/>
+    <col min="19" max="19" width="40.7109375" style="57" customWidth="1"/>
     <col min="20" max="20" width="5.7109375" style="48" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="15.28515625" style="48" customWidth="1"/>
     <col min="22" max="22" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.85546875" style="59" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="3.85546875" style="63" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="69" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="69" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.85546875" style="57" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="3.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="67" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" style="67" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" style="67" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="67" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
     <col min="34" max="16384" width="9.28515625" style="48"/>
   </cols>
   <sheetData>
@@ -5685,10 +5692,10 @@
       <c r="W1" s="43" t="s">
         <v>73</v>
       </c>
-      <c r="X1" s="70" t="s">
+      <c r="X1" s="68" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="71" t="s">
+      <c r="Y1" s="69" t="s">
         <v>34</v>
       </c>
       <c r="Z1" s="38" t="s">
@@ -5723,7 +5730,7 @@
       <c r="B2" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="C2" s="72" t="s">
+      <c r="C2" s="70" t="s">
         <v>74</v>
       </c>
       <c r="D2" s="47" t="s">
@@ -5824,7 +5831,7 @@
       <c r="B3" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="72" t="s">
+      <c r="C3" s="70" t="s">
         <v>174</v>
       </c>
       <c r="D3" s="47" t="s">
@@ -5925,7 +5932,7 @@
       <c r="B4" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="C4" s="72" t="s">
+      <c r="C4" s="70" t="s">
         <v>174</v>
       </c>
       <c r="D4" s="47" t="s">
@@ -6026,7 +6033,7 @@
       <c r="B5" s="32" t="s">
         <v>147</v>
       </c>
-      <c r="C5" s="72" t="s">
+      <c r="C5" s="70" t="s">
         <v>174</v>
       </c>
       <c r="D5" s="47" t="s">
@@ -6127,7 +6134,7 @@
       <c r="B6" s="32" t="s">
         <v>148</v>
       </c>
-      <c r="C6" s="72" t="s">
+      <c r="C6" s="70" t="s">
         <v>174</v>
       </c>
       <c r="D6" s="47" t="s">
@@ -6228,7 +6235,7 @@
       <c r="B7" s="32" t="s">
         <v>168</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="71" t="s">
         <v>178</v>
       </c>
       <c r="D7" s="47" t="s">
@@ -6240,7 +6247,7 @@
       <c r="F7" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="G7" s="60" t="s">
+      <c r="G7" s="58" t="s">
         <v>145</v>
       </c>
       <c r="H7" s="36" t="s">
@@ -6329,7 +6336,7 @@
       <c r="B8" s="32" t="s">
         <v>169</v>
       </c>
-      <c r="C8" s="73" t="s">
+      <c r="C8" s="71" t="s">
         <v>178</v>
       </c>
       <c r="D8" s="47" t="s">
@@ -6341,7 +6348,7 @@
       <c r="F8" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="G8" s="60" t="s">
+      <c r="G8" s="58" t="s">
         <v>146</v>
       </c>
       <c r="H8" s="36" t="s">
@@ -6430,7 +6437,7 @@
       <c r="B9" s="32" t="s">
         <v>170</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="71" t="s">
         <v>178</v>
       </c>
       <c r="D9" s="47" t="s">
@@ -6442,7 +6449,7 @@
       <c r="F9" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="G9" s="60" t="s">
+      <c r="G9" s="58" t="s">
         <v>147</v>
       </c>
       <c r="H9" s="36" t="s">
@@ -6531,7 +6538,7 @@
       <c r="B10" s="32" t="s">
         <v>171</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="71" t="s">
         <v>178</v>
       </c>
       <c r="D10" s="47" t="s">
@@ -6543,7 +6550,7 @@
       <c r="F10" s="47" t="s">
         <v>199</v>
       </c>
-      <c r="G10" s="60" t="s">
+      <c r="G10" s="58" t="s">
         <v>148</v>
       </c>
       <c r="H10" s="36" t="s">
@@ -6632,7 +6639,7 @@
       <c r="B11" s="32" t="s">
         <v>157</v>
       </c>
-      <c r="C11" s="72" t="s">
+      <c r="C11" s="70" t="s">
         <v>193</v>
       </c>
       <c r="D11" s="47" t="s">
@@ -6733,7 +6740,7 @@
       <c r="B12" s="32" t="s">
         <v>156</v>
       </c>
-      <c r="C12" s="72" t="s">
+      <c r="C12" s="70" t="s">
         <v>195</v>
       </c>
       <c r="D12" s="47" t="s">
@@ -6834,7 +6841,7 @@
       <c r="B13" s="32" t="s">
         <v>155</v>
       </c>
-      <c r="C13" s="72" t="s">
+      <c r="C13" s="70" t="s">
         <v>196</v>
       </c>
       <c r="D13" s="47" t="s">
@@ -6935,7 +6942,7 @@
       <c r="B14" s="32" t="s">
         <v>154</v>
       </c>
-      <c r="C14" s="72" t="s">
+      <c r="C14" s="70" t="s">
         <v>194</v>
       </c>
       <c r="D14" s="47" t="s">
@@ -7036,7 +7043,7 @@
       <c r="B15" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="C15" s="72" t="s">
+      <c r="C15" s="70" t="s">
         <v>197</v>
       </c>
       <c r="D15" s="47" t="s">
@@ -7130,58 +7137,58 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="30">
         <v>16</v>
       </c>
-      <c r="B16" s="64" t="s">
+      <c r="B16" s="62" t="s">
+        <v>215</v>
+      </c>
+      <c r="C16" s="76" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="64" t="s">
+        <v>79</v>
+      </c>
+      <c r="K16" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="L16" s="63" t="s">
+        <v>216</v>
+      </c>
+      <c r="M16" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="N16" s="63" t="s">
         <v>218</v>
       </c>
-      <c r="C16" s="76" t="s">
-        <v>253</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="66" t="s">
-        <v>79</v>
-      </c>
-      <c r="K16" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="L16" s="65" t="s">
+      <c r="O16" s="25" t="s">
         <v>219</v>
       </c>
-      <c r="M16" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="N16" s="65" t="s">
-        <v>221</v>
-      </c>
-      <c r="O16" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="P16" s="67" t="str">
+      <c r="P16" s="65" t="str">
         <f t="shared" ref="P16:P20" si="0">IF(Q16="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="Q16" s="68" t="s">
-        <v>224</v>
+      <c r="Q16" s="66" t="s">
+        <v>221</v>
       </c>
       <c r="R16" s="36" t="s">
         <v>1</v>
@@ -7189,13 +7196,13 @@
       <c r="S16" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T16" s="65" t="s">
+      <c r="T16" s="63" t="s">
         <v>1</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V16" s="74" t="s">
+      <c r="V16" s="72" t="s">
         <v>1</v>
       </c>
       <c r="W16" s="25" t="s">
@@ -7232,15 +7239,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="30">
         <v>17</v>
       </c>
-      <c r="B17" s="64" t="s">
-        <v>225</v>
+      <c r="B17" s="62" t="s">
+        <v>222</v>
       </c>
       <c r="C17" s="76" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>1</v>
@@ -7260,30 +7267,30 @@
       <c r="I17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J17" s="66" t="s">
+      <c r="J17" s="64" t="s">
         <v>79</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="L17" s="65" t="s">
-        <v>219</v>
+        <v>224</v>
+      </c>
+      <c r="L17" s="63" t="s">
+        <v>216</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="N17" s="65" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="N17" s="63" t="s">
+        <v>218</v>
       </c>
       <c r="O17" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="P17" s="67" t="str">
+        <v>223</v>
+      </c>
+      <c r="P17" s="65" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q17" s="68" t="s">
-        <v>228</v>
+      <c r="Q17" s="66" t="s">
+        <v>225</v>
       </c>
       <c r="R17" s="36" t="s">
         <v>1</v>
@@ -7291,13 +7298,13 @@
       <c r="S17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T17" s="65" t="s">
+      <c r="T17" s="63" t="s">
         <v>1</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V17" s="74" t="s">
+      <c r="V17" s="72" t="s">
         <v>1</v>
       </c>
       <c r="W17" s="25" t="s">
@@ -7334,15 +7341,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="30">
         <v>18</v>
       </c>
-      <c r="B18" s="64" t="s">
-        <v>229</v>
+      <c r="B18" s="62" t="s">
+        <v>226</v>
       </c>
       <c r="C18" s="76" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D18" s="47" t="s">
         <v>1</v>
@@ -7362,30 +7369,30 @@
       <c r="I18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J18" s="66" t="s">
+      <c r="J18" s="64" t="s">
         <v>79</v>
       </c>
       <c r="K18" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="L18" s="65" t="s">
-        <v>219</v>
+        <v>228</v>
+      </c>
+      <c r="L18" s="63" t="s">
+        <v>216</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="N18" s="65" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="N18" s="63" t="s">
+        <v>218</v>
       </c>
       <c r="O18" s="25" t="s">
-        <v>230</v>
-      </c>
-      <c r="P18" s="67" t="str">
+        <v>227</v>
+      </c>
+      <c r="P18" s="65" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q18" s="68" t="s">
-        <v>232</v>
+      <c r="Q18" s="66" t="s">
+        <v>229</v>
       </c>
       <c r="R18" s="36" t="s">
         <v>1</v>
@@ -7393,13 +7400,13 @@
       <c r="S18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T18" s="65" t="s">
+      <c r="T18" s="63" t="s">
         <v>1</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V18" s="74" t="s">
+      <c r="V18" s="72" t="s">
         <v>1</v>
       </c>
       <c r="W18" s="25" t="s">
@@ -7436,15 +7443,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="30">
         <v>19</v>
       </c>
-      <c r="B19" s="64" t="s">
-        <v>233</v>
+      <c r="B19" s="62" t="s">
+        <v>230</v>
       </c>
       <c r="C19" s="76" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D19" s="47" t="s">
         <v>1</v>
@@ -7464,30 +7471,30 @@
       <c r="I19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J19" s="66" t="s">
+      <c r="J19" s="64" t="s">
         <v>79</v>
       </c>
       <c r="K19" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="L19" s="65" t="s">
-        <v>219</v>
+        <v>232</v>
+      </c>
+      <c r="L19" s="63" t="s">
+        <v>216</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="N19" s="65" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="N19" s="63" t="s">
+        <v>218</v>
       </c>
       <c r="O19" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="P19" s="67" t="str">
+        <v>231</v>
+      </c>
+      <c r="P19" s="65" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q19" s="68" t="s">
-        <v>236</v>
+      <c r="Q19" s="66" t="s">
+        <v>233</v>
       </c>
       <c r="R19" s="36" t="s">
         <v>1</v>
@@ -7495,13 +7502,13 @@
       <c r="S19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T19" s="65" t="s">
+      <c r="T19" s="63" t="s">
         <v>1</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V19" s="74" t="s">
+      <c r="V19" s="72" t="s">
         <v>1</v>
       </c>
       <c r="W19" s="25" t="s">
@@ -7538,15 +7545,15 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:33" s="69" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="30">
         <v>20</v>
       </c>
-      <c r="B20" s="64" t="s">
-        <v>237</v>
+      <c r="B20" s="62" t="s">
+        <v>234</v>
       </c>
       <c r="C20" s="76" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>1</v>
@@ -7566,30 +7573,30 @@
       <c r="I20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J20" s="66" t="s">
+      <c r="J20" s="64" t="s">
         <v>79</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="L20" s="65" t="s">
-        <v>219</v>
+        <v>236</v>
+      </c>
+      <c r="L20" s="63" t="s">
+        <v>216</v>
       </c>
       <c r="M20" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="N20" s="65" t="s">
-        <v>221</v>
+        <v>217</v>
+      </c>
+      <c r="N20" s="63" t="s">
+        <v>218</v>
       </c>
       <c r="O20" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="P20" s="67" t="str">
+        <v>235</v>
+      </c>
+      <c r="P20" s="65" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q20" s="68" t="s">
-        <v>240</v>
+      <c r="Q20" s="66" t="s">
+        <v>237</v>
       </c>
       <c r="R20" s="36" t="s">
         <v>1</v>
@@ -7597,13 +7604,13 @@
       <c r="S20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T20" s="65" t="s">
+      <c r="T20" s="63" t="s">
         <v>1</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V20" s="74" t="s">
+      <c r="V20" s="72" t="s">
         <v>1</v>
       </c>
       <c r="W20" s="25" t="s">

--- a/Versão5/PRO/Ontologia_Requisitos.xlsx
+++ b/Versão5/PRO/Ontologia_Requisitos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Construtor_Onto\PRO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB26850B-E4E6-4F2D-AF2A-2798A1E8DEF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{831D90C0-555A-46EF-AF8D-8B17493B834E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" activeTab="1" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13290" tabRatio="577" xr2:uid="{6AA21774-678E-47D1-B8DD-6444A2CEB00E}"/>
   </bookViews>
   <sheets>
     <sheet name="Projeto" sheetId="26" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="285">
   <si>
     <t>Key</t>
   </si>
@@ -188,12 +188,6 @@
     <t>Autor</t>
   </si>
   <si>
-    <t>Edição</t>
-  </si>
-  <si>
-    <t>ISBN</t>
-  </si>
-  <si>
     <t>Observações</t>
   </si>
   <si>
@@ -213,21 +207,6 @@
   </si>
   <si>
     <t>Escola Politécnica da UFRJ</t>
-  </si>
-  <si>
-    <t>NormaNúmero</t>
-  </si>
-  <si>
-    <t>NormaEscopo</t>
-  </si>
-  <si>
-    <t>NormaReferência1</t>
-  </si>
-  <si>
-    <t>NormaReferência2</t>
-  </si>
-  <si>
-    <t>NormaReferência3</t>
   </si>
   <si>
     <t>DataHora</t>
@@ -388,57 +367,18 @@
     <t>Define um contêiner de informação de acordo à norma NBR 19650-1. Requerimentos de Sistemas Prediais para o Projeto.</t>
   </si>
   <si>
-    <t>Fonte1</t>
-  </si>
-  <si>
     <t>https://brasil.un.org/pt-br/sdgs</t>
   </si>
   <si>
-    <t>Fonte2</t>
-  </si>
-  <si>
     <t>https://eaesp.fgv.br/centros/centro-estudos-sustentabilidade/projetos/programa-brasileiro-ghg-protocol</t>
   </si>
   <si>
-    <t>Fonte3</t>
-  </si>
-  <si>
     <t>https://www.gov.br/fazenda/pt-br/acesso-a-informacao/acoes-e-programas/transformacao-ecologica/transformacao-ecologica</t>
   </si>
   <si>
-    <t>FonteVegetação1</t>
-  </si>
-  <si>
-    <t>FonteVegetação2</t>
-  </si>
-  <si>
-    <t>FonteVegetação3</t>
-  </si>
-  <si>
-    <t>FonteVegetação4</t>
-  </si>
-  <si>
-    <t>FonteVegetação5</t>
-  </si>
-  <si>
-    <t>FonteVegetação6</t>
-  </si>
-  <si>
-    <t>FonteVegetação7</t>
-  </si>
-  <si>
-    <t>FonteVegetação8</t>
-  </si>
-  <si>
-    <t>FonteTSB</t>
-  </si>
-  <si>
     <t>https://www.gov.br/fazenda/pt-br/orgaos/spe/taxonomia-sustentavel-brasileira/cadernos</t>
   </si>
   <si>
-    <t>FonteSINAPI</t>
-  </si>
-  <si>
     <t>https://www.caixa.gov.br/site/Paginas/downloads.aspx#categoria_888</t>
   </si>
   <si>
@@ -866,13 +806,133 @@
   </si>
   <si>
     <t>API.Método.Visual</t>
+  </si>
+  <si>
+    <t>Norma-Número</t>
+  </si>
+  <si>
+    <t>Norma-Edição</t>
+  </si>
+  <si>
+    <t>Norma-ISBN</t>
+  </si>
+  <si>
+    <t>Norma-Escopo</t>
+  </si>
+  <si>
+    <t>Norma-Referência-01</t>
+  </si>
+  <si>
+    <t>Norma-Referência-02</t>
+  </si>
+  <si>
+    <t>Norma-Referência-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-01</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-02</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-03</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-04</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-05</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-06</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-07</t>
+  </si>
+  <si>
+    <t>Fonte-Vegetação-08</t>
+  </si>
+  <si>
+    <t>Fonte-SINAPI</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-01</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-02</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-03</t>
+  </si>
+  <si>
+    <t>Fonte-Brasil-Saúde-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-01</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-02</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-03</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-04</t>
+  </si>
+  <si>
+    <t>Fonte-NBR-05</t>
+  </si>
+  <si>
+    <t>Fonte-Bombeiros-01</t>
+  </si>
+  <si>
+    <t>https://somasus.saude.gov.br/sistema/home</t>
+  </si>
+  <si>
+    <t>https://anvisalegis.datalegis.net</t>
+  </si>
+  <si>
+    <t>RDC 611/2022. Radiologia diagnóstica. Blindagem, proteção radiológica.</t>
+  </si>
+  <si>
+    <t>RDC 222/2018. Gerenciamento de resíduos. Plano de gerenciamento obrigatório.</t>
+  </si>
+  <si>
+    <t>NBR 9050. Acessibilidade. Todos os ambientes de uso público.</t>
+  </si>
+  <si>
+    <t>NBR 7256. Climatização em EAS. Obrigatória para CC, CTI, CME, hemodinâmica.</t>
+  </si>
+  <si>
+    <t>NBR 15575. Desempenho de edificações. Conforto térmico, acústico, lumínico.</t>
+  </si>
+  <si>
+    <t>NBR 13534. Instalações elétricas em EAS. Circuitos, aterramento, emergência.</t>
+  </si>
+  <si>
+    <t>NBR 12188. Gases medicinais. Centrais, redes, pontos de uso.</t>
+  </si>
+  <si>
+    <t>Segurança contra incêndio. Varia por estado, consultar regulamento local.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -982,25 +1042,12 @@
     </font>
     <font>
       <sz val="6"/>
-      <color theme="10"/>
-      <name val="Arial Nova Cond Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="6"/>
-      <color theme="10"/>
-      <name val="Arial Nova Cond Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="6"/>
       <color theme="1"/>
       <name val="Arial Nova Cond"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="28">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1163,6 +1210,12 @@
         <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAEAAAA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -1216,7 +1269,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1328,11 +1381,9 @@
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="22" fontId="12" fillId="19" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1366,18 +1417,6 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="18" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1409,10 +1448,10 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="22" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1442,12 +1481,39 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="28" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="12" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hiperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="29">
     <dxf>
       <font>
         <b val="0"/>
@@ -1646,42 +1712,6 @@
         <i/>
         <strike val="0"/>
         <color theme="0"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-        <strike val="0"/>
-        <color theme="0" tint="-0.499984740745262"/>
       </font>
     </dxf>
     <dxf>
@@ -2054,457 +2084,569 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{612B613C-8B96-43A0-BB50-A45AC26373E3}">
   <sheetPr codeName="Planilha1"/>
-  <dimension ref="A1:C39"/>
-  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C49"/>
+  <sheetFormatPr defaultColWidth="3.28515625" defaultRowHeight="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10" style="6" customWidth="1"/>
-    <col min="2" max="2" width="68.85546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="52.140625" style="6" customWidth="1"/>
+    <col min="3" max="3" width="3.42578125" style="44" bestFit="1" customWidth="1"/>
     <col min="4" max="16384" width="3.28515625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+    <row r="1" spans="1:3" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="73" t="s">
         <v>35</v>
       </c>
       <c r="B1" s="7" t="s">
         <v>34</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>125</v>
-      </c>
-      <c r="C3" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="C4" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="10" t="s">
         <v>37</v>
       </c>
       <c r="B5" s="8" t="str">
         <f>_xlfn.CONCAT(B4,"Prop")</f>
         <v>BIMProp</v>
       </c>
-      <c r="C5" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
+      <c r="C5" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B6" s="8" t="str">
         <f>_xlfn.CONCAT(B4,"Data")</f>
         <v>BIMData</v>
       </c>
-      <c r="C6" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+      <c r="C6" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
         <v>39</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>45</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
         <v>40</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
-        <v>48</v>
+        <v>86</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="10" t="s">
+        <v>46</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
-        <v>50</v>
+        <v>47</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>245</v>
       </c>
       <c r="B10" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
-        <v>41</v>
+      <c r="C10" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>246</v>
       </c>
       <c r="B11" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>42</v>
+      <c r="C11" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>247</v>
       </c>
       <c r="B12" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
-        <v>51</v>
+      <c r="C12" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
+        <v>248</v>
       </c>
       <c r="B13" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C13" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>52</v>
+      <c r="C13" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="10" t="s">
+        <v>249</v>
       </c>
       <c r="B14" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>53</v>
+      <c r="C14" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="10" t="s">
+        <v>250</v>
       </c>
       <c r="B15" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C15" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="s">
-        <v>54</v>
+      <c r="C15" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>251</v>
       </c>
       <c r="B16" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>43</v>
+      <c r="C16" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>41</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>126</v>
-      </c>
-      <c r="C17" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="B18" s="40">
+        <v>106</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="39">
         <f ca="1">NOW()</f>
-        <v>46274.402743634259</v>
-      </c>
-      <c r="C18" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="s">
-        <v>99</v>
+        <v>46276.433893981484</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="10" t="s">
+        <v>92</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C19" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C20" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C20" s="43" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>100</v>
+        <v>93</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C21" s="45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="s">
-        <v>56</v>
+      <c r="C21" s="43" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="10" t="s">
+        <v>49</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="s">
-        <v>57</v>
+      <c r="C22" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="10" t="s">
+        <v>50</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C23" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C23" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>127</v>
-      </c>
-      <c r="C24" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+      <c r="C24" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B25" s="11" t="str">
         <f>_xlfn.TRANSLATE(B24,"pt","es")</f>
         <v>Formalizar los conceptos de los elementos de Requisitos del Proyecto.</v>
       </c>
-      <c r="C25" s="45" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="10" t="s">
-        <v>92</v>
+      <c r="C25" s="43" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="8" t="s">
+        <v>85</v>
       </c>
       <c r="B26" s="11" t="str">
         <f>_xlfn.TRANSLATE(B25,"pt","en")</f>
         <v>Formalizar los conceptos de los elementos de Requisitos del Proyecto.</v>
       </c>
-      <c r="C26" s="45" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C26" s="43" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="B27" s="53" t="s">
-        <v>106</v>
-      </c>
-      <c r="C27" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+      <c r="B27" s="74" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="B28" s="54" t="s">
-        <v>108</v>
-      </c>
-      <c r="C28" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>253</v>
+      </c>
+      <c r="B28" s="75" t="s">
+        <v>99</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="B29" s="54" t="s">
-        <v>110</v>
-      </c>
-      <c r="C29" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>254</v>
+      </c>
+      <c r="B29" s="75" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="B30" s="39" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>255</v>
+      </c>
+      <c r="B30" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B31" s="39" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>256</v>
+      </c>
+      <c r="B31" s="77" t="s">
+        <v>78</v>
+      </c>
+      <c r="C31" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="8" t="s">
-        <v>113</v>
-      </c>
-      <c r="B32" s="39" t="s">
-        <v>87</v>
-      </c>
-      <c r="C32" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>257</v>
+      </c>
+      <c r="B32" s="77" t="s">
+        <v>77</v>
+      </c>
+      <c r="C32" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B33" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="C33" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+        <v>258</v>
+      </c>
+      <c r="B33" s="77" t="s">
+        <v>80</v>
+      </c>
+      <c r="C33" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="B34" s="41" t="s">
+        <v>259</v>
+      </c>
+      <c r="B34" s="78" t="s">
+        <v>76</v>
+      </c>
+      <c r="C34" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B35" s="78" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B36" s="77" t="s">
+        <v>79</v>
+      </c>
+      <c r="C36" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="B37" s="78" t="s">
+        <v>74</v>
+      </c>
+      <c r="C37" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B38" s="77" t="s">
         <v>82</v>
       </c>
-      <c r="C34" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="8" t="s">
-        <v>116</v>
-      </c>
-      <c r="B35" s="39" t="s">
-        <v>86</v>
-      </c>
-      <c r="C35" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B36" s="41" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B37" s="39" t="s">
-        <v>89</v>
-      </c>
-      <c r="C37" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
-        <v>119</v>
-      </c>
-      <c r="B38" s="55" t="s">
-        <v>120</v>
-      </c>
-      <c r="C38" s="45" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
+      <c r="C38" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" s="28" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A39" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="B39" s="56" t="s">
-        <v>122</v>
-      </c>
-      <c r="C39" s="45" t="s">
-        <v>96</v>
+        <v>264</v>
+      </c>
+      <c r="B39" s="79" t="s">
+        <v>102</v>
+      </c>
+      <c r="C39" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B40" s="79" t="s">
+        <v>275</v>
+      </c>
+      <c r="C40" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="B41" s="80" t="s">
+        <v>276</v>
+      </c>
+      <c r="C41" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="B42" s="81" t="s">
+        <v>277</v>
+      </c>
+      <c r="C42" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="B43" s="81" t="s">
+        <v>278</v>
+      </c>
+      <c r="C43" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B44" s="81" t="s">
+        <v>279</v>
+      </c>
+      <c r="C44" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="B45" s="81" t="s">
+        <v>280</v>
+      </c>
+      <c r="C45" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="8" t="s">
+        <v>271</v>
+      </c>
+      <c r="B46" s="81" t="s">
+        <v>281</v>
+      </c>
+      <c r="C46" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="B47" s="81" t="s">
+        <v>282</v>
+      </c>
+      <c r="C47" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="8" t="s">
+        <v>273</v>
+      </c>
+      <c r="B48" s="81" t="s">
+        <v>283</v>
+      </c>
+      <c r="C48" s="43" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B49" s="81" t="s">
+        <v>284</v>
+      </c>
+      <c r="C49" s="43" t="s">
+        <v>88</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B27" r:id="rId1" xr:uid="{3343E6A9-86A0-42D5-9FF3-99B9D570A215}"/>
-    <hyperlink ref="B29" r:id="rId2" xr:uid="{9F21B17E-1A88-4255-8D14-497AE2AC52F8}"/>
-    <hyperlink ref="B28" r:id="rId3" xr:uid="{B6F85019-4F90-451D-84D9-3549C8C3FFCF}"/>
-    <hyperlink ref="B38" r:id="rId4" xr:uid="{E23DD233-D0F5-48FB-8CE4-CF7A0A8CEE5C}"/>
-    <hyperlink ref="B39" r:id="rId5" location="categoria_888" xr:uid="{0E197C45-8E93-406B-B436-CDD35976D07C}"/>
+    <hyperlink ref="B27" r:id="rId1" xr:uid="{3EC41389-149C-409D-9A52-D4E4C5EF61E4}"/>
+    <hyperlink ref="B29" r:id="rId2" xr:uid="{D4C0BB36-0EB6-45DC-BAC1-2B9753906B23}"/>
+    <hyperlink ref="B28" r:id="rId3" xr:uid="{AB0B8BFB-6121-4DFF-AD19-22D1499F9156}"/>
+    <hyperlink ref="B39" r:id="rId4" location="categoria_888" xr:uid="{FAB3B0AD-9328-41FC-8597-4BCFC05C1144}"/>
+    <hyperlink ref="B40" r:id="rId5" xr:uid="{AF363146-0421-42DA-8E70-E55E119E91D4}"/>
+    <hyperlink ref="B41" r:id="rId6" xr:uid="{6FCAA10D-9705-4CB7-BEC9-0F59EA6EFC40}"/>
+    <hyperlink ref="B30" r:id="rId7" xr:uid="{D30D4A46-5020-474E-BBC0-EE840A74B9D1}"/>
   </hyperlinks>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -2530,7 +2672,7 @@
     <col min="16" max="16" width="64.5703125" style="27" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="73.42578125" style="27" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="67.7109375" style="27" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="4.140625" style="78" customWidth="1"/>
+    <col min="19" max="19" width="4.140625" style="72" customWidth="1"/>
     <col min="20" max="20" width="9.85546875" style="27" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.7109375" style="27" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="9.5703125" style="27" bestFit="1" customWidth="1"/>
@@ -2550,19 +2692,19 @@
         <v>1</v>
       </c>
       <c r="B1" s="14" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D1" s="14" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="E1" s="14" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="F1" s="14" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="G1" s="29" t="s">
         <v>24</v>
@@ -2592,83 +2734,83 @@
         <v>29</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="Q1" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="R1" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="S1" s="71" t="s">
+        <v>64</v>
+      </c>
+      <c r="T1" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="U1" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="V1" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="W1" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="X1" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="Y1" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="R1" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="S1" s="77" t="s">
-        <v>71</v>
-      </c>
-      <c r="T1" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="U1" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="V1" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="W1" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="X1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y1" s="16" t="s">
-        <v>77</v>
-      </c>
       <c r="Z1" s="16" t="s">
-        <v>212</v>
+        <v>192</v>
       </c>
       <c r="AA1" s="15" t="s">
-        <v>214</v>
+        <v>194</v>
       </c>
       <c r="AB1" s="15" t="s">
-        <v>213</v>
+        <v>193</v>
       </c>
       <c r="AC1" s="15" t="s">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="AD1" s="15" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="2" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="52">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="2" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="50">
         <v>2</v>
       </c>
-      <c r="B2" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D2" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E2" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F2" s="71" t="s">
-        <v>174</v>
-      </c>
-      <c r="G2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J2" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K2" s="49" t="s">
+      <c r="B2" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E2" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F2" s="65" t="s">
+        <v>154</v>
+      </c>
+      <c r="G2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J2" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K2" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L2" s="23" t="str">
@@ -2688,15 +2830,15 @@
         <v>É Requisito Geral</v>
       </c>
       <c r="P2" s="24" t="s">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="Q2" s="24" t="s">
-        <v>206</v>
+        <v>186</v>
       </c>
       <c r="R2" s="24" t="s">
-        <v>200</v>
-      </c>
-      <c r="S2" s="73" t="s">
+        <v>180</v>
+      </c>
+      <c r="S2" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T2" s="24" t="str">
@@ -2712,63 +2854,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W2" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X2" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X2" s="49" t="str">
         <f t="shared" ref="X2:X3" si="7">CONCATENATE("Key-REQ-",A2)</f>
         <v>Key-REQ-2</v>
       </c>
-      <c r="Y2" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="60" t="s">
+      <c r="Y2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC2" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD2" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="52">
+    <row r="3" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="50">
         <v>3</v>
       </c>
-      <c r="B3" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D3" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E3" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F3" s="71" t="s">
-        <v>180</v>
-      </c>
-      <c r="G3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K3" s="49" t="s">
+      <c r="B3" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C3" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D3" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E3" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="65" t="s">
+        <v>160</v>
+      </c>
+      <c r="G3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J3" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L3" s="23" t="str">
@@ -2788,15 +2930,15 @@
         <v>É Requisito Pessoal</v>
       </c>
       <c r="P3" s="24" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="Q3" s="24" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="R3" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="S3" s="73" t="s">
+        <v>181</v>
+      </c>
+      <c r="S3" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T3" s="24" t="str">
@@ -2812,63 +2954,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W3" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X3" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X3" s="49" t="str">
         <f t="shared" si="7"/>
         <v>Key-REQ-3</v>
       </c>
-      <c r="Y3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="60" t="s">
+      <c r="Y3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC3" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD3" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52">
+    <row r="4" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="50">
         <v>4</v>
       </c>
-      <c r="B4" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D4" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E4" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F4" s="71" t="s">
-        <v>151</v>
-      </c>
-      <c r="G4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J4" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K4" s="49" t="s">
+      <c r="B4" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D4" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="65" t="s">
+        <v>131</v>
+      </c>
+      <c r="G4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J4" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K4" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L4" s="23" t="str">
@@ -2888,15 +3030,15 @@
         <v>É Requisito Espacial</v>
       </c>
       <c r="P4" s="24" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="Q4" s="24" t="s">
-        <v>207</v>
+        <v>187</v>
       </c>
       <c r="R4" s="24" t="s">
-        <v>201</v>
-      </c>
-      <c r="S4" s="73" t="s">
+        <v>181</v>
+      </c>
+      <c r="S4" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T4" s="24" t="str">
@@ -2912,63 +3054,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W4" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X4" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X4" s="49" t="str">
         <f t="shared" ref="X4:X18" si="11">CONCATENATE("Key-REQ-",A4)</f>
         <v>Key-REQ-4</v>
       </c>
-      <c r="Y4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="60" t="s">
+      <c r="Y4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC4" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD4" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="52">
+    <row r="5" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="50">
         <v>5</v>
       </c>
-      <c r="B5" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D5" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E5" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F5" s="71" t="s">
-        <v>152</v>
-      </c>
-      <c r="G5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J5" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K5" s="49" t="s">
+      <c r="B5" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E5" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="65" t="s">
+        <v>132</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J5" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K5" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L5" s="23" t="str">
@@ -2988,15 +3130,15 @@
         <v>É Requisito Mobiliário</v>
       </c>
       <c r="P5" s="24" t="s">
-        <v>102</v>
+        <v>95</v>
       </c>
       <c r="Q5" s="24" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="R5" s="24" t="s">
-        <v>202</v>
-      </c>
-      <c r="S5" s="73" t="s">
+        <v>182</v>
+      </c>
+      <c r="S5" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T5" s="24" t="str">
@@ -3012,63 +3154,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W5" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X5" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X5" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-5</v>
       </c>
-      <c r="Y5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="60" t="s">
+      <c r="Y5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC5" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD5" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="52">
+    <row r="6" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="50">
         <v>6</v>
       </c>
-      <c r="B6" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D6" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E6" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F6" s="71" t="s">
-        <v>153</v>
-      </c>
-      <c r="G6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J6" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K6" s="49" t="s">
+      <c r="B6" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D6" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E6" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="65" t="s">
+        <v>133</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J6" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K6" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L6" s="23" t="str">
@@ -3088,15 +3230,15 @@
         <v>É Requisito Equipamento</v>
       </c>
       <c r="P6" s="24" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="Q6" s="24" t="s">
-        <v>209</v>
+        <v>189</v>
       </c>
       <c r="R6" s="24" t="s">
-        <v>203</v>
-      </c>
-      <c r="S6" s="73" t="s">
+        <v>183</v>
+      </c>
+      <c r="S6" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T6" s="24" t="str">
@@ -3112,63 +3254,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W6" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X6" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X6" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-6</v>
       </c>
-      <c r="Y6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="60" t="s">
+      <c r="Y6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC6" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD6" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="52">
+    <row r="7" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="50">
         <v>7</v>
       </c>
-      <c r="B7" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D7" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E7" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F7" s="71" t="s">
-        <v>187</v>
-      </c>
-      <c r="G7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J7" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K7" s="49" t="s">
+      <c r="B7" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C7" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="65" t="s">
+        <v>167</v>
+      </c>
+      <c r="G7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J7" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K7" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L7" s="23" t="str">
@@ -3188,15 +3330,15 @@
         <v>É Requisito Avac</v>
       </c>
       <c r="P7" s="24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q7" s="24" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="R7" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="S7" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="S7" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T7" s="24" t="str">
@@ -3212,63 +3354,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W7" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X7" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X7" s="49" t="str">
         <f t="shared" ref="X7:X11" si="19">CONCATENATE("Key-REQ-",A7)</f>
         <v>Key-REQ-7</v>
       </c>
-      <c r="Y7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="60" t="s">
+      <c r="Y7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC7" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD7" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="52">
+    <row r="8" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="50">
         <v>8</v>
       </c>
-      <c r="B8" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D8" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F8" s="71" t="s">
-        <v>188</v>
-      </c>
-      <c r="G8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J8" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K8" s="49" t="s">
+      <c r="B8" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C8" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E8" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="65" t="s">
+        <v>168</v>
+      </c>
+      <c r="G8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J8" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K8" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L8" s="23" t="str">
@@ -3288,15 +3430,15 @@
         <v>É Requisito Hidráulico</v>
       </c>
       <c r="P8" s="24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q8" s="24" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="R8" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="S8" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="S8" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T8" s="24" t="str">
@@ -3312,63 +3454,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W8" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X8" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X8" s="49" t="str">
         <f t="shared" si="19"/>
         <v>Key-REQ-8</v>
       </c>
-      <c r="Y8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="60" t="s">
+      <c r="Y8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC8" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD8" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="52">
+    <row r="9" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="50">
         <v>9</v>
       </c>
-      <c r="B9" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D9" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F9" s="71" t="s">
-        <v>189</v>
-      </c>
-      <c r="G9" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H9" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I9" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J9" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K9" s="49" t="s">
+      <c r="B9" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D9" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="65" t="s">
+        <v>169</v>
+      </c>
+      <c r="G9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J9" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K9" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L9" s="23" t="str">
@@ -3388,15 +3530,15 @@
         <v>É Requisito Elétrico</v>
       </c>
       <c r="P9" s="24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q9" s="24" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="R9" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="S9" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="S9" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T9" s="24" t="str">
@@ -3412,63 +3554,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W9" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X9" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X9" s="49" t="str">
         <f t="shared" si="19"/>
         <v>Key-REQ-9</v>
       </c>
-      <c r="Y9" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="60" t="s">
+      <c r="Y9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC9" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD9" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="52">
+    <row r="10" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="50">
         <v>10</v>
       </c>
-      <c r="B10" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D10" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E10" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F10" s="71" t="s">
-        <v>190</v>
-      </c>
-      <c r="G10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J10" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K10" s="49" t="s">
+      <c r="B10" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D10" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E10" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="65" t="s">
+        <v>170</v>
+      </c>
+      <c r="G10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J10" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K10" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L10" s="23" t="str">
@@ -3488,15 +3630,15 @@
         <v>É Requisito Incêndio</v>
       </c>
       <c r="P10" s="24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q10" s="24" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="R10" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="S10" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="S10" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T10" s="24" t="str">
@@ -3512,63 +3654,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W10" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X10" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X10" s="49" t="str">
         <f t="shared" si="19"/>
         <v>Key-REQ-10</v>
       </c>
-      <c r="Y10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="60" t="s">
+      <c r="Y10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC10" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD10" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="52">
+    <row r="11" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="50">
         <v>11</v>
       </c>
-      <c r="B11" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D11" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E11" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F11" s="71" t="s">
-        <v>191</v>
-      </c>
-      <c r="G11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J11" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K11" s="49" t="s">
+      <c r="B11" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C11" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D11" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E11" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="65" t="s">
+        <v>171</v>
+      </c>
+      <c r="G11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J11" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K11" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L11" s="23" t="str">
@@ -3588,15 +3730,15 @@
         <v>É Requisito Sanitário</v>
       </c>
       <c r="P11" s="24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q11" s="24" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="R11" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="S11" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="S11" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T11" s="24" t="str">
@@ -3612,63 +3754,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W11" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X11" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X11" s="49" t="str">
         <f t="shared" si="19"/>
         <v>Key-REQ-11</v>
       </c>
-      <c r="Y11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="60" t="s">
+      <c r="Y11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC11" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD11" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="52">
+    <row r="12" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="50">
         <v>12</v>
       </c>
-      <c r="B12" s="75" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="75" t="s">
-        <v>175</v>
-      </c>
-      <c r="D12" s="71" t="s">
-        <v>128</v>
-      </c>
-      <c r="E12" s="71" t="s">
-        <v>176</v>
-      </c>
-      <c r="F12" s="71" t="s">
-        <v>192</v>
-      </c>
-      <c r="G12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J12" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K12" s="49" t="s">
+      <c r="B12" s="69" t="s">
+        <v>103</v>
+      </c>
+      <c r="C12" s="69" t="s">
+        <v>155</v>
+      </c>
+      <c r="D12" s="65" t="s">
+        <v>108</v>
+      </c>
+      <c r="E12" s="65" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="65" t="s">
+        <v>172</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J12" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K12" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L12" s="23" t="str">
@@ -3688,15 +3830,15 @@
         <v>É Requisito Lógico</v>
       </c>
       <c r="P12" s="24" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="R12" s="24" t="s">
-        <v>204</v>
-      </c>
-      <c r="S12" s="73" t="s">
+        <v>184</v>
+      </c>
+      <c r="S12" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T12" s="24" t="str">
@@ -3712,63 +3854,63 @@
         <v>Requisitadas</v>
       </c>
       <c r="W12" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X12" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X12" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-12</v>
       </c>
-      <c r="Y12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="60" t="s">
+      <c r="Y12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC12" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD12" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="52">
+    <row r="13" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="50">
         <v>13</v>
       </c>
-      <c r="B13" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C13" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D13" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E13" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F13" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="G13" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H13" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I13" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J13" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K13" s="49" t="s">
+      <c r="B13" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D13" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E13" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F13" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="G13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J13" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K13" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L13" s="23" t="str">
@@ -3788,15 +3930,15 @@
         <v>Necessidade Geral</v>
       </c>
       <c r="P13" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q13" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R13" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S13" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S13" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T13" s="24" t="str">
@@ -3812,63 +3954,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W13" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X13" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X13" s="49" t="str">
         <f t="shared" ref="X13:X14" si="20">CONCATENATE("Key-REQ-",A13)</f>
         <v>Key-REQ-13</v>
       </c>
-      <c r="Y13" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="60" t="s">
+      <c r="Y13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC13" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD13" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="52">
+    <row r="14" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="50">
         <v>14</v>
       </c>
-      <c r="B14" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C14" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D14" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E14" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F14" s="71" t="s">
-        <v>179</v>
-      </c>
-      <c r="G14" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H14" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I14" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J14" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K14" s="49" t="s">
+      <c r="B14" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D14" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E14" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F14" s="65" t="s">
+        <v>159</v>
+      </c>
+      <c r="G14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J14" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K14" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L14" s="23" t="str">
@@ -3888,15 +4030,15 @@
         <v>Necessidade Pessoal</v>
       </c>
       <c r="P14" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q14" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R14" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S14" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S14" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T14" s="24" t="str">
@@ -3912,63 +4054,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W14" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X14" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X14" s="49" t="str">
         <f t="shared" si="20"/>
         <v>Key-REQ-14</v>
       </c>
-      <c r="Y14" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="60" t="s">
+      <c r="Y14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC14" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD14" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="52">
+    <row r="15" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="50">
         <v>15</v>
       </c>
-      <c r="B15" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D15" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E15" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F15" s="71" t="s">
-        <v>129</v>
-      </c>
-      <c r="G15" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H15" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I15" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J15" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K15" s="49" t="s">
+      <c r="B15" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C15" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D15" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E15" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F15" s="65" t="s">
+        <v>109</v>
+      </c>
+      <c r="G15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J15" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K15" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L15" s="23" t="str">
@@ -3988,15 +4130,15 @@
         <v>Necessidade Espacial</v>
       </c>
       <c r="P15" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q15" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R15" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S15" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S15" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T15" s="24" t="str">
@@ -4012,63 +4154,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W15" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X15" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X15" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-15</v>
       </c>
-      <c r="Y15" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="60" t="s">
+      <c r="Y15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC15" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD15" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="52">
+    <row r="16" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="50">
         <v>16</v>
       </c>
-      <c r="B16" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C16" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D16" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E16" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F16" s="71" t="s">
-        <v>130</v>
-      </c>
-      <c r="G16" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H16" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I16" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J16" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K16" s="49" t="s">
+      <c r="B16" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C16" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E16" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F16" s="65" t="s">
+        <v>110</v>
+      </c>
+      <c r="G16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J16" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K16" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L16" s="23" t="str">
@@ -4088,15 +4230,15 @@
         <v>Necessidade Mobiliário</v>
       </c>
       <c r="P16" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q16" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R16" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S16" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S16" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T16" s="24" t="str">
@@ -4112,63 +4254,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W16" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X16" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X16" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-16</v>
       </c>
-      <c r="Y16" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="60" t="s">
+      <c r="Y16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC16" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD16" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="52">
+    <row r="17" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="50">
         <v>17</v>
       </c>
-      <c r="B17" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D17" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E17" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F17" s="71" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H17" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I17" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J17" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K17" s="49" t="s">
+      <c r="B17" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C17" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D17" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E17" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F17" s="65" t="s">
+        <v>111</v>
+      </c>
+      <c r="G17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J17" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K17" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L17" s="23" t="str">
@@ -4188,15 +4330,15 @@
         <v>Necessidade Equipamento</v>
       </c>
       <c r="P17" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q17" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R17" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S17" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S17" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T17" s="24" t="str">
@@ -4212,63 +4354,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W17" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X17" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X17" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-17</v>
       </c>
-      <c r="Y17" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="60" t="s">
+      <c r="Y17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC17" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD17" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="52">
+    <row r="18" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="50">
         <v>18</v>
       </c>
-      <c r="B18" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" s="75" t="s">
+      <c r="B18" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D18" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E18" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F18" s="65" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E18" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F18" s="71" t="s">
-        <v>193</v>
-      </c>
-      <c r="G18" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H18" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I18" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J18" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K18" s="49" t="s">
+      <c r="G18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J18" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K18" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L18" s="23" t="str">
@@ -4288,15 +4430,15 @@
         <v>Necessidade Avac</v>
       </c>
       <c r="P18" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q18" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R18" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S18" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S18" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T18" s="24" t="str">
@@ -4312,63 +4454,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W18" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X18" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X18" s="49" t="str">
         <f t="shared" si="11"/>
         <v>Key-REQ-18</v>
       </c>
-      <c r="Y18" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="60" t="s">
+      <c r="Y18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC18" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD18" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="52">
+    <row r="19" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="50">
         <v>19</v>
       </c>
-      <c r="B19" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D19" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E19" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F19" s="71" t="s">
-        <v>195</v>
-      </c>
-      <c r="G19" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H19" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I19" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J19" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K19" s="49" t="s">
+      <c r="B19" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C19" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D19" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E19" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F19" s="65" t="s">
+        <v>175</v>
+      </c>
+      <c r="G19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J19" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K19" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L19" s="23" t="str">
@@ -4388,15 +4530,15 @@
         <v>Necessidade Hidráulica</v>
       </c>
       <c r="P19" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q19" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R19" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S19" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S19" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T19" s="24" t="str">
@@ -4412,63 +4554,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W19" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X19" s="51" t="str">
-        <f t="shared" ref="X19:X28" si="34">CONCATENATE("Key-REQ-",A19)</f>
+        <v>113</v>
+      </c>
+      <c r="X19" s="49" t="str">
+        <f t="shared" ref="X19:X23" si="34">CONCATENATE("Key-REQ-",A19)</f>
         <v>Key-REQ-19</v>
       </c>
-      <c r="Y19" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="60" t="s">
+      <c r="Y19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC19" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD19" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="52">
+    <row r="20" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="50">
         <v>20</v>
       </c>
-      <c r="B20" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C20" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D20" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E20" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F20" s="71" t="s">
-        <v>196</v>
-      </c>
-      <c r="G20" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H20" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I20" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J20" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K20" s="49" t="s">
+      <c r="B20" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F20" s="65" t="s">
+        <v>176</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J20" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K20" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L20" s="23" t="str">
@@ -4488,15 +4630,15 @@
         <v>Necessidade Elétrica</v>
       </c>
       <c r="P20" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q20" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R20" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S20" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S20" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T20" s="24" t="str">
@@ -4512,63 +4654,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W20" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X20" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X20" s="49" t="str">
         <f t="shared" si="34"/>
         <v>Key-REQ-20</v>
       </c>
-      <c r="Y20" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="60" t="s">
+      <c r="Y20" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC20" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD20" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="52">
+    <row r="21" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="50">
         <v>21</v>
       </c>
-      <c r="B21" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C21" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D21" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E21" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F21" s="71" t="s">
-        <v>194</v>
-      </c>
-      <c r="G21" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H21" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I21" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J21" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K21" s="49" t="s">
+      <c r="B21" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C21" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F21" s="65" t="s">
+        <v>174</v>
+      </c>
+      <c r="G21" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H21" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I21" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J21" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K21" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L21" s="23" t="str">
@@ -4588,15 +4730,15 @@
         <v>Necessidade Incêndio</v>
       </c>
       <c r="P21" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q21" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R21" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S21" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S21" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T21" s="24" t="str">
@@ -4612,63 +4754,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W21" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X21" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X21" s="49" t="str">
         <f t="shared" si="34"/>
         <v>Key-REQ-21</v>
       </c>
-      <c r="Y21" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z21" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA21" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB21" s="60" t="s">
+      <c r="Y21" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB21" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC21" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD21" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="52">
+    <row r="22" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="50">
         <v>22</v>
       </c>
-      <c r="B22" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C22" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D22" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E22" s="71" t="s">
+      <c r="B22" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C22" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D22" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F22" s="65" t="s">
         <v>177</v>
       </c>
-      <c r="F22" s="71" t="s">
-        <v>197</v>
-      </c>
-      <c r="G22" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H22" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I22" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J22" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K22" s="49" t="s">
+      <c r="G22" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H22" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I22" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J22" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K22" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L22" s="23" t="str">
@@ -4688,15 +4830,15 @@
         <v>Necessidade Sanitária</v>
       </c>
       <c r="P22" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S22" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S22" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T22" s="24" t="str">
@@ -4712,63 +4854,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W22" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X22" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X22" s="49" t="str">
         <f t="shared" si="34"/>
         <v>Key-REQ-22</v>
       </c>
-      <c r="Y22" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z22" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA22" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB22" s="60" t="s">
+      <c r="Y22" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB22" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC22" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD22" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:30" s="57" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="52">
+    <row r="23" spans="1:30" s="51" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="50">
         <v>23</v>
       </c>
-      <c r="B23" s="75" t="s">
-        <v>74</v>
-      </c>
-      <c r="C23" s="75" t="s">
-        <v>173</v>
-      </c>
-      <c r="D23" s="71" t="s">
-        <v>135</v>
-      </c>
-      <c r="E23" s="71" t="s">
-        <v>177</v>
-      </c>
-      <c r="F23" s="71" t="s">
-        <v>198</v>
-      </c>
-      <c r="G23" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H23" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I23" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J23" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K23" s="49" t="s">
+      <c r="B23" s="69" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" s="69" t="s">
+        <v>153</v>
+      </c>
+      <c r="D23" s="65" t="s">
+        <v>115</v>
+      </c>
+      <c r="E23" s="65" t="s">
+        <v>157</v>
+      </c>
+      <c r="F23" s="65" t="s">
+        <v>178</v>
+      </c>
+      <c r="G23" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H23" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I23" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J23" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K23" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L23" s="23" t="str">
@@ -4788,15 +4930,15 @@
         <v>Necessidade Lógica</v>
       </c>
       <c r="P23" s="24" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="Q23" s="24" t="s">
-        <v>211</v>
+        <v>191</v>
       </c>
       <c r="R23" s="24" t="s">
-        <v>205</v>
-      </c>
-      <c r="S23" s="73" t="s">
+        <v>185</v>
+      </c>
+      <c r="S23" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T23" s="24" t="str">
@@ -4812,63 +4954,63 @@
         <v>Atendidas</v>
       </c>
       <c r="W23" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X23" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X23" s="49" t="str">
         <f t="shared" si="34"/>
         <v>Key-REQ-23</v>
       </c>
-      <c r="Y23" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z23" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA23" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB23" s="60" t="s">
+      <c r="Y23" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB23" s="54" t="s">
         <v>1</v>
       </c>
       <c r="AC23" s="24" t="s">
-        <v>124</v>
+        <v>104</v>
       </c>
       <c r="AD23" s="24" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="52">
+    <row r="24" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="50">
         <v>24</v>
       </c>
-      <c r="B24" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="C24" s="76" t="s">
-        <v>260</v>
-      </c>
-      <c r="D24" s="76" t="s">
-        <v>261</v>
-      </c>
-      <c r="E24" s="76" t="s">
-        <v>262</v>
-      </c>
-      <c r="F24" s="76" t="s">
-        <v>238</v>
-      </c>
-      <c r="G24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J24" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K24" s="49" t="s">
+      <c r="B24" s="69" t="s">
+        <v>239</v>
+      </c>
+      <c r="C24" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D24" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="E24" s="70" t="s">
+        <v>242</v>
+      </c>
+      <c r="F24" s="70" t="s">
+        <v>218</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H24" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I24" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J24" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K24" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L24" s="23" t="str">
@@ -4888,15 +5030,15 @@
         <v>Função Auxiliar</v>
       </c>
       <c r="P24" s="24" t="s">
-        <v>239</v>
+        <v>219</v>
       </c>
       <c r="Q24" s="24" t="s">
-        <v>240</v>
+        <v>220</v>
       </c>
       <c r="R24" s="24" t="s">
-        <v>241</v>
-      </c>
-      <c r="S24" s="73" t="s">
+        <v>221</v>
+      </c>
+      <c r="S24" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T24" s="24" t="str">
@@ -4907,68 +5049,68 @@
         <f t="shared" si="39"/>
         <v>API Macros</v>
       </c>
-      <c r="V24" s="59" t="str">
+      <c r="V24" s="53" t="str">
         <f t="shared" si="39"/>
         <v>API Método</v>
       </c>
       <c r="W24" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X24" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X24" s="49" t="str">
         <f t="shared" ref="X24:X28" si="41">CONCATENATE("Key-REQ-",A24)</f>
         <v>Key-REQ-24</v>
       </c>
-      <c r="Y24" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z24" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA24" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB24" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC24" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD24" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="52">
+      <c r="Y24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC24" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD24" s="54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="50">
         <v>25</v>
       </c>
-      <c r="B25" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="C25" s="76" t="s">
-        <v>260</v>
-      </c>
-      <c r="D25" s="76" t="s">
-        <v>261</v>
-      </c>
-      <c r="E25" s="76" t="s">
-        <v>262</v>
-      </c>
-      <c r="F25" s="76" t="s">
+      <c r="B25" s="69" t="s">
+        <v>239</v>
+      </c>
+      <c r="C25" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D25" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="E25" s="70" t="s">
         <v>242</v>
       </c>
-      <c r="G25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K25" s="49" t="s">
+      <c r="F25" s="70" t="s">
+        <v>222</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H25" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I25" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J25" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K25" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L25" s="23" t="str">
@@ -4988,15 +5130,15 @@
         <v>Função Global</v>
       </c>
       <c r="P25" s="24" t="s">
-        <v>243</v>
+        <v>223</v>
       </c>
       <c r="Q25" s="24" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="R25" s="24" t="s">
-        <v>245</v>
-      </c>
-      <c r="S25" s="73" t="s">
+        <v>225</v>
+      </c>
+      <c r="S25" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T25" s="24" t="str">
@@ -5007,68 +5149,68 @@
         <f t="shared" si="39"/>
         <v>API Macros</v>
       </c>
-      <c r="V25" s="59" t="str">
+      <c r="V25" s="53" t="str">
         <f t="shared" si="39"/>
         <v>API Método</v>
       </c>
       <c r="W25" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X25" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X25" s="49" t="str">
         <f t="shared" si="41"/>
         <v>Key-REQ-25</v>
       </c>
-      <c r="Y25" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z25" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA25" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB25" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC25" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD25" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="52">
+      <c r="Y25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="50">
         <v>26</v>
       </c>
-      <c r="B26" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="C26" s="76" t="s">
-        <v>260</v>
-      </c>
-      <c r="D26" s="76" t="s">
-        <v>261</v>
-      </c>
-      <c r="E26" s="76" t="s">
-        <v>262</v>
-      </c>
-      <c r="F26" s="76" t="s">
-        <v>246</v>
-      </c>
-      <c r="G26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J26" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K26" s="49" t="s">
+      <c r="B26" s="69" t="s">
+        <v>239</v>
+      </c>
+      <c r="C26" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D26" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="E26" s="70" t="s">
+        <v>242</v>
+      </c>
+      <c r="F26" s="70" t="s">
+        <v>226</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J26" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K26" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L26" s="23" t="str">
@@ -5088,15 +5230,15 @@
         <v>Função Local</v>
       </c>
       <c r="P26" s="24" t="s">
-        <v>247</v>
+        <v>227</v>
       </c>
       <c r="Q26" s="24" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="R26" s="24" t="s">
-        <v>249</v>
-      </c>
-      <c r="S26" s="73" t="s">
+        <v>229</v>
+      </c>
+      <c r="S26" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T26" s="24" t="str">
@@ -5107,68 +5249,68 @@
         <f t="shared" si="39"/>
         <v>API Macros</v>
       </c>
-      <c r="V26" s="59" t="str">
+      <c r="V26" s="53" t="str">
         <f t="shared" si="39"/>
         <v>API Método</v>
       </c>
       <c r="W26" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X26" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X26" s="49" t="str">
         <f t="shared" si="41"/>
         <v>Key-REQ-26</v>
       </c>
-      <c r="Y26" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z26" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA26" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB26" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC26" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD26" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="52">
+      <c r="Y26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="50">
         <v>27</v>
       </c>
-      <c r="B27" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="C27" s="76" t="s">
-        <v>260</v>
-      </c>
-      <c r="D27" s="76" t="s">
-        <v>261</v>
-      </c>
-      <c r="E27" s="76" t="s">
-        <v>262</v>
-      </c>
-      <c r="F27" s="76" t="s">
-        <v>250</v>
-      </c>
-      <c r="G27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J27" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K27" s="49" t="s">
+      <c r="B27" s="69" t="s">
+        <v>239</v>
+      </c>
+      <c r="C27" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D27" s="70" t="s">
+        <v>241</v>
+      </c>
+      <c r="E27" s="70" t="s">
+        <v>242</v>
+      </c>
+      <c r="F27" s="70" t="s">
+        <v>230</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H27" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I27" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J27" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K27" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L27" s="23" t="str">
@@ -5188,15 +5330,15 @@
         <v>Função Filtro</v>
       </c>
       <c r="P27" s="24" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="Q27" s="24" t="s">
-        <v>252</v>
+        <v>232</v>
       </c>
       <c r="R27" s="24" t="s">
-        <v>253</v>
-      </c>
-      <c r="S27" s="73" t="s">
+        <v>233</v>
+      </c>
+      <c r="S27" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T27" s="24" t="str">
@@ -5207,68 +5349,68 @@
         <f t="shared" si="39"/>
         <v>API Macros</v>
       </c>
-      <c r="V27" s="59" t="str">
+      <c r="V27" s="53" t="str">
         <f t="shared" si="39"/>
         <v>API Método</v>
       </c>
       <c r="W27" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X27" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X27" s="49" t="str">
         <f t="shared" si="41"/>
         <v>Key-REQ-27</v>
       </c>
-      <c r="Y27" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z27" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA27" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB27" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC27" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD27" s="60" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:30" s="74" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="52">
+      <c r="Y27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC27" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD27" s="54" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:30" s="68" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="50">
         <v>28</v>
       </c>
-      <c r="B28" s="75" t="s">
-        <v>259</v>
-      </c>
-      <c r="C28" s="76" t="s">
-        <v>260</v>
-      </c>
-      <c r="D28" s="76" t="s">
-        <v>263</v>
-      </c>
-      <c r="E28" s="76" t="s">
-        <v>264</v>
-      </c>
-      <c r="F28" s="76" t="s">
-        <v>254</v>
-      </c>
-      <c r="G28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="H28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="I28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="J28" s="49" t="s">
-        <v>1</v>
-      </c>
-      <c r="K28" s="49" t="s">
+      <c r="B28" s="69" t="s">
+        <v>239</v>
+      </c>
+      <c r="C28" s="70" t="s">
+        <v>240</v>
+      </c>
+      <c r="D28" s="70" t="s">
+        <v>243</v>
+      </c>
+      <c r="E28" s="70" t="s">
+        <v>244</v>
+      </c>
+      <c r="F28" s="70" t="s">
+        <v>234</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="H28" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="I28" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="J28" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="K28" s="47" t="s">
         <v>1</v>
       </c>
       <c r="L28" s="23" t="str">
@@ -5288,15 +5430,15 @@
         <v>Bloco de Código</v>
       </c>
       <c r="P28" s="24" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="Q28" s="24" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="R28" s="24" t="s">
-        <v>257</v>
-      </c>
-      <c r="S28" s="73" t="s">
+        <v>237</v>
+      </c>
+      <c r="S28" s="67" t="s">
         <v>1</v>
       </c>
       <c r="T28" s="24" t="str">
@@ -5307,59 +5449,59 @@
         <f t="shared" si="39"/>
         <v>API Macros Visuais</v>
       </c>
-      <c r="V28" s="59" t="str">
+      <c r="V28" s="53" t="str">
         <f t="shared" si="39"/>
         <v>API Método Visual</v>
       </c>
       <c r="W28" s="24" t="s">
-        <v>133</v>
-      </c>
-      <c r="X28" s="51" t="str">
+        <v>113</v>
+      </c>
+      <c r="X28" s="49" t="str">
         <f t="shared" si="41"/>
         <v>Key-REQ-28</v>
       </c>
-      <c r="Y28" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z28" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA28" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB28" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC28" s="60" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD28" s="60" t="s">
+      <c r="Y28" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA28" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB28" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC28" s="54" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD28" s="54" t="s">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <conditionalFormatting sqref="A2:B23 A24:A28">
-    <cfRule type="cellIs" dxfId="32" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="28" priority="5" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:C1 L1:Q1 S1:X1 AA1:XFD1 A29:C1048576 L29:X1048576 AA29:XFD1048576">
-    <cfRule type="cellIs" dxfId="31" priority="441" operator="equal">
+    <cfRule type="cellIs" dxfId="27" priority="441" operator="equal">
       <formula>"null"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F1:F23 F29:F1048576">
-    <cfRule type="duplicateValues" dxfId="29" priority="18"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="R1:R23">
-    <cfRule type="cellIs" dxfId="27" priority="8" operator="equal">
-      <formula>"null"</formula>
-    </cfRule>
+    <cfRule type="duplicateValues" dxfId="26" priority="18"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F24:F28">
     <cfRule type="duplicateValues" dxfId="25" priority="1"/>
     <cfRule type="duplicateValues" dxfId="24" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="R1:R23">
+    <cfRule type="cellIs" dxfId="23" priority="8" operator="equal">
+      <formula>"null"</formula>
+    </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -5536,13 +5678,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C1" s="19" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="D1" s="19" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:4" s="28" customFormat="1" ht="8.25" customHeight="1" x14ac:dyDescent="0.15">
@@ -5587,39 +5729,39 @@
   <dimension ref="A1:AG20"/>
   <sheetFormatPr defaultColWidth="9.28515625" defaultRowHeight="7.35" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="2.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.28515625" style="48" customWidth="1"/>
-    <col min="4" max="4" width="7" style="48" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" style="48" customWidth="1"/>
-    <col min="6" max="6" width="3.42578125" style="48" customWidth="1"/>
-    <col min="7" max="7" width="4.5703125" style="48" customWidth="1"/>
-    <col min="8" max="8" width="7.85546875" style="48" customWidth="1"/>
-    <col min="9" max="9" width="11" style="48" customWidth="1"/>
-    <col min="10" max="10" width="6" style="48" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="46.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="4.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.85546875" style="48" customWidth="1"/>
-    <col min="16" max="16" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.42578125" style="57" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="8.42578125" style="48" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="40.7109375" style="57" customWidth="1"/>
-    <col min="20" max="20" width="5.7109375" style="48" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15.28515625" style="48" customWidth="1"/>
-    <col min="22" max="22" width="7.28515625" style="48" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.85546875" style="57" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="3.85546875" style="61" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="4.28515625" style="67" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="4.28515625" style="67" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="4.28515625" style="67" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="4.28515625" style="67" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="4.85546875" style="67" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.28515625" style="48"/>
+    <col min="1" max="1" width="2.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="46" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.28515625" style="46" customWidth="1"/>
+    <col min="4" max="4" width="7" style="46" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" style="46" customWidth="1"/>
+    <col min="6" max="6" width="3.42578125" style="46" customWidth="1"/>
+    <col min="7" max="7" width="4.5703125" style="46" customWidth="1"/>
+    <col min="8" max="8" width="7.85546875" style="46" customWidth="1"/>
+    <col min="9" max="9" width="11" style="46" customWidth="1"/>
+    <col min="10" max="10" width="6" style="46" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="46.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="4.7109375" style="46" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.85546875" style="46" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.42578125" style="51" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="8.42578125" style="46" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="40.7109375" style="51" customWidth="1"/>
+    <col min="20" max="20" width="5.7109375" style="46" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="15.28515625" style="46" customWidth="1"/>
+    <col min="22" max="22" width="7.28515625" style="46" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="9.85546875" style="51" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="3.85546875" style="55" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="4.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="4.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="4.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="4.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="4.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="4.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="4.28515625" style="61" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="4.85546875" style="61" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.28515625" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" ht="16.350000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -5627,75 +5769,75 @@
         <v>1</v>
       </c>
       <c r="B1" s="17" t="s">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="C1" s="38" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="D1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="E1" s="43" t="s">
-        <v>88</v>
+      <c r="E1" s="41" t="s">
+        <v>81</v>
       </c>
       <c r="F1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="G1" s="43" t="s">
-        <v>88</v>
+      <c r="G1" s="41" t="s">
+        <v>81</v>
       </c>
       <c r="H1" s="17" t="s">
         <v>33</v>
       </c>
       <c r="I1" s="37" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="J1" s="17" t="s">
         <v>33</v>
       </c>
       <c r="K1" s="37" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="L1" s="17" t="s">
         <v>33</v>
       </c>
       <c r="M1" s="37" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="N1" s="38" t="s">
         <v>33</v>
       </c>
       <c r="O1" s="37" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="P1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="Q1" s="43" t="s">
-        <v>88</v>
+      <c r="Q1" s="41" t="s">
+        <v>81</v>
       </c>
       <c r="R1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="S1" s="43" t="s">
-        <v>88</v>
+      <c r="S1" s="41" t="s">
+        <v>81</v>
       </c>
       <c r="T1" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="U1" s="43" t="s">
-        <v>88</v>
+      <c r="U1" s="41" t="s">
+        <v>81</v>
       </c>
       <c r="V1" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="W1" s="43" t="s">
-        <v>73</v>
-      </c>
-      <c r="X1" s="68" t="s">
+      <c r="W1" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="X1" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="Y1" s="69" t="s">
+      <c r="Y1" s="63" t="s">
         <v>34</v>
       </c>
       <c r="Z1" s="38" t="s">
@@ -5728,21 +5870,21 @@
         <v>2</v>
       </c>
       <c r="B2" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="70" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G2" s="42" t="s">
+        <v>114</v>
+      </c>
+      <c r="C2" s="64" t="s">
+        <v>67</v>
+      </c>
+      <c r="D2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G2" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H2" s="36" t="s">
@@ -5752,75 +5894,75 @@
         <v>1</v>
       </c>
       <c r="J2" s="36" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K2" s="25" t="s">
+        <v>143</v>
+      </c>
+      <c r="L2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="M2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="P2" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="25" t="s">
+        <v>1</v>
+      </c>
+      <c r="R2" s="26" t="s">
+        <v>116</v>
+      </c>
+      <c r="S2" s="33" t="s">
+        <v>117</v>
+      </c>
+      <c r="T2" s="26" t="s">
+        <v>118</v>
+      </c>
+      <c r="U2" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="V2" s="26" t="s">
+        <v>162</v>
+      </c>
+      <c r="W2" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="L2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="M2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="N2" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="O2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="P2" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="25" t="s">
-        <v>1</v>
-      </c>
-      <c r="R2" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="S2" s="33" t="s">
-        <v>137</v>
-      </c>
-      <c r="T2" s="26" t="s">
-        <v>138</v>
-      </c>
-      <c r="U2" s="31" t="s">
-        <v>139</v>
-      </c>
-      <c r="V2" s="26" t="s">
-        <v>182</v>
-      </c>
-      <c r="W2" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="X2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE2" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG2" s="42" t="s">
+      <c r="X2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG2" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5829,34 +5971,34 @@
         <v>3</v>
       </c>
       <c r="B3" s="32" t="s">
-        <v>145</v>
-      </c>
-      <c r="C3" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="42" t="s">
+        <v>125</v>
+      </c>
+      <c r="C3" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G3" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H3" s="36" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="I3" s="25" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="J3" s="36" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K3" s="25" t="s">
-        <v>159</v>
+        <v>139</v>
       </c>
       <c r="L3" s="36" t="s">
         <v>1</v>
@@ -5894,34 +6036,34 @@
       <c r="W3" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE3" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF3" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG3" s="42" t="s">
+      <c r="X3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -5930,34 +6072,34 @@
         <v>4</v>
       </c>
       <c r="B4" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="C4" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="D4" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E4" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G4" s="42" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="D4" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H4" s="36" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="I4" s="25" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="J4" s="36" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K4" s="25" t="s">
-        <v>160</v>
+        <v>140</v>
       </c>
       <c r="L4" s="36" t="s">
         <v>1</v>
@@ -5995,34 +6137,34 @@
       <c r="W4" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE4" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF4" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG4" s="42" t="s">
+      <c r="X4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6031,34 +6173,34 @@
         <v>5</v>
       </c>
       <c r="B5" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="C5" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="D5" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E5" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G5" s="42" t="s">
+        <v>127</v>
+      </c>
+      <c r="C5" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E5" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H5" s="36" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="I5" s="25" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="J5" s="36" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K5" s="25" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="L5" s="36" t="s">
         <v>1</v>
@@ -6096,34 +6238,34 @@
       <c r="W5" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE5" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF5" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG5" s="42" t="s">
+      <c r="X5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6132,34 +6274,34 @@
         <v>6</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="C6" s="70" t="s">
-        <v>174</v>
-      </c>
-      <c r="D6" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G6" s="42" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="64" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H6" s="36" t="s">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="I6" s="25" t="s">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="J6" s="36" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K6" s="25" t="s">
-        <v>162</v>
+        <v>142</v>
       </c>
       <c r="L6" s="36" t="s">
         <v>1</v>
@@ -6197,34 +6339,34 @@
       <c r="W6" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE6" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF6" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG6" s="42" t="s">
+      <c r="X6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6233,34 +6375,34 @@
         <v>7</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="C7" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="D7" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E7" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F7" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="G7" s="58" t="s">
-        <v>145</v>
+        <v>148</v>
+      </c>
+      <c r="C7" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F7" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="52" t="s">
+        <v>125</v>
       </c>
       <c r="H7" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I7" s="25" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="J7" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K7" s="25" t="s">
-        <v>164</v>
+        <v>144</v>
       </c>
       <c r="L7" s="36" t="s">
         <v>1</v>
@@ -6298,34 +6440,34 @@
       <c r="W7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE7" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF7" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG7" s="42" t="s">
+      <c r="X7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6334,34 +6476,34 @@
         <v>8</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E8" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F8" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="G8" s="58" t="s">
-        <v>146</v>
+        <v>149</v>
+      </c>
+      <c r="C8" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E8" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F8" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>126</v>
       </c>
       <c r="H8" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I8" s="25" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="J8" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K8" s="25" t="s">
-        <v>165</v>
+        <v>145</v>
       </c>
       <c r="L8" s="36" t="s">
         <v>1</v>
@@ -6399,34 +6541,34 @@
       <c r="W8" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE8" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF8" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG8" s="42" t="s">
+      <c r="X8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6435,34 +6577,34 @@
         <v>9</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="D9" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F9" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="G9" s="58" t="s">
-        <v>147</v>
+        <v>150</v>
+      </c>
+      <c r="C9" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="D9" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E9" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F9" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="52" t="s">
+        <v>127</v>
       </c>
       <c r="H9" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I9" s="25" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="J9" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K9" s="25" t="s">
-        <v>166</v>
+        <v>146</v>
       </c>
       <c r="L9" s="36" t="s">
         <v>1</v>
@@ -6500,34 +6642,34 @@
       <c r="W9" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE9" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF9" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG9" s="42" t="s">
+      <c r="X9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6536,34 +6678,34 @@
         <v>10</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>171</v>
-      </c>
-      <c r="C10" s="71" t="s">
-        <v>178</v>
-      </c>
-      <c r="D10" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E10" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" s="47" t="s">
-        <v>199</v>
-      </c>
-      <c r="G10" s="58" t="s">
-        <v>148</v>
+        <v>151</v>
+      </c>
+      <c r="C10" s="65" t="s">
+        <v>158</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E10" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>179</v>
+      </c>
+      <c r="G10" s="52" t="s">
+        <v>128</v>
       </c>
       <c r="H10" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I10" s="25" t="s">
-        <v>185</v>
+        <v>165</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K10" s="25" t="s">
-        <v>167</v>
+        <v>147</v>
       </c>
       <c r="L10" s="36" t="s">
         <v>1</v>
@@ -6601,34 +6743,34 @@
       <c r="W10" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE10" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF10" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG10" s="42" t="s">
+      <c r="X10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6637,34 +6779,34 @@
         <v>11</v>
       </c>
       <c r="B11" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="70" t="s">
-        <v>193</v>
-      </c>
-      <c r="D11" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E11" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G11" s="42" t="s">
+        <v>137</v>
+      </c>
+      <c r="C11" s="64" t="s">
+        <v>173</v>
+      </c>
+      <c r="D11" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E11" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H11" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I11" s="25" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="J11" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K11" s="25" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="L11" s="36" t="s">
         <v>1</v>
@@ -6702,34 +6844,34 @@
       <c r="W11" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE11" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF11" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG11" s="42" t="s">
+      <c r="X11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC11" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE11" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6738,34 +6880,34 @@
         <v>12</v>
       </c>
       <c r="B12" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="C12" s="70" t="s">
-        <v>195</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G12" s="42" t="s">
+        <v>136</v>
+      </c>
+      <c r="C12" s="64" t="s">
+        <v>175</v>
+      </c>
+      <c r="D12" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H12" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I12" s="25" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="J12" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K12" s="25" t="s">
-        <v>141</v>
+        <v>121</v>
       </c>
       <c r="L12" s="36" t="s">
         <v>1</v>
@@ -6803,34 +6945,34 @@
       <c r="W12" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE12" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF12" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG12" s="42" t="s">
+      <c r="X12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6839,34 +6981,34 @@
         <v>13</v>
       </c>
       <c r="B13" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="C13" s="70" t="s">
-        <v>196</v>
-      </c>
-      <c r="D13" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G13" s="42" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" s="64" t="s">
+        <v>176</v>
+      </c>
+      <c r="D13" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E13" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H13" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I13" s="25" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="J13" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K13" s="25" t="s">
-        <v>142</v>
+        <v>122</v>
       </c>
       <c r="L13" s="36" t="s">
         <v>1</v>
@@ -6904,34 +7046,34 @@
       <c r="W13" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE13" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF13" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG13" s="42" t="s">
+      <c r="X13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -6940,34 +7082,34 @@
         <v>14</v>
       </c>
       <c r="B14" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="C14" s="70" t="s">
-        <v>194</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E14" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="F14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G14" s="42" t="s">
+      <c r="C14" s="64" t="s">
+        <v>174</v>
+      </c>
+      <c r="D14" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E14" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H14" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I14" s="25" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="J14" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K14" s="25" t="s">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="L14" s="36" t="s">
         <v>1</v>
@@ -7005,34 +7147,34 @@
       <c r="W14" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE14" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF14" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG14" s="42" t="s">
+      <c r="X14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y14" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC14" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="40" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7041,34 +7183,34 @@
         <v>15</v>
       </c>
       <c r="B15" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="C15" s="70" t="s">
-        <v>197</v>
-      </c>
-      <c r="D15" s="47" t="s">
-        <v>181</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="F15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G15" s="42" t="s">
+        <v>138</v>
+      </c>
+      <c r="C15" s="64" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="45" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="F15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H15" s="36" t="s">
-        <v>184</v>
+        <v>164</v>
       </c>
       <c r="I15" s="25" t="s">
-        <v>186</v>
+        <v>166</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="K15" s="25" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="L15" s="36" t="s">
         <v>1</v>
@@ -7106,57 +7248,57 @@
       <c r="W15" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE15" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF15" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG15" s="42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y15" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC15" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="30">
         <v>16</v>
       </c>
-      <c r="B16" s="62" t="s">
-        <v>215</v>
-      </c>
-      <c r="C16" s="76" t="s">
-        <v>250</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G16" s="42" t="s">
+      <c r="B16" s="56" t="s">
+        <v>195</v>
+      </c>
+      <c r="C16" s="70" t="s">
+        <v>230</v>
+      </c>
+      <c r="D16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G16" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H16" s="36" t="s">
@@ -7165,30 +7307,30 @@
       <c r="I16" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J16" s="64" t="s">
-        <v>79</v>
+      <c r="J16" s="58" t="s">
+        <v>72</v>
       </c>
       <c r="K16" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="L16" s="63" t="s">
-        <v>216</v>
+        <v>200</v>
+      </c>
+      <c r="L16" s="57" t="s">
+        <v>196</v>
       </c>
       <c r="M16" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="N16" s="63" t="s">
-        <v>218</v>
+        <v>197</v>
+      </c>
+      <c r="N16" s="57" t="s">
+        <v>198</v>
       </c>
       <c r="O16" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="P16" s="65" t="str">
+        <v>199</v>
+      </c>
+      <c r="P16" s="59" t="str">
         <f t="shared" ref="P16:P20" si="0">IF(Q16="null", "null", "método.revit")</f>
         <v>método.revit</v>
       </c>
-      <c r="Q16" s="66" t="s">
-        <v>221</v>
+      <c r="Q16" s="60" t="s">
+        <v>201</v>
       </c>
       <c r="R16" s="36" t="s">
         <v>1</v>
@@ -7196,69 +7338,69 @@
       <c r="S16" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T16" s="63" t="s">
+      <c r="T16" s="57" t="s">
         <v>1</v>
       </c>
       <c r="U16" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V16" s="72" t="s">
+      <c r="V16" s="66" t="s">
         <v>1</v>
       </c>
       <c r="W16" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE16" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF16" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y16" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="30">
         <v>17</v>
       </c>
-      <c r="B17" s="62" t="s">
-        <v>222</v>
-      </c>
-      <c r="C17" s="76" t="s">
-        <v>250</v>
-      </c>
-      <c r="D17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G17" s="42" t="s">
+      <c r="B17" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" s="70" t="s">
+        <v>230</v>
+      </c>
+      <c r="D17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E17" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H17" s="36" t="s">
@@ -7267,30 +7409,30 @@
       <c r="I17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J17" s="64" t="s">
-        <v>79</v>
+      <c r="J17" s="58" t="s">
+        <v>72</v>
       </c>
       <c r="K17" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="L17" s="63" t="s">
-        <v>216</v>
+        <v>204</v>
+      </c>
+      <c r="L17" s="57" t="s">
+        <v>196</v>
       </c>
       <c r="M17" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="N17" s="63" t="s">
-        <v>218</v>
+        <v>197</v>
+      </c>
+      <c r="N17" s="57" t="s">
+        <v>198</v>
       </c>
       <c r="O17" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="P17" s="65" t="str">
+        <v>203</v>
+      </c>
+      <c r="P17" s="59" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q17" s="66" t="s">
-        <v>225</v>
+      <c r="Q17" s="60" t="s">
+        <v>205</v>
       </c>
       <c r="R17" s="36" t="s">
         <v>1</v>
@@ -7298,69 +7440,69 @@
       <c r="S17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T17" s="63" t="s">
+      <c r="T17" s="57" t="s">
         <v>1</v>
       </c>
       <c r="U17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V17" s="72" t="s">
+      <c r="V17" s="66" t="s">
         <v>1</v>
       </c>
       <c r="W17" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE17" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF17" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG17" s="42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y17" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="30">
         <v>18</v>
       </c>
-      <c r="B18" s="62" t="s">
-        <v>226</v>
-      </c>
-      <c r="C18" s="76" t="s">
-        <v>250</v>
-      </c>
-      <c r="D18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G18" s="42" t="s">
+      <c r="B18" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="C18" s="70" t="s">
+        <v>230</v>
+      </c>
+      <c r="D18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G18" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H18" s="36" t="s">
@@ -7369,30 +7511,30 @@
       <c r="I18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J18" s="64" t="s">
-        <v>79</v>
+      <c r="J18" s="58" t="s">
+        <v>72</v>
       </c>
       <c r="K18" s="25" t="s">
-        <v>228</v>
-      </c>
-      <c r="L18" s="63" t="s">
-        <v>216</v>
+        <v>208</v>
+      </c>
+      <c r="L18" s="57" t="s">
+        <v>196</v>
       </c>
       <c r="M18" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="N18" s="63" t="s">
-        <v>218</v>
+        <v>197</v>
+      </c>
+      <c r="N18" s="57" t="s">
+        <v>198</v>
       </c>
       <c r="O18" s="25" t="s">
-        <v>227</v>
-      </c>
-      <c r="P18" s="65" t="str">
+        <v>207</v>
+      </c>
+      <c r="P18" s="59" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q18" s="66" t="s">
-        <v>229</v>
+      <c r="Q18" s="60" t="s">
+        <v>209</v>
       </c>
       <c r="R18" s="36" t="s">
         <v>1</v>
@@ -7400,69 +7542,69 @@
       <c r="S18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T18" s="63" t="s">
+      <c r="T18" s="57" t="s">
         <v>1</v>
       </c>
       <c r="U18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V18" s="72" t="s">
+      <c r="V18" s="66" t="s">
         <v>1</v>
       </c>
       <c r="W18" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE18" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF18" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG18" s="42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y18" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC18" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="30">
         <v>19</v>
       </c>
-      <c r="B19" s="62" t="s">
+      <c r="B19" s="56" t="s">
+        <v>210</v>
+      </c>
+      <c r="C19" s="70" t="s">
         <v>230</v>
       </c>
-      <c r="C19" s="76" t="s">
-        <v>250</v>
-      </c>
-      <c r="D19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G19" s="42" t="s">
+      <c r="D19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E19" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G19" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H19" s="36" t="s">
@@ -7471,30 +7613,30 @@
       <c r="I19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J19" s="64" t="s">
-        <v>79</v>
+      <c r="J19" s="58" t="s">
+        <v>72</v>
       </c>
       <c r="K19" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="L19" s="63" t="s">
-        <v>216</v>
+        <v>212</v>
+      </c>
+      <c r="L19" s="57" t="s">
+        <v>196</v>
       </c>
       <c r="M19" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="N19" s="63" t="s">
-        <v>218</v>
+        <v>197</v>
+      </c>
+      <c r="N19" s="57" t="s">
+        <v>198</v>
       </c>
       <c r="O19" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="P19" s="65" t="str">
+        <v>211</v>
+      </c>
+      <c r="P19" s="59" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q19" s="66" t="s">
-        <v>233</v>
+      <c r="Q19" s="60" t="s">
+        <v>213</v>
       </c>
       <c r="R19" s="36" t="s">
         <v>1</v>
@@ -7502,69 +7644,69 @@
       <c r="S19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T19" s="63" t="s">
+      <c r="T19" s="57" t="s">
         <v>1</v>
       </c>
       <c r="U19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V19" s="72" t="s">
+      <c r="V19" s="66" t="s">
         <v>1</v>
       </c>
       <c r="W19" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE19" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF19" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG19" s="42" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:33" s="67" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="X19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y19" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC19" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="40" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" s="61" customFormat="1" ht="6.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="30">
         <v>20</v>
       </c>
-      <c r="B20" s="62" t="s">
-        <v>234</v>
-      </c>
-      <c r="C20" s="76" t="s">
-        <v>250</v>
-      </c>
-      <c r="D20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="E20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="F20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="G20" s="42" t="s">
+      <c r="B20" s="56" t="s">
+        <v>214</v>
+      </c>
+      <c r="C20" s="70" t="s">
+        <v>230</v>
+      </c>
+      <c r="D20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="F20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="G20" s="40" t="s">
         <v>1</v>
       </c>
       <c r="H20" s="36" t="s">
@@ -7573,30 +7715,30 @@
       <c r="I20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="J20" s="64" t="s">
-        <v>79</v>
+      <c r="J20" s="58" t="s">
+        <v>72</v>
       </c>
       <c r="K20" s="25" t="s">
-        <v>236</v>
-      </c>
-      <c r="L20" s="63" t="s">
         <v>216</v>
       </c>
+      <c r="L20" s="57" t="s">
+        <v>196</v>
+      </c>
       <c r="M20" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="N20" s="63" t="s">
-        <v>218</v>
+        <v>197</v>
+      </c>
+      <c r="N20" s="57" t="s">
+        <v>198</v>
       </c>
       <c r="O20" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="P20" s="65" t="str">
+        <v>215</v>
+      </c>
+      <c r="P20" s="59" t="str">
         <f t="shared" si="0"/>
         <v>método.revit</v>
       </c>
-      <c r="Q20" s="66" t="s">
-        <v>237</v>
+      <c r="Q20" s="60" t="s">
+        <v>217</v>
       </c>
       <c r="R20" s="36" t="s">
         <v>1</v>
@@ -7604,46 +7746,46 @@
       <c r="S20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="T20" s="63" t="s">
+      <c r="T20" s="57" t="s">
         <v>1</v>
       </c>
       <c r="U20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="V20" s="72" t="s">
+      <c r="V20" s="66" t="s">
         <v>1</v>
       </c>
       <c r="W20" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="X20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="Y20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AA20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AB20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AC20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AD20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AE20" s="42" t="s">
-        <v>1</v>
-      </c>
-      <c r="AF20" s="47" t="s">
-        <v>1</v>
-      </c>
-      <c r="AG20" s="42" t="s">
+      <c r="X20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AB20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="40" t="s">
         <v>1</v>
       </c>
     </row>
